--- a/hardware/bom/master_bom.xlsx
+++ b/hardware/bom/master_bom.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Volumes/POLI/Magistrale/21_ACAV/F1tenth_PoliMI/hardware/bom/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A0E5D092-A3A5-0D42-B3FE-32228A3DBCD3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{01780B49-EB64-6C40-A11A-738064B3CA79}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="4360" yWindow="660" windowWidth="30200" windowHeight="19820" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="100" yWindow="660" windowWidth="17300" windowHeight="19820" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="(POLIMI) Rally + Orin Nano v1" sheetId="9" r:id="rId1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="266" uniqueCount="181">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="265" uniqueCount="180">
   <si>
     <t>Scroll right to see links</t>
   </si>
@@ -641,9 +641,6 @@
     <t>Choose ONE of the listed options</t>
   </si>
   <si>
-    <t>TOTAL in the Kit = 720 pcs</t>
-  </si>
-  <si>
     <t>TOTAL in the Kit = 720 pcs (Note: ~8$ + 12$ shipping, same supplier as above so ordering together may cut costs)</t>
   </si>
   <si>
@@ -717,12 +714,6 @@
     <t>https://amzn.eu/d/04ogTQuG</t>
   </si>
   <si>
-    <t>https://a.co/d/0dyM1Yp7</t>
-  </si>
-  <si>
-    <t>https://a.co/d/01DhHfBo</t>
-  </si>
-  <si>
     <t>https://amzn.eu/d/0934urF9</t>
   </si>
   <si>
@@ -744,19 +735,10 @@
     <t>https://orders.ambimat.com/product/roboracer-power-board-multi-qty-rohs-compliant/</t>
   </si>
   <si>
-    <t>https://a.co/d/0aQPatBC</t>
-  </si>
-  <si>
-    <t>https://a.co/d/0bI2TfQP</t>
-  </si>
-  <si>
     <t>https://amzn.eu/d/04H49Gdl</t>
   </si>
   <si>
     <t>https://amzn.eu/d/0ibdH4zI</t>
-  </si>
-  <si>
-    <t>https://a.co/d/0hFfle4p</t>
   </si>
   <si>
     <t>https://amzn.eu/d/0ak3Mr9H</t>
@@ -859,7 +841,22 @@
     <t>Updated: 2026-09-24</t>
   </si>
   <si>
-    <t>s</t>
+    <t>https://amzn.eu/d/096jB5FS</t>
+  </si>
+  <si>
+    <t>https://amzn.eu/d/0dPEUR2n</t>
+  </si>
+  <si>
+    <t>https://amzn.eu/d/02tJmKlW</t>
+  </si>
+  <si>
+    <t>https://amzn.eu/d/09jG02MS</t>
+  </si>
+  <si>
+    <t>TOTAL in the Kit = 480 pcs</t>
+  </si>
+  <si>
+    <t>https://amzn.eu/d/0hnQ0stW</t>
   </si>
 </sst>
 </file>
@@ -1636,7 +1633,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="45" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="176">
+  <cellXfs count="175">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left"/>
@@ -1932,9 +1929,6 @@
     <xf numFmtId="0" fontId="47" fillId="5" borderId="8" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="47" fillId="6" borderId="8" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
@@ -2019,6 +2013,36 @@
     <xf numFmtId="0" fontId="56" fillId="9" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="6" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="6" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="52" fillId="6" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="52" fillId="6" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="3" fillId="5" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="3" fillId="5" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="6" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="6" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="50" fillId="6" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="50" fillId="6" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
@@ -2060,36 +2084,6 @@
     </xf>
     <xf numFmtId="0" fontId="46" fillId="5" borderId="10" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="3" fillId="5" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="3" fillId="5" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="6" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="6" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="52" fillId="6" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="52" fillId="6" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="6" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="6" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="50" fillId="6" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="50" fillId="6" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="26" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
@@ -2336,25 +2330,25 @@
   <sheetData>
     <row r="1" spans="2:14" ht="17" thickBot="1"/>
     <row r="2" spans="2:14" s="95" customFormat="1" ht="23" thickBot="1">
-      <c r="B2" s="140" t="s">
+      <c r="B2" s="139" t="s">
         <v>0</v>
       </c>
-      <c r="C2" s="141" t="s">
+      <c r="C2" s="140" t="s">
         <v>1</v>
       </c>
-      <c r="D2" s="142" t="s">
-        <v>178</v>
-      </c>
-      <c r="E2" s="142" t="s">
+      <c r="D2" s="141" t="s">
+        <v>172</v>
+      </c>
+      <c r="E2" s="141" t="s">
         <v>131</v>
       </c>
-      <c r="F2" s="142" t="s">
-        <v>140</v>
-      </c>
-      <c r="G2" s="143" t="s">
+      <c r="F2" s="141" t="s">
+        <v>139</v>
+      </c>
+      <c r="G2" s="142" t="s">
         <v>4</v>
       </c>
-      <c r="H2" s="144" t="s">
+      <c r="H2" s="143" t="s">
         <v>130</v>
       </c>
       <c r="I2" s="104"/>
@@ -2364,15 +2358,15 @@
       <c r="M2" s="94"/>
     </row>
     <row r="3" spans="2:14" ht="17">
-      <c r="B3" s="134" t="s">
+      <c r="B3" s="133" t="s">
         <v>6</v>
       </c>
-      <c r="C3" s="135"/>
-      <c r="D3" s="136"/>
-      <c r="E3" s="136"/>
-      <c r="F3" s="137"/>
-      <c r="G3" s="138"/>
-      <c r="H3" s="139"/>
+      <c r="C3" s="134"/>
+      <c r="D3" s="135"/>
+      <c r="E3" s="135"/>
+      <c r="F3" s="136"/>
+      <c r="G3" s="137"/>
+      <c r="H3" s="138"/>
       <c r="I3" s="105"/>
       <c r="J3" s="60"/>
       <c r="K3" s="60"/>
@@ -2381,10 +2375,10 @@
       <c r="N3" s="61"/>
     </row>
     <row r="4" spans="2:14" ht="17">
-      <c r="B4" s="162" t="s">
-        <v>149</v>
-      </c>
-      <c r="C4" s="126">
+      <c r="B4" s="145" t="s">
+        <v>148</v>
+      </c>
+      <c r="C4" s="125">
         <v>1</v>
       </c>
       <c r="D4" s="69">
@@ -2395,11 +2389,11 @@
         <v>479.9</v>
       </c>
       <c r="F4" s="69"/>
-      <c r="G4" s="164" t="s">
-        <v>176</v>
+      <c r="G4" s="147" t="s">
+        <v>170</v>
       </c>
       <c r="H4" s="112" t="s">
-        <v>172</v>
+        <v>166</v>
       </c>
       <c r="I4" s="105"/>
       <c r="J4" s="60"/>
@@ -2409,8 +2403,8 @@
       <c r="N4" s="61"/>
     </row>
     <row r="5" spans="2:14" ht="17">
-      <c r="B5" s="163"/>
-      <c r="C5" s="126">
+      <c r="B5" s="146"/>
+      <c r="C5" s="125">
         <v>1</v>
       </c>
       <c r="D5" s="69">
@@ -2421,11 +2415,11 @@
         <v>425</v>
       </c>
       <c r="F5" s="69" t="s">
-        <v>141</v>
-      </c>
-      <c r="G5" s="165"/>
+        <v>140</v>
+      </c>
+      <c r="G5" s="148"/>
       <c r="H5" s="112" t="s">
-        <v>173</v>
+        <v>167</v>
       </c>
       <c r="I5" s="105"/>
       <c r="J5" s="60"/>
@@ -2435,8 +2429,8 @@
       <c r="N5" s="61"/>
     </row>
     <row r="6" spans="2:14" ht="17">
-      <c r="B6" s="163"/>
-      <c r="C6" s="126">
+      <c r="B6" s="146"/>
+      <c r="C6" s="125">
         <v>1</v>
       </c>
       <c r="D6" s="69">
@@ -2447,9 +2441,9 @@
         <v>425</v>
       </c>
       <c r="F6" s="69"/>
-      <c r="G6" s="165"/>
+      <c r="G6" s="148"/>
       <c r="H6" s="112" t="s">
-        <v>174</v>
+        <v>168</v>
       </c>
       <c r="I6" s="105"/>
       <c r="J6" s="60"/>
@@ -2459,10 +2453,10 @@
       <c r="N6" s="61"/>
     </row>
     <row r="7" spans="2:14" ht="17">
-      <c r="B7" s="131" t="s">
+      <c r="B7" s="130" t="s">
         <v>16</v>
       </c>
-      <c r="C7" s="127">
+      <c r="C7" s="126">
         <v>1</v>
       </c>
       <c r="D7" s="67">
@@ -2473,11 +2467,11 @@
         <v>88.99</v>
       </c>
       <c r="F7" s="67" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="G7" s="66"/>
       <c r="H7" s="113" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="I7" s="106"/>
       <c r="J7" s="60"/>
@@ -2487,10 +2481,10 @@
       <c r="N7" s="61"/>
     </row>
     <row r="8" spans="2:14" ht="17">
-      <c r="B8" s="132" t="s">
+      <c r="B8" s="131" t="s">
         <v>20</v>
       </c>
-      <c r="C8" s="126">
+      <c r="C8" s="125">
         <v>1</v>
       </c>
       <c r="D8" s="69">
@@ -2501,11 +2495,11 @@
         <v>69.989999999999995</v>
       </c>
       <c r="F8" s="69" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="G8" s="68"/>
       <c r="H8" s="112" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="I8" s="106"/>
       <c r="J8" s="60"/>
@@ -2515,10 +2509,10 @@
       <c r="N8" s="61"/>
     </row>
     <row r="9" spans="2:14" ht="17">
-      <c r="B9" s="131" t="s">
+      <c r="B9" s="130" t="s">
         <v>24</v>
       </c>
-      <c r="C9" s="127">
+      <c r="C9" s="126">
         <v>1</v>
       </c>
       <c r="D9" s="67">
@@ -2529,7 +2523,7 @@
         <v>10</v>
       </c>
       <c r="F9" s="67" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="G9" s="66" t="s">
         <v>25</v>
@@ -2545,10 +2539,10 @@
       <c r="N9" s="61"/>
     </row>
     <row r="10" spans="2:14" ht="17">
-      <c r="B10" s="132" t="s">
+      <c r="B10" s="131" t="s">
         <v>31</v>
       </c>
-      <c r="C10" s="126">
+      <c r="C10" s="125">
         <v>1</v>
       </c>
       <c r="D10" s="69">
@@ -2559,7 +2553,7 @@
         <v>20</v>
       </c>
       <c r="F10" s="69" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="G10" s="68" t="s">
         <v>32</v>
@@ -2575,10 +2569,10 @@
       <c r="N10" s="61"/>
     </row>
     <row r="11" spans="2:14" ht="17">
-      <c r="B11" s="130" t="s">
+      <c r="B11" s="129" t="s">
         <v>39</v>
       </c>
-      <c r="C11" s="125"/>
+      <c r="C11" s="124"/>
       <c r="D11" s="59"/>
       <c r="E11" s="59"/>
       <c r="F11" s="73"/>
@@ -2592,27 +2586,27 @@
       <c r="N11" s="61"/>
     </row>
     <row r="12" spans="2:14" ht="17">
-      <c r="B12" s="131" t="s">
+      <c r="B12" s="130" t="s">
         <v>40</v>
       </c>
-      <c r="C12" s="127">
+      <c r="C12" s="126">
         <v>1</v>
       </c>
       <c r="D12" s="67">
-        <v>20.32</v>
+        <v>13</v>
       </c>
       <c r="E12" s="67">
         <f t="shared" si="1"/>
-        <v>20.32</v>
+        <v>13</v>
       </c>
       <c r="F12" s="67" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="G12" s="66" t="s">
-        <v>134</v>
-      </c>
-      <c r="H12" s="116" t="s">
-        <v>152</v>
+        <v>178</v>
+      </c>
+      <c r="H12" s="113" t="s">
+        <v>177</v>
       </c>
       <c r="I12" s="106"/>
       <c r="J12" s="60"/>
@@ -2622,27 +2616,27 @@
       <c r="N12" s="61"/>
     </row>
     <row r="13" spans="2:14" ht="17">
-      <c r="B13" s="132" t="s">
+      <c r="B13" s="131" t="s">
         <v>43</v>
       </c>
-      <c r="C13" s="126">
+      <c r="C13" s="125">
         <v>1</v>
       </c>
       <c r="D13" s="69">
-        <v>20.239999999999998</v>
+        <v>16</v>
       </c>
       <c r="E13" s="69">
         <f>C13*D13</f>
-        <v>20.239999999999998</v>
+        <v>16</v>
       </c>
       <c r="F13" s="69" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="G13" s="68" t="s">
-        <v>135</v>
-      </c>
-      <c r="H13" s="117" t="s">
-        <v>153</v>
+        <v>134</v>
+      </c>
+      <c r="H13" s="112" t="s">
+        <v>179</v>
       </c>
       <c r="I13" s="106"/>
       <c r="J13" s="60"/>
@@ -2652,27 +2646,27 @@
       <c r="N13" s="61"/>
     </row>
     <row r="14" spans="2:14" ht="17">
-      <c r="B14" s="131" t="s">
+      <c r="B14" s="130" t="s">
         <v>51</v>
       </c>
-      <c r="C14" s="150">
+      <c r="C14" s="159">
         <v>1</v>
       </c>
-      <c r="D14" s="160">
+      <c r="D14" s="149">
         <v>12</v>
       </c>
-      <c r="E14" s="160">
+      <c r="E14" s="149">
         <f>C14*D14</f>
         <v>12</v>
       </c>
-      <c r="F14" s="160" t="s">
-        <v>141</v>
-      </c>
-      <c r="G14" s="156" t="s">
-        <v>136</v>
-      </c>
-      <c r="H14" s="158" t="s">
-        <v>154</v>
+      <c r="F14" s="149" t="s">
+        <v>140</v>
+      </c>
+      <c r="G14" s="165" t="s">
+        <v>135</v>
+      </c>
+      <c r="H14" s="167" t="s">
+        <v>151</v>
       </c>
       <c r="I14" s="106"/>
       <c r="J14" s="60"/>
@@ -2682,15 +2676,15 @@
       <c r="N14" s="61"/>
     </row>
     <row r="15" spans="2:14" ht="17">
-      <c r="B15" s="131" t="s">
+      <c r="B15" s="130" t="s">
         <v>55</v>
       </c>
-      <c r="C15" s="151"/>
-      <c r="D15" s="161"/>
-      <c r="E15" s="161"/>
-      <c r="F15" s="161"/>
-      <c r="G15" s="157"/>
-      <c r="H15" s="159"/>
+      <c r="C15" s="160"/>
+      <c r="D15" s="150"/>
+      <c r="E15" s="150"/>
+      <c r="F15" s="150"/>
+      <c r="G15" s="166"/>
+      <c r="H15" s="168"/>
       <c r="I15" s="106"/>
       <c r="J15" s="60"/>
       <c r="K15" s="60"/>
@@ -2699,27 +2693,27 @@
       <c r="N15" s="61"/>
     </row>
     <row r="16" spans="2:14" ht="17">
-      <c r="B16" s="132" t="s">
+      <c r="B16" s="131" t="s">
         <v>60</v>
       </c>
-      <c r="C16" s="126">
+      <c r="C16" s="125">
         <v>1</v>
       </c>
-      <c r="D16" s="69" t="s">
-        <v>180</v>
-      </c>
-      <c r="E16" s="69" t="e">
+      <c r="D16" s="69">
+        <v>14.39</v>
+      </c>
+      <c r="E16" s="69">
         <f t="shared" si="1"/>
-        <v>#VALUE!</v>
+        <v>14.39</v>
       </c>
       <c r="F16" s="69" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="G16" s="68" t="s">
-        <v>137</v>
-      </c>
-      <c r="H16" s="117" t="s">
-        <v>155</v>
+        <v>136</v>
+      </c>
+      <c r="H16" s="112" t="s">
+        <v>152</v>
       </c>
       <c r="I16" s="106"/>
       <c r="J16" s="60"/>
@@ -2729,10 +2723,10 @@
       <c r="N16" s="61"/>
     </row>
     <row r="17" spans="2:29" ht="34">
-      <c r="B17" s="131" t="s">
+      <c r="B17" s="130" t="s">
         <v>63</v>
       </c>
-      <c r="C17" s="127">
+      <c r="C17" s="126">
         <v>1</v>
       </c>
       <c r="D17" s="67">
@@ -2743,13 +2737,13 @@
         <v>9.7899999999999991</v>
       </c>
       <c r="F17" s="67" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="G17" s="66" t="s">
-        <v>138</v>
-      </c>
-      <c r="H17" s="116" t="s">
-        <v>156</v>
+        <v>137</v>
+      </c>
+      <c r="H17" s="113" t="s">
+        <v>153</v>
       </c>
       <c r="I17" s="106"/>
       <c r="J17" s="60"/>
@@ -2759,10 +2753,10 @@
       <c r="N17" s="61"/>
     </row>
     <row r="18" spans="2:29" ht="17">
-      <c r="B18" s="132" t="s">
+      <c r="B18" s="131" t="s">
         <v>67</v>
       </c>
-      <c r="C18" s="126">
+      <c r="C18" s="125">
         <v>1</v>
       </c>
       <c r="D18" s="69">
@@ -2773,13 +2767,13 @@
         <v>8.9</v>
       </c>
       <c r="F18" s="69" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="G18" s="68" t="s">
-        <v>139</v>
-      </c>
-      <c r="H18" s="117" t="s">
-        <v>157</v>
+        <v>138</v>
+      </c>
+      <c r="H18" s="112" t="s">
+        <v>154</v>
       </c>
       <c r="I18" s="106"/>
       <c r="J18" s="60"/>
@@ -2789,15 +2783,15 @@
       <c r="N18" s="61"/>
     </row>
     <row r="19" spans="2:29" ht="17">
-      <c r="B19" s="130" t="s">
+      <c r="B19" s="129" t="s">
         <v>71</v>
       </c>
-      <c r="C19" s="128"/>
+      <c r="C19" s="127"/>
       <c r="D19" s="65"/>
       <c r="E19" s="59"/>
       <c r="F19" s="73"/>
       <c r="G19" s="64"/>
-      <c r="H19" s="118"/>
+      <c r="H19" s="117"/>
       <c r="I19" s="108"/>
       <c r="J19" s="96"/>
       <c r="K19" s="96"/>
@@ -2820,10 +2814,10 @@
       <c r="AB19" s="97"/>
     </row>
     <row r="20" spans="2:29" ht="17">
-      <c r="B20" s="131" t="s">
+      <c r="B20" s="130" t="s">
         <v>74</v>
       </c>
-      <c r="C20" s="127">
+      <c r="C20" s="126">
         <v>1</v>
       </c>
       <c r="D20" s="67">
@@ -2834,9 +2828,9 @@
         <v>355</v>
       </c>
       <c r="F20" s="67" t="s">
-        <v>141</v>
-      </c>
-      <c r="G20" s="148" t="s">
+        <v>140</v>
+      </c>
+      <c r="G20" s="157" t="s">
         <v>133</v>
       </c>
       <c r="H20" s="116" t="s">
@@ -2864,8 +2858,8 @@
       <c r="AB20" s="97"/>
     </row>
     <row r="21" spans="2:29" ht="17">
-      <c r="B21" s="131"/>
-      <c r="C21" s="127">
+      <c r="B21" s="130"/>
+      <c r="C21" s="126">
         <v>1</v>
       </c>
       <c r="D21" s="67">
@@ -2876,9 +2870,9 @@
         <v>529</v>
       </c>
       <c r="F21" s="67"/>
-      <c r="G21" s="155"/>
+      <c r="G21" s="164"/>
       <c r="H21" s="116" t="s">
-        <v>158</v>
+        <v>155</v>
       </c>
       <c r="I21" s="108"/>
       <c r="J21" s="96"/>
@@ -2902,10 +2896,10 @@
       <c r="AB21" s="97"/>
     </row>
     <row r="22" spans="2:29" ht="17">
-      <c r="B22" s="132" t="s">
+      <c r="B22" s="131" t="s">
         <v>77</v>
       </c>
-      <c r="C22" s="126">
+      <c r="C22" s="125">
         <v>1</v>
       </c>
       <c r="D22" s="69">
@@ -2916,11 +2910,11 @@
         <v>99</v>
       </c>
       <c r="F22" s="69" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="G22" s="76"/>
-      <c r="H22" s="119" t="s">
-        <v>159</v>
+      <c r="H22" s="118" t="s">
+        <v>156</v>
       </c>
       <c r="I22" s="108"/>
       <c r="J22" s="96"/>
@@ -2945,15 +2939,15 @@
       <c r="AC22" s="97"/>
     </row>
     <row r="23" spans="2:29" ht="17">
-      <c r="B23" s="130" t="s">
-        <v>145</v>
-      </c>
-      <c r="C23" s="128"/>
+      <c r="B23" s="129" t="s">
+        <v>144</v>
+      </c>
+      <c r="C23" s="127"/>
       <c r="D23" s="65"/>
       <c r="E23" s="59"/>
       <c r="F23" s="73"/>
       <c r="G23" s="64"/>
-      <c r="H23" s="118"/>
+      <c r="H23" s="117"/>
       <c r="I23" s="108"/>
       <c r="J23" s="96"/>
       <c r="K23" s="96"/>
@@ -2977,10 +2971,10 @@
       <c r="AC23" s="97"/>
     </row>
     <row r="24" spans="2:29" ht="17">
-      <c r="B24" s="131" t="s">
+      <c r="B24" s="130" t="s">
         <v>85</v>
       </c>
-      <c r="C24" s="127">
+      <c r="C24" s="126">
         <v>1</v>
       </c>
       <c r="D24" s="67">
@@ -2991,10 +2985,10 @@
         <v>1200</v>
       </c>
       <c r="F24" s="67"/>
-      <c r="G24" s="148" t="s">
-        <v>177</v>
-      </c>
-      <c r="H24" s="120" t="s">
+      <c r="G24" s="157" t="s">
+        <v>171</v>
+      </c>
+      <c r="H24" s="119" t="s">
         <v>92</v>
       </c>
       <c r="I24" s="108"/>
@@ -3020,10 +3014,10 @@
       <c r="AC24" s="97"/>
     </row>
     <row r="25" spans="2:29" ht="17">
-      <c r="B25" s="131" t="s">
-        <v>146</v>
-      </c>
-      <c r="C25" s="127">
+      <c r="B25" s="130" t="s">
+        <v>145</v>
+      </c>
+      <c r="C25" s="126">
         <v>1</v>
       </c>
       <c r="D25" s="67">
@@ -3034,11 +3028,11 @@
         <v>535.69000000000005</v>
       </c>
       <c r="F25" s="67" t="s">
+        <v>140</v>
+      </c>
+      <c r="G25" s="158"/>
+      <c r="H25" s="116" t="s">
         <v>141</v>
-      </c>
-      <c r="G25" s="149"/>
-      <c r="H25" s="116" t="s">
-        <v>142</v>
       </c>
       <c r="I25" s="108"/>
       <c r="J25" s="96"/>
@@ -3063,10 +3057,10 @@
       <c r="AC25" s="97"/>
     </row>
     <row r="26" spans="2:29" ht="17">
-      <c r="B26" s="131" t="s">
-        <v>147</v>
-      </c>
-      <c r="C26" s="127">
+      <c r="B26" s="130" t="s">
+        <v>146</v>
+      </c>
+      <c r="C26" s="126">
         <v>1</v>
       </c>
       <c r="D26" s="67">
@@ -3077,9 +3071,9 @@
         <v>553.44000000000005</v>
       </c>
       <c r="F26" s="67"/>
-      <c r="G26" s="149"/>
+      <c r="G26" s="158"/>
       <c r="H26" s="116" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="I26" s="108"/>
       <c r="J26" s="96"/>
@@ -3104,10 +3098,10 @@
       <c r="AC26" s="97"/>
     </row>
     <row r="27" spans="2:29" ht="17">
-      <c r="B27" s="131" t="s">
-        <v>148</v>
-      </c>
-      <c r="C27" s="127">
+      <c r="B27" s="130" t="s">
+        <v>147</v>
+      </c>
+      <c r="C27" s="126">
         <v>1</v>
       </c>
       <c r="D27" s="67">
@@ -3118,9 +3112,9 @@
         <v>442.53</v>
       </c>
       <c r="F27" s="67"/>
-      <c r="G27" s="149"/>
+      <c r="G27" s="158"/>
       <c r="H27" s="116" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="I27" s="108"/>
       <c r="J27" s="96"/>
@@ -3145,15 +3139,15 @@
       <c r="AC27" s="97"/>
     </row>
     <row r="28" spans="2:29" ht="17">
-      <c r="B28" s="130" t="s">
+      <c r="B28" s="129" t="s">
         <v>93</v>
       </c>
-      <c r="C28" s="128"/>
+      <c r="C28" s="127"/>
       <c r="D28" s="65"/>
       <c r="E28" s="59"/>
       <c r="F28" s="73"/>
       <c r="G28" s="64"/>
-      <c r="H28" s="118"/>
+      <c r="H28" s="117"/>
       <c r="I28" s="108"/>
       <c r="J28" s="96"/>
       <c r="K28" s="96"/>
@@ -3177,10 +3171,10 @@
       <c r="AC28" s="97"/>
     </row>
     <row r="29" spans="2:29" ht="17">
-      <c r="B29" s="132" t="s">
+      <c r="B29" s="131" t="s">
         <v>94</v>
       </c>
-      <c r="C29" s="126">
+      <c r="C29" s="125">
         <v>1</v>
       </c>
       <c r="D29" s="69">
@@ -3191,11 +3185,11 @@
         <v>110</v>
       </c>
       <c r="F29" s="69" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="G29" s="77"/>
       <c r="H29" s="112" t="s">
-        <v>160</v>
+        <v>157</v>
       </c>
       <c r="I29" s="109"/>
       <c r="J29" s="98"/>
@@ -3220,10 +3214,10 @@
       <c r="AC29" s="97"/>
     </row>
     <row r="30" spans="2:29" ht="34">
-      <c r="B30" s="131" t="s">
+      <c r="B30" s="130" t="s">
         <v>96</v>
       </c>
-      <c r="C30" s="127">
+      <c r="C30" s="126">
         <v>1</v>
       </c>
       <c r="D30" s="67">
@@ -3234,17 +3228,17 @@
         <v>219</v>
       </c>
       <c r="F30" s="67" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="G30" s="75"/>
       <c r="H30" s="113" t="s">
         <v>97</v>
       </c>
-      <c r="I30" s="152"/>
-      <c r="J30" s="152"/>
-      <c r="K30" s="152"/>
-      <c r="L30" s="152"/>
-      <c r="M30" s="153"/>
+      <c r="I30" s="161"/>
+      <c r="J30" s="161"/>
+      <c r="K30" s="161"/>
+      <c r="L30" s="161"/>
+      <c r="M30" s="162"/>
       <c r="N30" s="97"/>
       <c r="O30" s="97"/>
       <c r="P30" s="97"/>
@@ -3263,25 +3257,25 @@
       <c r="AC30" s="97"/>
     </row>
     <row r="31" spans="2:29" ht="17">
-      <c r="B31" s="132" t="s">
+      <c r="B31" s="131" t="s">
         <v>98</v>
       </c>
-      <c r="C31" s="126">
+      <c r="C31" s="125">
         <v>1</v>
       </c>
       <c r="D31" s="69">
-        <v>26.29</v>
+        <v>36.61</v>
       </c>
       <c r="E31" s="69">
         <f t="shared" si="1"/>
-        <v>26.29</v>
+        <v>36.61</v>
       </c>
       <c r="F31" s="69" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="G31" s="82"/>
       <c r="H31" s="112" t="s">
-        <v>161</v>
+        <v>174</v>
       </c>
       <c r="I31" s="108"/>
       <c r="J31" s="96"/>
@@ -3306,29 +3300,29 @@
       <c r="AC31" s="97"/>
     </row>
     <row r="32" spans="2:29" ht="34">
-      <c r="B32" s="131" t="s">
+      <c r="B32" s="130" t="s">
         <v>101</v>
       </c>
-      <c r="C32" s="127">
+      <c r="C32" s="126">
         <v>1</v>
       </c>
       <c r="D32" s="67">
-        <v>5.99</v>
+        <v>8.99</v>
       </c>
       <c r="E32" s="67">
         <f t="shared" si="1"/>
-        <v>5.99</v>
+        <v>8.99</v>
       </c>
       <c r="F32" s="67" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="G32" s="83"/>
       <c r="H32" s="113" t="s">
-        <v>162</v>
-      </c>
-      <c r="I32" s="154"/>
-      <c r="J32" s="147"/>
-      <c r="K32" s="147"/>
+        <v>175</v>
+      </c>
+      <c r="I32" s="163"/>
+      <c r="J32" s="156"/>
+      <c r="K32" s="156"/>
       <c r="L32" s="96"/>
       <c r="M32" s="96"/>
       <c r="N32" s="97"/>
@@ -3349,10 +3343,10 @@
       <c r="AC32" s="97"/>
     </row>
     <row r="33" spans="2:29" ht="17">
-      <c r="B33" s="132" t="s">
+      <c r="B33" s="131" t="s">
         <v>103</v>
       </c>
-      <c r="C33" s="126">
+      <c r="C33" s="125">
         <v>1</v>
       </c>
       <c r="D33" s="69">
@@ -3363,13 +3357,13 @@
         <v>9.99</v>
       </c>
       <c r="F33" s="69" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="G33" s="81" t="s">
         <v>104</v>
       </c>
       <c r="H33" s="112" t="s">
-        <v>163</v>
+        <v>158</v>
       </c>
       <c r="I33" s="110"/>
       <c r="J33" s="99"/>
@@ -3394,10 +3388,10 @@
       <c r="AC33" s="97"/>
     </row>
     <row r="34" spans="2:29" ht="17">
-      <c r="B34" s="131" t="s">
+      <c r="B34" s="130" t="s">
         <v>106</v>
       </c>
-      <c r="C34" s="127">
+      <c r="C34" s="126">
         <v>1</v>
       </c>
       <c r="D34" s="67">
@@ -3408,13 +3402,13 @@
         <v>8.99</v>
       </c>
       <c r="F34" s="67" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="G34" s="84" t="s">
         <v>104</v>
       </c>
       <c r="H34" s="113" t="s">
-        <v>164</v>
+        <v>159</v>
       </c>
       <c r="I34" s="110"/>
       <c r="J34" s="99"/>
@@ -3439,25 +3433,25 @@
       <c r="AC34" s="97"/>
     </row>
     <row r="35" spans="2:29" ht="17">
-      <c r="B35" s="166" t="s">
+      <c r="B35" s="151" t="s">
         <v>108</v>
       </c>
-      <c r="C35" s="126">
+      <c r="C35" s="125">
         <v>1</v>
       </c>
       <c r="D35" s="69">
-        <v>20</v>
+        <v>13</v>
       </c>
       <c r="E35" s="69">
         <f t="shared" si="1"/>
-        <v>20</v>
+        <v>13</v>
       </c>
       <c r="F35" s="69"/>
-      <c r="G35" s="168" t="s">
-        <v>175</v>
+      <c r="G35" s="153" t="s">
+        <v>169</v>
       </c>
       <c r="H35" s="112" t="s">
-        <v>165</v>
+        <v>176</v>
       </c>
       <c r="I35" s="110"/>
       <c r="J35" s="99"/>
@@ -3482,8 +3476,8 @@
       <c r="AC35" s="97"/>
     </row>
     <row r="36" spans="2:29" ht="17">
-      <c r="B36" s="167"/>
-      <c r="C36" s="126">
+      <c r="B36" s="152"/>
+      <c r="C36" s="125">
         <v>1</v>
       </c>
       <c r="D36" s="69">
@@ -3494,11 +3488,11 @@
         <v>15.65</v>
       </c>
       <c r="F36" s="69" t="s">
-        <v>141</v>
-      </c>
-      <c r="G36" s="169"/>
+        <v>140</v>
+      </c>
+      <c r="G36" s="154"/>
       <c r="H36" s="112" t="s">
-        <v>166</v>
+        <v>160</v>
       </c>
       <c r="I36" s="110"/>
       <c r="J36" s="99"/>
@@ -3523,10 +3517,10 @@
       <c r="AC36" s="97"/>
     </row>
     <row r="37" spans="2:29" ht="17">
-      <c r="B37" s="131" t="s">
+      <c r="B37" s="130" t="s">
         <v>110</v>
       </c>
-      <c r="C37" s="127">
+      <c r="C37" s="126">
         <v>1</v>
       </c>
       <c r="D37" s="67">
@@ -3537,11 +3531,11 @@
         <v>405</v>
       </c>
       <c r="F37" s="67" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="G37" s="75"/>
       <c r="H37" s="113" t="s">
-        <v>167</v>
+        <v>161</v>
       </c>
       <c r="I37" s="108"/>
       <c r="J37" s="96"/>
@@ -3566,15 +3560,15 @@
       <c r="AC37" s="97"/>
     </row>
     <row r="38" spans="2:29" ht="17">
-      <c r="B38" s="130" t="s">
+      <c r="B38" s="129" t="s">
         <v>112</v>
       </c>
-      <c r="C38" s="128"/>
+      <c r="C38" s="127"/>
       <c r="D38" s="65"/>
       <c r="E38" s="59"/>
       <c r="F38" s="73"/>
       <c r="G38" s="64"/>
-      <c r="H38" s="118"/>
+      <c r="H38" s="117"/>
       <c r="I38" s="108"/>
       <c r="J38" s="96"/>
       <c r="K38" s="96"/>
@@ -3598,10 +3592,10 @@
       <c r="AC38" s="97"/>
     </row>
     <row r="39" spans="2:29" ht="17">
-      <c r="B39" s="132" t="s">
+      <c r="B39" s="131" t="s">
         <v>113</v>
       </c>
-      <c r="C39" s="126">
+      <c r="C39" s="125">
         <v>1</v>
       </c>
       <c r="D39" s="69">
@@ -3612,13 +3606,13 @@
         <v>17.43</v>
       </c>
       <c r="F39" s="69" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="G39" s="68" t="s">
         <v>114</v>
       </c>
       <c r="H39" s="112" t="s">
-        <v>168</v>
+        <v>162</v>
       </c>
       <c r="I39" s="108"/>
       <c r="J39" s="96"/>
@@ -3643,10 +3637,10 @@
       <c r="AC39" s="97"/>
     </row>
     <row r="40" spans="2:29" ht="17">
-      <c r="B40" s="131" t="s">
+      <c r="B40" s="130" t="s">
         <v>116</v>
       </c>
-      <c r="C40" s="127">
+      <c r="C40" s="126">
         <v>1</v>
       </c>
       <c r="D40" s="67">
@@ -3657,10 +3651,10 @@
         <v>3.38</v>
       </c>
       <c r="F40" s="67" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="G40" s="85"/>
-      <c r="H40" s="120" t="s">
+      <c r="H40" s="119" t="s">
         <v>118</v>
       </c>
       <c r="I40" s="108"/>
@@ -3686,10 +3680,10 @@
       <c r="AC40" s="97"/>
     </row>
     <row r="41" spans="2:29" ht="17">
-      <c r="B41" s="132" t="s">
+      <c r="B41" s="131" t="s">
         <v>119</v>
       </c>
-      <c r="C41" s="126">
+      <c r="C41" s="125">
         <v>1</v>
       </c>
       <c r="D41" s="69">
@@ -3700,15 +3694,15 @@
         <v>10.39</v>
       </c>
       <c r="F41" s="69" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="G41" s="77"/>
       <c r="H41" s="112" t="s">
-        <v>169</v>
-      </c>
-      <c r="I41" s="154"/>
-      <c r="J41" s="147"/>
-      <c r="K41" s="147"/>
+        <v>163</v>
+      </c>
+      <c r="I41" s="163"/>
+      <c r="J41" s="156"/>
+      <c r="K41" s="156"/>
       <c r="L41" s="96"/>
       <c r="M41" s="96"/>
       <c r="N41" s="97"/>
@@ -3729,10 +3723,10 @@
       <c r="AC41" s="97"/>
     </row>
     <row r="42" spans="2:29" ht="17">
-      <c r="B42" s="131" t="s">
+      <c r="B42" s="130" t="s">
         <v>121</v>
       </c>
-      <c r="C42" s="127">
+      <c r="C42" s="126">
         <v>1</v>
       </c>
       <c r="D42" s="67">
@@ -3743,17 +3737,17 @@
         <v>7.59</v>
       </c>
       <c r="F42" s="67" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="G42" s="66"/>
       <c r="H42" s="113" t="s">
-        <v>170</v>
-      </c>
-      <c r="I42" s="154"/>
-      <c r="J42" s="147"/>
-      <c r="K42" s="147"/>
-      <c r="L42" s="147"/>
-      <c r="M42" s="147"/>
+        <v>164</v>
+      </c>
+      <c r="I42" s="163"/>
+      <c r="J42" s="156"/>
+      <c r="K42" s="156"/>
+      <c r="L42" s="156"/>
+      <c r="M42" s="156"/>
       <c r="N42" s="97"/>
       <c r="O42" s="97"/>
       <c r="P42" s="97"/>
@@ -3772,10 +3766,10 @@
       <c r="AC42" s="97"/>
     </row>
     <row r="43" spans="2:29" ht="17">
-      <c r="B43" s="132" t="s">
+      <c r="B43" s="131" t="s">
         <v>124</v>
       </c>
-      <c r="C43" s="126">
+      <c r="C43" s="125">
         <v>1</v>
       </c>
       <c r="D43" s="69">
@@ -3786,14 +3780,14 @@
         <v>13.99</v>
       </c>
       <c r="F43" s="69" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="G43" s="77"/>
       <c r="H43" s="112" t="s">
-        <v>171</v>
-      </c>
-      <c r="I43" s="146"/>
-      <c r="J43" s="147"/>
+        <v>165</v>
+      </c>
+      <c r="I43" s="155"/>
+      <c r="J43" s="156"/>
       <c r="K43" s="96"/>
       <c r="L43" s="96"/>
       <c r="M43" s="96"/>
@@ -3815,20 +3809,20 @@
       <c r="AC43" s="97"/>
     </row>
     <row r="44" spans="2:29" ht="18" thickBot="1">
-      <c r="B44" s="133"/>
-      <c r="C44" s="129" t="s">
+      <c r="B44" s="132"/>
+      <c r="C44" s="128" t="s">
         <v>127</v>
       </c>
-      <c r="D44" s="121"/>
-      <c r="E44" s="121" t="e">
+      <c r="D44" s="120"/>
+      <c r="E44" s="120">
         <f>SUMIF(F4:F43, "x", E4:E43)</f>
-        <v>#VALUE!</v>
-      </c>
-      <c r="F44" s="122"/>
-      <c r="G44" s="123" t="s">
+        <v>2544.7599999999993</v>
+      </c>
+      <c r="F44" s="121"/>
+      <c r="G44" s="122" t="s">
         <v>128</v>
       </c>
-      <c r="H44" s="124"/>
+      <c r="H44" s="123"/>
       <c r="I44" s="106"/>
       <c r="J44" s="60"/>
       <c r="K44" s="60"/>
@@ -3852,8 +3846,8 @@
       <c r="N45" s="61"/>
     </row>
     <row r="46" spans="2:29" ht="17">
-      <c r="B46" s="145" t="s">
-        <v>179</v>
+      <c r="B46" s="144" t="s">
+        <v>173</v>
       </c>
       <c r="C46" s="62"/>
       <c r="D46" s="63"/>
@@ -6334,11 +6328,6 @@
     </row>
   </sheetData>
   <mergeCells count="17">
-    <mergeCell ref="B4:B6"/>
-    <mergeCell ref="G4:G6"/>
-    <mergeCell ref="F14:F15"/>
-    <mergeCell ref="B35:B36"/>
-    <mergeCell ref="G35:G36"/>
     <mergeCell ref="I43:J43"/>
     <mergeCell ref="G24:G27"/>
     <mergeCell ref="C14:C15"/>
@@ -6351,6 +6340,11 @@
     <mergeCell ref="H14:H15"/>
     <mergeCell ref="E14:E15"/>
     <mergeCell ref="D14:D15"/>
+    <mergeCell ref="B4:B6"/>
+    <mergeCell ref="G4:G6"/>
+    <mergeCell ref="F14:F15"/>
+    <mergeCell ref="B35:B36"/>
+    <mergeCell ref="G35:G36"/>
   </mergeCells>
   <hyperlinks>
     <hyperlink ref="H20" r:id="rId1" xr:uid="{4F589D68-222B-4A43-B023-CE0E141D78F2}"/>
@@ -6363,22 +6357,28 @@
     <hyperlink ref="H8" r:id="rId8" xr:uid="{689DF752-7941-4144-8E85-2BC5EDE4EE9F}"/>
     <hyperlink ref="H7" r:id="rId9" xr:uid="{2934E811-74B4-4046-9874-E7173E570E08}"/>
     <hyperlink ref="H14:H15" r:id="rId10" display="https://amzn.eu/d/0934urF9" xr:uid="{8676A0BC-3CA7-5A4D-9375-C4DB3329C5CF}"/>
-    <hyperlink ref="H31" r:id="rId11" xr:uid="{F5D99B89-6CAA-7744-9475-E3D723F36977}"/>
-    <hyperlink ref="H32" r:id="rId12" xr:uid="{64C2AE3C-53EB-F447-A72F-B8254E0A6943}"/>
-    <hyperlink ref="H33" r:id="rId13" xr:uid="{D3DDAC29-B62D-8B48-AB0E-61B1D189861F}"/>
-    <hyperlink ref="H34" r:id="rId14" xr:uid="{2DE65291-3594-8C40-814C-4D30492506AA}"/>
-    <hyperlink ref="H36" r:id="rId15" xr:uid="{E066F5DA-2521-654D-A23E-5C0473B1DEBF}"/>
-    <hyperlink ref="H37" r:id="rId16" xr:uid="{58EBA077-E5F2-994C-8461-2CB641F3F2DD}"/>
-    <hyperlink ref="H39" r:id="rId17" xr:uid="{F414D4C9-B9F1-AB42-A1EA-7F72CE2987F0}"/>
-    <hyperlink ref="H40" r:id="rId18" xr:uid="{408FDA23-B771-5D46-B410-D154953720BF}"/>
-    <hyperlink ref="H41" r:id="rId19" xr:uid="{9F446349-F706-4F48-A3F0-4AE8C344ED77}"/>
-    <hyperlink ref="H42" r:id="rId20" xr:uid="{931E712D-264A-254F-ACE0-A9FEC29370E1}"/>
-    <hyperlink ref="H43" r:id="rId21" xr:uid="{0B1E7D38-FD1B-B84C-973D-74B46D3BD0BE}"/>
-    <hyperlink ref="H30" r:id="rId22" xr:uid="{5E2B787A-0D4D-C045-BC84-CEEBEC939FCE}"/>
-    <hyperlink ref="H29" r:id="rId23" xr:uid="{F77BF5C0-0154-FC41-9146-71EC5D057BEC}"/>
-    <hyperlink ref="H4" r:id="rId24" xr:uid="{62579853-ACC6-3F45-AB43-AB666B0CE4A5}"/>
-    <hyperlink ref="H5" r:id="rId25" xr:uid="{76B7116F-5CED-BE43-923A-75F6BB4F5B73}"/>
-    <hyperlink ref="H6" r:id="rId26" xr:uid="{270E0A71-47D3-A04D-8714-FBF827AA7557}"/>
+    <hyperlink ref="H33" r:id="rId11" xr:uid="{D3DDAC29-B62D-8B48-AB0E-61B1D189861F}"/>
+    <hyperlink ref="H34" r:id="rId12" xr:uid="{2DE65291-3594-8C40-814C-4D30492506AA}"/>
+    <hyperlink ref="H36" r:id="rId13" xr:uid="{E066F5DA-2521-654D-A23E-5C0473B1DEBF}"/>
+    <hyperlink ref="H37" r:id="rId14" xr:uid="{58EBA077-E5F2-994C-8461-2CB641F3F2DD}"/>
+    <hyperlink ref="H39" r:id="rId15" xr:uid="{F414D4C9-B9F1-AB42-A1EA-7F72CE2987F0}"/>
+    <hyperlink ref="H40" r:id="rId16" xr:uid="{408FDA23-B771-5D46-B410-D154953720BF}"/>
+    <hyperlink ref="H41" r:id="rId17" xr:uid="{9F446349-F706-4F48-A3F0-4AE8C344ED77}"/>
+    <hyperlink ref="H42" r:id="rId18" xr:uid="{931E712D-264A-254F-ACE0-A9FEC29370E1}"/>
+    <hyperlink ref="H43" r:id="rId19" xr:uid="{0B1E7D38-FD1B-B84C-973D-74B46D3BD0BE}"/>
+    <hyperlink ref="H30" r:id="rId20" xr:uid="{5E2B787A-0D4D-C045-BC84-CEEBEC939FCE}"/>
+    <hyperlink ref="H29" r:id="rId21" xr:uid="{F77BF5C0-0154-FC41-9146-71EC5D057BEC}"/>
+    <hyperlink ref="H4" r:id="rId22" xr:uid="{62579853-ACC6-3F45-AB43-AB666B0CE4A5}"/>
+    <hyperlink ref="H5" r:id="rId23" xr:uid="{76B7116F-5CED-BE43-923A-75F6BB4F5B73}"/>
+    <hyperlink ref="H6" r:id="rId24" xr:uid="{270E0A71-47D3-A04D-8714-FBF827AA7557}"/>
+    <hyperlink ref="H16" r:id="rId25" xr:uid="{971DF0EC-EE8D-0C47-81D5-EF37815C0D19}"/>
+    <hyperlink ref="H17" r:id="rId26" xr:uid="{9BCE5E90-2283-1346-9910-C49BA27E9B1E}"/>
+    <hyperlink ref="H18" r:id="rId27" xr:uid="{53E460B5-A4B1-8246-ACC0-E0B4F59AB955}"/>
+    <hyperlink ref="H31" r:id="rId28" xr:uid="{C4091FB8-58CC-8C4E-A974-5E3E367873CA}"/>
+    <hyperlink ref="H32" r:id="rId29" xr:uid="{5E006F4D-3F8F-624E-8244-07949F264730}"/>
+    <hyperlink ref="H35" r:id="rId30" xr:uid="{D6C5B699-3F20-B44E-BECC-D137DF3D9A84}"/>
+    <hyperlink ref="H12" r:id="rId31" xr:uid="{518C1E8F-4B66-D443-900D-95BD554E0194}"/>
+    <hyperlink ref="H13" r:id="rId32" xr:uid="{0EC365AA-565B-7140-9816-E9EA47F836DA}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -6960,14 +6960,14 @@
         <v>249.75</v>
       </c>
       <c r="D23" s="29"/>
-      <c r="E23" s="170" t="s">
+      <c r="E23" s="169" t="s">
         <v>97</v>
       </c>
-      <c r="F23" s="171"/>
-      <c r="G23" s="171"/>
-      <c r="H23" s="171"/>
-      <c r="I23" s="171"/>
-      <c r="J23" s="171"/>
+      <c r="F23" s="170"/>
+      <c r="G23" s="170"/>
+      <c r="H23" s="170"/>
+      <c r="I23" s="170"/>
+      <c r="J23" s="170"/>
       <c r="K23" s="29"/>
       <c r="L23" s="29"/>
       <c r="M23" s="29"/>
@@ -7034,12 +7034,12 @@
         <v>6.99</v>
       </c>
       <c r="D25" s="44"/>
-      <c r="E25" s="172" t="s">
+      <c r="E25" s="171" t="s">
         <v>102</v>
       </c>
-      <c r="F25" s="171"/>
-      <c r="G25" s="171"/>
-      <c r="H25" s="171"/>
+      <c r="F25" s="170"/>
+      <c r="G25" s="170"/>
+      <c r="H25" s="170"/>
       <c r="I25" s="29"/>
       <c r="J25" s="29"/>
       <c r="K25" s="29"/>
@@ -7324,12 +7324,12 @@
         <v>6.99</v>
       </c>
       <c r="D33" s="27"/>
-      <c r="E33" s="173" t="s">
+      <c r="E33" s="172" t="s">
         <v>120</v>
       </c>
-      <c r="F33" s="171"/>
-      <c r="G33" s="171"/>
-      <c r="H33" s="171"/>
+      <c r="F33" s="170"/>
+      <c r="G33" s="170"/>
+      <c r="H33" s="170"/>
       <c r="I33" s="29"/>
       <c r="J33" s="29"/>
       <c r="K33" s="29"/>
@@ -7362,14 +7362,14 @@
       <c r="D34" s="7" t="s">
         <v>122</v>
       </c>
-      <c r="E34" s="173" t="s">
+      <c r="E34" s="172" t="s">
         <v>123</v>
       </c>
-      <c r="F34" s="171"/>
-      <c r="G34" s="171"/>
-      <c r="H34" s="171"/>
-      <c r="I34" s="171"/>
-      <c r="J34" s="171"/>
+      <c r="F34" s="170"/>
+      <c r="G34" s="170"/>
+      <c r="H34" s="170"/>
+      <c r="I34" s="170"/>
+      <c r="J34" s="170"/>
       <c r="K34" s="29"/>
       <c r="L34" s="29"/>
       <c r="M34" s="29"/>
@@ -7401,10 +7401,10 @@
       <c r="E35" s="51" t="s">
         <v>125</v>
       </c>
-      <c r="F35" s="174" t="s">
+      <c r="F35" s="173" t="s">
         <v>126</v>
       </c>
-      <c r="G35" s="171"/>
+      <c r="G35" s="170"/>
       <c r="H35" s="29"/>
       <c r="I35" s="29"/>
       <c r="J35" s="29"/>
@@ -10700,14 +10700,14 @@
         <v>0</v>
       </c>
       <c r="C6" s="7"/>
-      <c r="D6" s="175" t="s">
+      <c r="D6" s="174" t="s">
         <v>17</v>
       </c>
-      <c r="E6" s="171"/>
-      <c r="F6" s="171"/>
-      <c r="G6" s="171"/>
-      <c r="H6" s="171"/>
-      <c r="I6" s="171"/>
+      <c r="E6" s="170"/>
+      <c r="F6" s="170"/>
+      <c r="G6" s="170"/>
+      <c r="H6" s="170"/>
+      <c r="I6" s="170"/>
       <c r="J6" s="7"/>
     </row>
     <row r="7" spans="1:10" ht="15.75" customHeight="1">
@@ -10935,15 +10935,15 @@
         <v>1</v>
       </c>
       <c r="C20" s="7"/>
-      <c r="D20" s="175" t="s">
+      <c r="D20" s="174" t="s">
         <v>84</v>
       </c>
-      <c r="E20" s="171"/>
-      <c r="F20" s="171"/>
-      <c r="G20" s="171"/>
-      <c r="H20" s="171"/>
-      <c r="I20" s="171"/>
-      <c r="J20" s="171"/>
+      <c r="E20" s="170"/>
+      <c r="F20" s="170"/>
+      <c r="G20" s="170"/>
+      <c r="H20" s="170"/>
+      <c r="I20" s="170"/>
+      <c r="J20" s="170"/>
     </row>
     <row r="21" spans="1:24" ht="15.75" customHeight="1">
       <c r="A21" s="7" t="s">
@@ -10953,15 +10953,15 @@
         <v>1</v>
       </c>
       <c r="C21" s="7"/>
-      <c r="D21" s="175" t="s">
+      <c r="D21" s="174" t="s">
         <v>88</v>
       </c>
-      <c r="E21" s="171"/>
-      <c r="F21" s="171"/>
-      <c r="G21" s="171"/>
-      <c r="H21" s="171"/>
-      <c r="I21" s="171"/>
-      <c r="J21" s="171"/>
+      <c r="E21" s="170"/>
+      <c r="F21" s="170"/>
+      <c r="G21" s="170"/>
+      <c r="H21" s="170"/>
+      <c r="I21" s="170"/>
+      <c r="J21" s="170"/>
     </row>
     <row r="22" spans="1:24" ht="15.75" customHeight="1">
       <c r="A22" s="35" t="s">

--- a/hardware/bom/master_bom.xlsx
+++ b/hardware/bom/master_bom.xlsx
@@ -10,7 +10,7 @@
   </mc:AlternateContent>
   <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{01780B49-EB64-6C40-A11A-738064B3CA79}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="100" yWindow="660" windowWidth="17300" windowHeight="19820" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="4360" yWindow="660" windowWidth="30200" windowHeight="19820" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="(POLIMI) Rally + Orin Nano v1" sheetId="9" r:id="rId1"/>

--- a/hardware/bom/master_bom.xlsx
+++ b/hardware/bom/master_bom.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Volumes/POLI/Magistrale/21_ACAV/f1tenth_PoliMI/hardware/bom/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{98E0C908-63C8-204A-937A-168C16A36B32}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{30EC810C-286C-9448-9F34-03F794087BD7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="4360" yWindow="660" windowWidth="30200" windowHeight="19820" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="660" windowWidth="34560" windowHeight="21680" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="(POLIMI) Rally + Orin Nano v1" sheetId="9" r:id="rId1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="279" uniqueCount="191">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="278" uniqueCount="192">
   <si>
     <t>Scroll right to see links</t>
   </si>
@@ -891,6 +891,9 @@
   <si>
     <t>PoliMi BOM</t>
   </si>
+  <si>
+    <t>Intel RealSense D435i</t>
+  </si>
 </sst>
 </file>
 
@@ -900,7 +903,7 @@
     <numFmt numFmtId="44" formatCode="_(&quot;$&quot;* #,##0.00_);_(&quot;$&quot;* \(#,##0.00\);_(&quot;$&quot;* &quot;-&quot;??_);_(@_)"/>
     <numFmt numFmtId="164" formatCode="_([$€-2]\ * #,##0.00_);_([$€-2]\ * \(#,##0.00\);_([$€-2]\ * &quot;-&quot;??_);_(@_)"/>
   </numFmts>
-  <fonts count="61">
+  <fonts count="64">
     <font>
       <sz val="10"/>
       <color rgb="FF000000"/>
@@ -1313,6 +1316,29 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <strike/>
+      <sz val="12"/>
+      <color rgb="FFFF0000"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <strike/>
+      <sz val="10"/>
+      <color rgb="FFFF0000"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <strike/>
+      <u/>
+      <sz val="12"/>
+      <color rgb="FFFF0000"/>
+      <name val="Arial"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
   <fills count="11">
     <fill>
@@ -1718,7 +1744,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="33" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="188">
+  <cellXfs count="193">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -1937,63 +1963,6 @@
     <xf numFmtId="0" fontId="4" fillId="6" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="6" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="6" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="40" fillId="6" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="40" fillId="6" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="4" fillId="5" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="4" fillId="5" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="6" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="6" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="38" fillId="6" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="38" fillId="6" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="38" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="38" fillId="5" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="5" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="5" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="38" fillId="5" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="5" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="34" fillId="5" borderId="8" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="34" fillId="5" borderId="9" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="4" fillId="6" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -2010,9 +1979,6 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="10" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="46" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="46" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -2088,188 +2054,265 @@
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="59" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="44" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="44" fontId="3" fillId="0" borderId="23" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="44" fontId="3" fillId="3" borderId="23" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="44" fontId="4" fillId="0" borderId="23" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="44" fontId="3" fillId="3" borderId="23" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="44" fontId="3" fillId="3" borderId="23" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="2" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="44" fontId="3" fillId="3" borderId="23" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="2" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="44" fontId="4" fillId="4" borderId="23" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="59" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="59" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="38" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="38" fillId="5" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="38" fillId="5" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="34" fillId="5" borderId="8" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="34" fillId="5" borderId="9" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="4" fillId="5" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="4" fillId="5" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="6" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="6" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="40" fillId="6" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="40" fillId="6" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="6" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="6" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="38" fillId="6" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="38" fillId="6" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="10" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="59" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="60" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="59" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="59" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="44" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="59" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="61" fillId="6" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="61" fillId="6" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="44" fontId="3" fillId="0" borderId="23" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="44" fontId="3" fillId="3" borderId="23" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="44" fontId="4" fillId="0" borderId="23" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="44" fontId="3" fillId="3" borderId="23" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="44" fontId="3" fillId="3" borderId="23" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="2" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="44" fontId="3" fillId="3" borderId="23" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="2" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="44" fontId="4" fillId="4" borderId="23" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
+    <xf numFmtId="164" fontId="61" fillId="6" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="61" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="62" fillId="6" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="63" fillId="6" borderId="8" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -2504,17 +2547,17 @@
     <col min="9" max="16384" width="12.6640625" style="21"/>
   </cols>
   <sheetData>
-    <row r="2" spans="1:8" s="105" customFormat="1" ht="47" customHeight="1" thickBot="1">
-      <c r="A2" s="127"/>
-      <c r="B2" s="146" t="s">
+    <row r="2" spans="1:8" s="85" customFormat="1" ht="47" customHeight="1" thickBot="1">
+      <c r="A2" s="106"/>
+      <c r="B2" s="163" t="s">
         <v>190</v>
       </c>
-      <c r="C2" s="146"/>
-      <c r="D2" s="146"/>
-      <c r="E2" s="146"/>
-      <c r="F2" s="146"/>
-      <c r="G2" s="146"/>
-      <c r="H2" s="146"/>
+      <c r="C2" s="163"/>
+      <c r="D2" s="163"/>
+      <c r="E2" s="163"/>
+      <c r="F2" s="163"/>
+      <c r="G2" s="163"/>
+      <c r="H2" s="163"/>
     </row>
     <row r="3" spans="1:8" s="33" customFormat="1" ht="23" thickBot="1">
       <c r="B3" s="67" t="s">
@@ -2551,7 +2594,7 @@
       <c r="H4" s="66"/>
     </row>
     <row r="5" spans="1:8" ht="17">
-      <c r="B5" s="74" t="s">
+      <c r="B5" s="175" t="s">
         <v>144</v>
       </c>
       <c r="C5" s="53">
@@ -2565,7 +2608,7 @@
         <v>479.9</v>
       </c>
       <c r="F5" s="16"/>
-      <c r="G5" s="76" t="s">
+      <c r="G5" s="177" t="s">
         <v>166</v>
       </c>
       <c r="H5" s="40" t="s">
@@ -2573,7 +2616,7 @@
       </c>
     </row>
     <row r="6" spans="1:8" ht="17">
-      <c r="B6" s="75"/>
+      <c r="B6" s="176"/>
       <c r="C6" s="53">
         <v>1</v>
       </c>
@@ -2587,13 +2630,13 @@
       <c r="F6" s="16" t="s">
         <v>136</v>
       </c>
-      <c r="G6" s="77"/>
+      <c r="G6" s="178"/>
       <c r="H6" s="40" t="s">
         <v>163</v>
       </c>
     </row>
     <row r="7" spans="1:8" ht="17">
-      <c r="B7" s="75"/>
+      <c r="B7" s="176"/>
       <c r="C7" s="53">
         <v>1</v>
       </c>
@@ -2605,7 +2648,7 @@
         <v>425</v>
       </c>
       <c r="F7" s="16"/>
-      <c r="G7" s="77"/>
+      <c r="G7" s="178"/>
       <c r="H7" s="40" t="s">
         <v>164</v>
       </c>
@@ -2765,23 +2808,23 @@
       <c r="B15" s="58" t="s">
         <v>51</v>
       </c>
-      <c r="C15" s="86">
+      <c r="C15" s="166">
         <v>1</v>
       </c>
-      <c r="D15" s="78">
+      <c r="D15" s="173">
         <v>12</v>
       </c>
-      <c r="E15" s="78">
+      <c r="E15" s="173">
         <f>C15*D15</f>
         <v>12</v>
       </c>
-      <c r="F15" s="78" t="s">
+      <c r="F15" s="173" t="s">
         <v>136</v>
       </c>
-      <c r="G15" s="89" t="s">
+      <c r="G15" s="169" t="s">
         <v>131</v>
       </c>
-      <c r="H15" s="91" t="s">
+      <c r="H15" s="171" t="s">
         <v>147</v>
       </c>
     </row>
@@ -2789,12 +2832,12 @@
       <c r="B16" s="58" t="s">
         <v>55</v>
       </c>
-      <c r="C16" s="87"/>
-      <c r="D16" s="79"/>
-      <c r="E16" s="79"/>
-      <c r="F16" s="79"/>
-      <c r="G16" s="90"/>
-      <c r="H16" s="92"/>
+      <c r="C16" s="167"/>
+      <c r="D16" s="174"/>
+      <c r="E16" s="174"/>
+      <c r="F16" s="174"/>
+      <c r="G16" s="170"/>
+      <c r="H16" s="172"/>
     </row>
     <row r="17" spans="2:17" ht="17">
       <c r="B17" s="59" t="s">
@@ -2904,7 +2947,7 @@
       <c r="F21" s="14" t="s">
         <v>136</v>
       </c>
-      <c r="G21" s="84" t="s">
+      <c r="G21" s="164" t="s">
         <v>129</v>
       </c>
       <c r="H21" s="44" t="s">
@@ -2932,7 +2975,7 @@
         <v>529</v>
       </c>
       <c r="F22" s="14"/>
-      <c r="G22" s="88"/>
+      <c r="G22" s="168"/>
       <c r="H22" s="44" t="s">
         <v>151</v>
       </c>
@@ -3011,7 +3054,7 @@
         <v>1200</v>
       </c>
       <c r="F25" s="14"/>
-      <c r="G25" s="84" t="s">
+      <c r="G25" s="164" t="s">
         <v>167</v>
       </c>
       <c r="H25" s="47" t="s">
@@ -3044,7 +3087,7 @@
       <c r="F26" s="14" t="s">
         <v>136</v>
       </c>
-      <c r="G26" s="85"/>
+      <c r="G26" s="165"/>
       <c r="H26" s="44" t="s">
         <v>137</v>
       </c>
@@ -3073,7 +3116,7 @@
         <v>553.44000000000005</v>
       </c>
       <c r="F27" s="14"/>
-      <c r="G27" s="85"/>
+      <c r="G27" s="165"/>
       <c r="H27" s="44" t="s">
         <v>138</v>
       </c>
@@ -3102,7 +3145,7 @@
         <v>442.53</v>
       </c>
       <c r="F28" s="14"/>
-      <c r="G28" s="85"/>
+      <c r="G28" s="165"/>
       <c r="H28" s="44" t="s">
         <v>139</v>
       </c>
@@ -3327,7 +3370,7 @@
       <c r="Q35" s="34"/>
     </row>
     <row r="36" spans="2:17" ht="17">
-      <c r="B36" s="80" t="s">
+      <c r="B36" s="179" t="s">
         <v>105</v>
       </c>
       <c r="C36" s="53">
@@ -3341,7 +3384,7 @@
         <v>13</v>
       </c>
       <c r="F36" s="16"/>
-      <c r="G36" s="82" t="s">
+      <c r="G36" s="181" t="s">
         <v>165</v>
       </c>
       <c r="H36" s="40" t="s">
@@ -3358,7 +3401,7 @@
       <c r="Q36" s="34"/>
     </row>
     <row r="37" spans="2:17" ht="17">
-      <c r="B37" s="81"/>
+      <c r="B37" s="180"/>
       <c r="C37" s="53">
         <v>1</v>
       </c>
@@ -3372,7 +3415,7 @@
       <c r="F37" s="16" t="s">
         <v>136</v>
       </c>
-      <c r="G37" s="83"/>
+      <c r="G37" s="182"/>
       <c r="H37" s="40" t="s">
         <v>156</v>
       </c>
@@ -3388,7 +3431,7 @@
     </row>
     <row r="38" spans="2:17" ht="17">
       <c r="B38" s="58" t="s">
-        <v>107</v>
+        <v>191</v>
       </c>
       <c r="C38" s="54">
         <v>1</v>
@@ -3618,21 +3661,21 @@
       <c r="B46" s="73" t="s">
         <v>178</v>
       </c>
-      <c r="C46" s="93">
+      <c r="C46" s="74">
         <v>1</v>
       </c>
-      <c r="D46" s="94">
+      <c r="D46" s="75">
         <v>8.99</v>
       </c>
       <c r="E46" s="16">
         <f t="shared" si="1"/>
         <v>8.99</v>
       </c>
-      <c r="F46" s="94" t="s">
+      <c r="F46" s="75" t="s">
         <v>136</v>
       </c>
-      <c r="G46" s="95"/>
-      <c r="H46" s="96" t="s">
+      <c r="G46" s="76"/>
+      <c r="H46" s="77" t="s">
         <v>176</v>
       </c>
       <c r="I46" s="34"/>
@@ -3649,21 +3692,21 @@
       <c r="B47" s="73" t="s">
         <v>179</v>
       </c>
-      <c r="C47" s="93">
+      <c r="C47" s="74">
         <v>1</v>
       </c>
-      <c r="D47" s="94">
+      <c r="D47" s="75">
         <v>10.99</v>
       </c>
       <c r="E47" s="16">
         <f t="shared" si="1"/>
         <v>10.99</v>
       </c>
-      <c r="F47" s="94" t="s">
+      <c r="F47" s="75" t="s">
         <v>136</v>
       </c>
-      <c r="G47" s="95"/>
-      <c r="H47" s="96" t="s">
+      <c r="G47" s="76"/>
+      <c r="H47" s="77" t="s">
         <v>180</v>
       </c>
       <c r="I47" s="34"/>
@@ -3677,27 +3720,25 @@
       <c r="Q47" s="34"/>
     </row>
     <row r="48" spans="2:17" ht="34">
-      <c r="B48" s="73" t="s">
+      <c r="B48" s="187" t="s">
         <v>181</v>
       </c>
-      <c r="C48" s="93">
+      <c r="C48" s="188">
         <v>10</v>
       </c>
-      <c r="D48" s="94">
+      <c r="D48" s="189">
         <v>51.9</v>
       </c>
-      <c r="E48" s="16">
+      <c r="E48" s="190">
         <f t="shared" si="1"/>
         <v>519</v>
       </c>
-      <c r="F48" s="94" t="s">
-        <v>136</v>
-      </c>
-      <c r="G48" s="95" t="str">
+      <c r="F48" s="189"/>
+      <c r="G48" s="191" t="str">
         <f>_xlfn.CONCAT("TRACK LENGTH = ", PRODUCT(C48, 9.8, 0.5), " meters")</f>
         <v>TRACK LENGTH = 49 meters</v>
       </c>
-      <c r="H48" s="96" t="s">
+      <c r="H48" s="192" t="s">
         <v>182</v>
       </c>
       <c r="I48" s="34"/>
@@ -3718,7 +3759,7 @@
       <c r="D49" s="48"/>
       <c r="E49" s="48">
         <f>SUMIF(F5:F48, "x", E5:E48)</f>
-        <v>3083.7399999999989</v>
+        <v>2564.7399999999989</v>
       </c>
       <c r="F49" s="49"/>
       <c r="G49" s="50" t="s">
@@ -5156,6 +5197,8 @@
     </row>
   </sheetData>
   <mergeCells count="13">
+    <mergeCell ref="B36:B37"/>
+    <mergeCell ref="G36:G37"/>
     <mergeCell ref="B2:H2"/>
     <mergeCell ref="G25:G28"/>
     <mergeCell ref="C15:C16"/>
@@ -5167,8 +5210,6 @@
     <mergeCell ref="B5:B7"/>
     <mergeCell ref="G5:G7"/>
     <mergeCell ref="F15:F16"/>
-    <mergeCell ref="B36:B37"/>
-    <mergeCell ref="G36:G37"/>
   </mergeCells>
   <hyperlinks>
     <hyperlink ref="H21" r:id="rId1" xr:uid="{4F589D68-222B-4A43-B023-CE0E141D78F2}"/>
@@ -5221,38 +5262,38 @@
   <dimension ref="A1:Z239"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="12.6640625" defaultRowHeight="13"/>
   <cols>
-    <col min="1" max="1" width="49.1640625" style="132" customWidth="1"/>
-    <col min="2" max="2" width="5.5" style="132" customWidth="1"/>
-    <col min="3" max="3" width="12.6640625" style="144" customWidth="1"/>
-    <col min="4" max="4" width="66.6640625" style="132" customWidth="1"/>
-    <col min="5" max="5" width="164.1640625" style="132" customWidth="1"/>
-    <col min="6" max="6" width="12.6640625" style="132" customWidth="1"/>
-    <col min="7" max="16384" width="12.6640625" style="132"/>
+    <col min="1" max="1" width="49.1640625" style="108" customWidth="1"/>
+    <col min="2" max="2" width="5.5" style="108" customWidth="1"/>
+    <col min="3" max="3" width="12.6640625" style="120" customWidth="1"/>
+    <col min="4" max="4" width="66.6640625" style="108" customWidth="1"/>
+    <col min="5" max="5" width="164.1640625" style="108" customWidth="1"/>
+    <col min="6" max="6" width="12.6640625" style="108" customWidth="1"/>
+    <col min="7" max="16384" width="12.6640625" style="108"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11" s="105" customFormat="1" ht="28">
-      <c r="A1" s="129" t="s">
+    <row r="1" spans="1:11" s="85" customFormat="1" ht="28">
+      <c r="A1" s="184" t="s">
         <v>189</v>
       </c>
-      <c r="B1" s="129"/>
-      <c r="C1" s="129"/>
-      <c r="D1" s="129"/>
-      <c r="E1" s="129"/>
+      <c r="B1" s="184"/>
+      <c r="C1" s="184"/>
+      <c r="D1" s="184"/>
+      <c r="E1" s="184"/>
     </row>
     <row r="2" spans="1:11" ht="17">
-      <c r="A2" s="147" t="s">
+      <c r="A2" s="122" t="s">
         <v>0</v>
       </c>
-      <c r="B2" s="148" t="s">
+      <c r="B2" s="123" t="s">
         <v>1</v>
       </c>
-      <c r="C2" s="149" t="s">
+      <c r="C2" s="124" t="s">
         <v>3</v>
       </c>
-      <c r="D2" s="150" t="s">
+      <c r="D2" s="125" t="s">
         <v>4</v>
       </c>
-      <c r="E2" s="151" t="s">
+      <c r="E2" s="126" t="s">
         <v>5</v>
       </c>
       <c r="F2" s="4"/>
@@ -5263,14 +5304,14 @@
       <c r="K2" s="4"/>
     </row>
     <row r="3" spans="1:11" ht="17">
-      <c r="A3" s="152" t="s">
+      <c r="A3" s="127" t="s">
         <v>6</v>
       </c>
-      <c r="B3" s="152"/>
-      <c r="C3" s="153"/>
-      <c r="D3" s="152"/>
-      <c r="E3" s="152"/>
-      <c r="F3" s="131"/>
+      <c r="B3" s="127"/>
+      <c r="C3" s="128"/>
+      <c r="D3" s="127"/>
+      <c r="E3" s="127"/>
+      <c r="F3" s="107"/>
       <c r="G3" s="4"/>
       <c r="H3" s="4"/>
       <c r="I3" s="4"/>
@@ -5278,22 +5319,22 @@
       <c r="K3" s="4"/>
     </row>
     <row r="4" spans="1:11" ht="102" customHeight="1">
-      <c r="A4" s="154" t="s">
+      <c r="A4" s="129" t="s">
         <v>8</v>
       </c>
-      <c r="B4" s="155">
+      <c r="B4" s="130">
         <v>1</v>
       </c>
-      <c r="C4" s="156">
+      <c r="C4" s="131">
         <v>429.95</v>
       </c>
-      <c r="D4" s="157" t="s">
+      <c r="D4" s="132" t="s">
         <v>10</v>
       </c>
-      <c r="E4" s="158" t="s">
+      <c r="E4" s="133" t="s">
         <v>13</v>
       </c>
-      <c r="F4" s="131"/>
+      <c r="F4" s="107"/>
       <c r="G4" s="4"/>
       <c r="H4" s="4"/>
       <c r="I4" s="4"/>
@@ -5301,20 +5342,20 @@
       <c r="K4" s="4"/>
     </row>
     <row r="5" spans="1:11" ht="17">
-      <c r="A5" s="159" t="s">
+      <c r="A5" s="134" t="s">
         <v>16</v>
       </c>
-      <c r="B5" s="155">
+      <c r="B5" s="130">
         <v>1</v>
       </c>
-      <c r="C5" s="156">
+      <c r="C5" s="131">
         <v>89.99</v>
       </c>
-      <c r="D5" s="160"/>
-      <c r="E5" s="158" t="s">
+      <c r="D5" s="135"/>
+      <c r="E5" s="133" t="s">
         <v>19</v>
       </c>
-      <c r="F5" s="135"/>
+      <c r="F5" s="111"/>
       <c r="G5" s="4"/>
       <c r="H5" s="4"/>
       <c r="I5" s="4"/>
@@ -5322,20 +5363,20 @@
       <c r="K5" s="4"/>
     </row>
     <row r="6" spans="1:11" ht="17">
-      <c r="A6" s="159" t="s">
+      <c r="A6" s="134" t="s">
         <v>20</v>
       </c>
-      <c r="B6" s="155">
+      <c r="B6" s="130">
         <v>1</v>
       </c>
-      <c r="C6" s="156">
+      <c r="C6" s="131">
         <v>33.99</v>
       </c>
-      <c r="D6" s="160"/>
-      <c r="E6" s="158" t="s">
+      <c r="D6" s="135"/>
+      <c r="E6" s="133" t="s">
         <v>22</v>
       </c>
-      <c r="F6" s="135"/>
+      <c r="F6" s="111"/>
       <c r="G6" s="4"/>
       <c r="H6" s="4"/>
       <c r="I6" s="4"/>
@@ -5343,22 +5384,22 @@
       <c r="K6" s="4"/>
     </row>
     <row r="7" spans="1:11" ht="17">
-      <c r="A7" s="159" t="s">
+      <c r="A7" s="134" t="s">
         <v>24</v>
       </c>
-      <c r="B7" s="155">
+      <c r="B7" s="130">
         <v>1</v>
       </c>
-      <c r="C7" s="156">
+      <c r="C7" s="131">
         <v>10</v>
       </c>
-      <c r="D7" s="160" t="s">
+      <c r="D7" s="135" t="s">
         <v>25</v>
       </c>
-      <c r="E7" s="158" t="s">
+      <c r="E7" s="133" t="s">
         <v>26</v>
       </c>
-      <c r="F7" s="135"/>
+      <c r="F7" s="111"/>
       <c r="G7" s="4"/>
       <c r="H7" s="4"/>
       <c r="I7" s="4"/>
@@ -5366,22 +5407,22 @@
       <c r="K7" s="4"/>
     </row>
     <row r="8" spans="1:11" ht="17">
-      <c r="A8" s="159" t="s">
+      <c r="A8" s="134" t="s">
         <v>31</v>
       </c>
-      <c r="B8" s="155">
+      <c r="B8" s="130">
         <v>1</v>
       </c>
-      <c r="C8" s="156">
+      <c r="C8" s="131">
         <v>20</v>
       </c>
-      <c r="D8" s="159" t="s">
+      <c r="D8" s="134" t="s">
         <v>32</v>
       </c>
-      <c r="E8" s="158" t="s">
+      <c r="E8" s="133" t="s">
         <v>33</v>
       </c>
-      <c r="F8" s="136"/>
+      <c r="F8" s="112"/>
       <c r="G8" s="4"/>
       <c r="H8" s="4"/>
       <c r="I8" s="4"/>
@@ -5389,13 +5430,13 @@
       <c r="K8" s="4"/>
     </row>
     <row r="9" spans="1:11" ht="17">
-      <c r="A9" s="161" t="s">
+      <c r="A9" s="136" t="s">
         <v>39</v>
       </c>
-      <c r="B9" s="161"/>
-      <c r="C9" s="162"/>
-      <c r="D9" s="161"/>
-      <c r="E9" s="161"/>
+      <c r="B9" s="136"/>
+      <c r="C9" s="137"/>
+      <c r="D9" s="136"/>
+      <c r="E9" s="136"/>
       <c r="F9" s="4"/>
       <c r="G9" s="4"/>
       <c r="H9" s="4"/>
@@ -5404,17 +5445,17 @@
       <c r="K9" s="4"/>
     </row>
     <row r="10" spans="1:11" ht="17">
-      <c r="A10" s="159" t="s">
+      <c r="A10" s="134" t="s">
         <v>40</v>
       </c>
-      <c r="B10" s="155">
+      <c r="B10" s="130">
         <v>1</v>
       </c>
-      <c r="C10" s="156">
+      <c r="C10" s="131">
         <v>22.86</v>
       </c>
-      <c r="D10" s="159"/>
-      <c r="E10" s="158" t="s">
+      <c r="D10" s="134"/>
+      <c r="E10" s="133" t="s">
         <v>41</v>
       </c>
       <c r="F10" s="4"/>
@@ -5425,19 +5466,19 @@
       <c r="K10" s="4"/>
     </row>
     <row r="11" spans="1:11" ht="34">
-      <c r="A11" s="159" t="s">
+      <c r="A11" s="134" t="s">
         <v>43</v>
       </c>
-      <c r="B11" s="155">
+      <c r="B11" s="130">
         <v>1</v>
       </c>
-      <c r="C11" s="156">
+      <c r="C11" s="131">
         <v>8.66</v>
       </c>
-      <c r="D11" s="159" t="s">
+      <c r="D11" s="134" t="s">
         <v>44</v>
       </c>
-      <c r="E11" s="163" t="s">
+      <c r="E11" s="138" t="s">
         <v>45</v>
       </c>
       <c r="F11" s="4"/>
@@ -5448,17 +5489,17 @@
       <c r="K11" s="4"/>
     </row>
     <row r="12" spans="1:11" ht="17">
-      <c r="A12" s="159" t="s">
+      <c r="A12" s="134" t="s">
         <v>51</v>
       </c>
-      <c r="B12" s="155">
+      <c r="B12" s="130">
         <v>2</v>
       </c>
-      <c r="C12" s="156">
+      <c r="C12" s="131">
         <v>3.68</v>
       </c>
-      <c r="D12" s="159"/>
-      <c r="E12" s="163" t="s">
+      <c r="D12" s="134"/>
+      <c r="E12" s="138" t="s">
         <v>52</v>
       </c>
       <c r="F12" s="4"/>
@@ -5469,17 +5510,17 @@
       <c r="K12" s="4"/>
     </row>
     <row r="13" spans="1:11" ht="17">
-      <c r="A13" s="159" t="s">
+      <c r="A13" s="134" t="s">
         <v>55</v>
       </c>
-      <c r="B13" s="155">
+      <c r="B13" s="130">
         <v>4</v>
       </c>
-      <c r="C13" s="156">
+      <c r="C13" s="131">
         <v>10.76</v>
       </c>
-      <c r="D13" s="159"/>
-      <c r="E13" s="163" t="s">
+      <c r="D13" s="134"/>
+      <c r="E13" s="138" t="s">
         <v>57</v>
       </c>
       <c r="F13" s="4"/>
@@ -5490,17 +5531,17 @@
       <c r="K13" s="4"/>
     </row>
     <row r="14" spans="1:11" ht="17">
-      <c r="A14" s="159" t="s">
+      <c r="A14" s="134" t="s">
         <v>59</v>
       </c>
-      <c r="B14" s="155">
+      <c r="B14" s="130">
         <v>6</v>
       </c>
-      <c r="C14" s="156">
+      <c r="C14" s="131">
         <v>27.9</v>
       </c>
-      <c r="D14" s="159"/>
-      <c r="E14" s="163" t="s">
+      <c r="D14" s="134"/>
+      <c r="E14" s="138" t="s">
         <v>60</v>
       </c>
       <c r="F14" s="4"/>
@@ -5511,19 +5552,19 @@
       <c r="K14" s="4"/>
     </row>
     <row r="15" spans="1:11" ht="68" customHeight="1">
-      <c r="A15" s="159" t="s">
+      <c r="A15" s="134" t="s">
         <v>62</v>
       </c>
-      <c r="B15" s="155">
+      <c r="B15" s="130">
         <v>4</v>
       </c>
-      <c r="C15" s="156">
+      <c r="C15" s="131">
         <v>5.3</v>
       </c>
-      <c r="D15" s="159" t="s">
+      <c r="D15" s="134" t="s">
         <v>64</v>
       </c>
-      <c r="E15" s="158" t="s">
+      <c r="E15" s="133" t="s">
         <v>65</v>
       </c>
       <c r="F15" s="4"/>
@@ -5534,17 +5575,17 @@
       <c r="K15" s="4"/>
     </row>
     <row r="16" spans="1:11" ht="17">
-      <c r="A16" s="159" t="s">
+      <c r="A16" s="134" t="s">
         <v>66</v>
       </c>
-      <c r="B16" s="155">
+      <c r="B16" s="130">
         <v>4</v>
       </c>
-      <c r="C16" s="156">
+      <c r="C16" s="131">
         <v>2.16</v>
       </c>
-      <c r="D16" s="159"/>
-      <c r="E16" s="158" t="s">
+      <c r="D16" s="134"/>
+      <c r="E16" s="133" t="s">
         <v>67</v>
       </c>
       <c r="F16" s="4"/>
@@ -5555,712 +5596,712 @@
       <c r="K16" s="4"/>
     </row>
     <row r="17" spans="1:26" ht="17">
-      <c r="A17" s="164" t="s">
+      <c r="A17" s="139" t="s">
         <v>69</v>
       </c>
-      <c r="B17" s="164"/>
-      <c r="C17" s="165"/>
-      <c r="D17" s="164"/>
-      <c r="E17" s="164"/>
+      <c r="B17" s="139"/>
+      <c r="C17" s="140"/>
+      <c r="D17" s="139"/>
+      <c r="E17" s="139"/>
       <c r="F17" s="2"/>
-      <c r="G17" s="137"/>
-      <c r="H17" s="137"/>
-      <c r="I17" s="137"/>
-      <c r="J17" s="137"/>
-      <c r="K17" s="137"/>
-      <c r="L17" s="137"/>
-      <c r="M17" s="137"/>
-      <c r="N17" s="137"/>
-      <c r="O17" s="137"/>
-      <c r="P17" s="137"/>
-      <c r="Q17" s="137"/>
-      <c r="R17" s="137"/>
-      <c r="S17" s="137"/>
-      <c r="T17" s="137"/>
-      <c r="U17" s="137"/>
-      <c r="V17" s="137"/>
-      <c r="W17" s="137"/>
-      <c r="X17" s="137"/>
-      <c r="Y17" s="137"/>
+      <c r="G17" s="113"/>
+      <c r="H17" s="113"/>
+      <c r="I17" s="113"/>
+      <c r="J17" s="113"/>
+      <c r="K17" s="113"/>
+      <c r="L17" s="113"/>
+      <c r="M17" s="113"/>
+      <c r="N17" s="113"/>
+      <c r="O17" s="113"/>
+      <c r="P17" s="113"/>
+      <c r="Q17" s="113"/>
+      <c r="R17" s="113"/>
+      <c r="S17" s="113"/>
+      <c r="T17" s="113"/>
+      <c r="U17" s="113"/>
+      <c r="V17" s="113"/>
+      <c r="W17" s="113"/>
+      <c r="X17" s="113"/>
+      <c r="Y17" s="113"/>
     </row>
     <row r="18" spans="1:26" ht="17">
-      <c r="A18" s="159" t="s">
+      <c r="A18" s="134" t="s">
         <v>71</v>
       </c>
-      <c r="B18" s="155">
+      <c r="B18" s="130">
         <v>1</v>
       </c>
-      <c r="C18" s="156">
+      <c r="C18" s="131">
         <v>249</v>
       </c>
-      <c r="D18" s="166"/>
-      <c r="E18" s="167" t="s">
+      <c r="D18" s="141"/>
+      <c r="E18" s="142" t="s">
         <v>72</v>
       </c>
       <c r="F18" s="2"/>
-      <c r="G18" s="137"/>
-      <c r="H18" s="137"/>
-      <c r="I18" s="137"/>
-      <c r="J18" s="137"/>
-      <c r="K18" s="137"/>
-      <c r="L18" s="137"/>
-      <c r="M18" s="137"/>
-      <c r="N18" s="137"/>
-      <c r="O18" s="137"/>
-      <c r="P18" s="137"/>
-      <c r="Q18" s="137"/>
-      <c r="R18" s="137"/>
-      <c r="S18" s="137"/>
-      <c r="T18" s="137"/>
-      <c r="U18" s="137"/>
-      <c r="V18" s="137"/>
-      <c r="W18" s="137"/>
-      <c r="X18" s="137"/>
-      <c r="Y18" s="137"/>
+      <c r="G18" s="113"/>
+      <c r="H18" s="113"/>
+      <c r="I18" s="113"/>
+      <c r="J18" s="113"/>
+      <c r="K18" s="113"/>
+      <c r="L18" s="113"/>
+      <c r="M18" s="113"/>
+      <c r="N18" s="113"/>
+      <c r="O18" s="113"/>
+      <c r="P18" s="113"/>
+      <c r="Q18" s="113"/>
+      <c r="R18" s="113"/>
+      <c r="S18" s="113"/>
+      <c r="T18" s="113"/>
+      <c r="U18" s="113"/>
+      <c r="V18" s="113"/>
+      <c r="W18" s="113"/>
+      <c r="X18" s="113"/>
+      <c r="Y18" s="113"/>
     </row>
     <row r="19" spans="1:26" ht="17">
-      <c r="A19" s="159" t="s">
+      <c r="A19" s="134" t="s">
         <v>74</v>
       </c>
-      <c r="B19" s="155">
+      <c r="B19" s="130">
         <v>1</v>
       </c>
-      <c r="C19" s="156">
+      <c r="C19" s="131">
         <v>100</v>
       </c>
-      <c r="D19" s="168"/>
-      <c r="E19" s="167" t="s">
+      <c r="D19" s="143"/>
+      <c r="E19" s="142" t="s">
         <v>75</v>
       </c>
       <c r="F19" s="2"/>
-      <c r="G19" s="137"/>
-      <c r="H19" s="137"/>
-      <c r="I19" s="137"/>
-      <c r="J19" s="137"/>
-      <c r="K19" s="137"/>
-      <c r="L19" s="137"/>
-      <c r="M19" s="137"/>
-      <c r="N19" s="137"/>
-      <c r="O19" s="137"/>
-      <c r="P19" s="137"/>
-      <c r="Q19" s="137"/>
-      <c r="R19" s="137"/>
-      <c r="S19" s="137"/>
-      <c r="T19" s="137"/>
-      <c r="U19" s="137"/>
-      <c r="V19" s="137"/>
-      <c r="W19" s="137"/>
-      <c r="X19" s="137"/>
-      <c r="Y19" s="137"/>
-      <c r="Z19" s="137"/>
+      <c r="G19" s="113"/>
+      <c r="H19" s="113"/>
+      <c r="I19" s="113"/>
+      <c r="J19" s="113"/>
+      <c r="K19" s="113"/>
+      <c r="L19" s="113"/>
+      <c r="M19" s="113"/>
+      <c r="N19" s="113"/>
+      <c r="O19" s="113"/>
+      <c r="P19" s="113"/>
+      <c r="Q19" s="113"/>
+      <c r="R19" s="113"/>
+      <c r="S19" s="113"/>
+      <c r="T19" s="113"/>
+      <c r="U19" s="113"/>
+      <c r="V19" s="113"/>
+      <c r="W19" s="113"/>
+      <c r="X19" s="113"/>
+      <c r="Y19" s="113"/>
+      <c r="Z19" s="113"/>
     </row>
     <row r="20" spans="1:26" ht="17">
-      <c r="A20" s="164" t="s">
+      <c r="A20" s="139" t="s">
         <v>78</v>
       </c>
-      <c r="B20" s="164"/>
-      <c r="C20" s="165"/>
-      <c r="D20" s="164"/>
-      <c r="E20" s="164"/>
+      <c r="B20" s="139"/>
+      <c r="C20" s="140"/>
+      <c r="D20" s="139"/>
+      <c r="E20" s="139"/>
       <c r="F20" s="2"/>
-      <c r="G20" s="137"/>
-      <c r="H20" s="137"/>
-      <c r="I20" s="137"/>
-      <c r="J20" s="137"/>
-      <c r="K20" s="137"/>
-      <c r="L20" s="137"/>
-      <c r="M20" s="137"/>
-      <c r="N20" s="137"/>
-      <c r="O20" s="137"/>
-      <c r="P20" s="137"/>
-      <c r="Q20" s="137"/>
-      <c r="R20" s="137"/>
-      <c r="S20" s="137"/>
-      <c r="T20" s="137"/>
-      <c r="U20" s="137"/>
-      <c r="V20" s="137"/>
-      <c r="W20" s="137"/>
-      <c r="X20" s="137"/>
-      <c r="Y20" s="137"/>
-      <c r="Z20" s="137"/>
+      <c r="G20" s="113"/>
+      <c r="H20" s="113"/>
+      <c r="I20" s="113"/>
+      <c r="J20" s="113"/>
+      <c r="K20" s="113"/>
+      <c r="L20" s="113"/>
+      <c r="M20" s="113"/>
+      <c r="N20" s="113"/>
+      <c r="O20" s="113"/>
+      <c r="P20" s="113"/>
+      <c r="Q20" s="113"/>
+      <c r="R20" s="113"/>
+      <c r="S20" s="113"/>
+      <c r="T20" s="113"/>
+      <c r="U20" s="113"/>
+      <c r="V20" s="113"/>
+      <c r="W20" s="113"/>
+      <c r="X20" s="113"/>
+      <c r="Y20" s="113"/>
+      <c r="Z20" s="113"/>
     </row>
     <row r="21" spans="1:26" ht="56" customHeight="1">
-      <c r="A21" s="159" t="s">
+      <c r="A21" s="134" t="s">
         <v>82</v>
       </c>
-      <c r="B21" s="155">
+      <c r="B21" s="130">
         <v>1</v>
       </c>
-      <c r="C21" s="156">
+      <c r="C21" s="131">
         <v>1200</v>
       </c>
-      <c r="D21" s="169" t="s">
+      <c r="D21" s="144" t="s">
         <v>83</v>
       </c>
-      <c r="E21" s="170" t="s">
+      <c r="E21" s="145" t="s">
         <v>89</v>
       </c>
       <c r="F21" s="2"/>
-      <c r="G21" s="137"/>
-      <c r="H21" s="137"/>
-      <c r="I21" s="137"/>
-      <c r="J21" s="137"/>
-      <c r="K21" s="137"/>
-      <c r="L21" s="137"/>
-      <c r="M21" s="137"/>
-      <c r="N21" s="137"/>
-      <c r="O21" s="137"/>
-      <c r="P21" s="137"/>
-      <c r="Q21" s="137"/>
-      <c r="R21" s="137"/>
-      <c r="S21" s="137"/>
-      <c r="T21" s="137"/>
-      <c r="U21" s="137"/>
-      <c r="V21" s="137"/>
-      <c r="W21" s="137"/>
-      <c r="X21" s="137"/>
-      <c r="Y21" s="137"/>
-      <c r="Z21" s="137"/>
+      <c r="G21" s="113"/>
+      <c r="H21" s="113"/>
+      <c r="I21" s="113"/>
+      <c r="J21" s="113"/>
+      <c r="K21" s="113"/>
+      <c r="L21" s="113"/>
+      <c r="M21" s="113"/>
+      <c r="N21" s="113"/>
+      <c r="O21" s="113"/>
+      <c r="P21" s="113"/>
+      <c r="Q21" s="113"/>
+      <c r="R21" s="113"/>
+      <c r="S21" s="113"/>
+      <c r="T21" s="113"/>
+      <c r="U21" s="113"/>
+      <c r="V21" s="113"/>
+      <c r="W21" s="113"/>
+      <c r="X21" s="113"/>
+      <c r="Y21" s="113"/>
+      <c r="Z21" s="113"/>
     </row>
     <row r="22" spans="1:26" ht="17">
-      <c r="A22" s="164" t="s">
+      <c r="A22" s="139" t="s">
         <v>90</v>
       </c>
-      <c r="B22" s="164"/>
-      <c r="C22" s="165"/>
-      <c r="D22" s="164"/>
-      <c r="E22" s="164"/>
+      <c r="B22" s="139"/>
+      <c r="C22" s="140"/>
+      <c r="D22" s="139"/>
+      <c r="E22" s="139"/>
       <c r="F22" s="2"/>
-      <c r="G22" s="137"/>
-      <c r="H22" s="137"/>
-      <c r="I22" s="137"/>
-      <c r="J22" s="137"/>
-      <c r="K22" s="137"/>
-      <c r="L22" s="137"/>
-      <c r="M22" s="137"/>
-      <c r="N22" s="137"/>
-      <c r="O22" s="137"/>
-      <c r="P22" s="137"/>
-      <c r="Q22" s="137"/>
-      <c r="R22" s="137"/>
-      <c r="S22" s="137"/>
-      <c r="T22" s="137"/>
-      <c r="U22" s="137"/>
-      <c r="V22" s="137"/>
-      <c r="W22" s="137"/>
-      <c r="X22" s="137"/>
-      <c r="Y22" s="137"/>
-      <c r="Z22" s="137"/>
+      <c r="G22" s="113"/>
+      <c r="H22" s="113"/>
+      <c r="I22" s="113"/>
+      <c r="J22" s="113"/>
+      <c r="K22" s="113"/>
+      <c r="L22" s="113"/>
+      <c r="M22" s="113"/>
+      <c r="N22" s="113"/>
+      <c r="O22" s="113"/>
+      <c r="P22" s="113"/>
+      <c r="Q22" s="113"/>
+      <c r="R22" s="113"/>
+      <c r="S22" s="113"/>
+      <c r="T22" s="113"/>
+      <c r="U22" s="113"/>
+      <c r="V22" s="113"/>
+      <c r="W22" s="113"/>
+      <c r="X22" s="113"/>
+      <c r="Y22" s="113"/>
+      <c r="Z22" s="113"/>
     </row>
     <row r="23" spans="1:26" ht="17">
-      <c r="A23" s="159" t="s">
+      <c r="A23" s="134" t="s">
         <v>91</v>
       </c>
-      <c r="B23" s="155">
+      <c r="B23" s="130">
         <v>1</v>
       </c>
-      <c r="C23" s="156">
+      <c r="C23" s="131">
         <v>125</v>
       </c>
-      <c r="D23" s="171"/>
-      <c r="E23" s="167" t="s">
+      <c r="D23" s="146"/>
+      <c r="E23" s="142" t="s">
         <v>92</v>
       </c>
-      <c r="F23" s="138"/>
-      <c r="G23" s="138"/>
-      <c r="H23" s="138"/>
-      <c r="I23" s="138"/>
-      <c r="J23" s="138"/>
-      <c r="K23" s="137"/>
-      <c r="L23" s="137"/>
-      <c r="M23" s="137"/>
-      <c r="N23" s="137"/>
-      <c r="O23" s="137"/>
-      <c r="P23" s="137"/>
-      <c r="Q23" s="137"/>
-      <c r="R23" s="137"/>
-      <c r="S23" s="137"/>
-      <c r="T23" s="137"/>
-      <c r="U23" s="137"/>
-      <c r="V23" s="137"/>
-      <c r="W23" s="137"/>
-      <c r="X23" s="137"/>
-      <c r="Y23" s="137"/>
-      <c r="Z23" s="137"/>
+      <c r="F23" s="114"/>
+      <c r="G23" s="114"/>
+      <c r="H23" s="114"/>
+      <c r="I23" s="114"/>
+      <c r="J23" s="114"/>
+      <c r="K23" s="113"/>
+      <c r="L23" s="113"/>
+      <c r="M23" s="113"/>
+      <c r="N23" s="113"/>
+      <c r="O23" s="113"/>
+      <c r="P23" s="113"/>
+      <c r="Q23" s="113"/>
+      <c r="R23" s="113"/>
+      <c r="S23" s="113"/>
+      <c r="T23" s="113"/>
+      <c r="U23" s="113"/>
+      <c r="V23" s="113"/>
+      <c r="W23" s="113"/>
+      <c r="X23" s="113"/>
+      <c r="Y23" s="113"/>
+      <c r="Z23" s="113"/>
     </row>
     <row r="24" spans="1:26" ht="17">
-      <c r="A24" s="159" t="s">
+      <c r="A24" s="134" t="s">
         <v>93</v>
       </c>
-      <c r="B24" s="155">
+      <c r="B24" s="130">
         <v>1</v>
       </c>
-      <c r="C24" s="156">
+      <c r="C24" s="131">
         <v>249.75</v>
       </c>
-      <c r="D24" s="171"/>
-      <c r="E24" s="172" t="s">
+      <c r="D24" s="146"/>
+      <c r="E24" s="147" t="s">
         <v>94</v>
       </c>
-      <c r="K24" s="137"/>
-      <c r="L24" s="137"/>
-      <c r="M24" s="137"/>
-      <c r="N24" s="137"/>
-      <c r="O24" s="137"/>
-      <c r="P24" s="137"/>
-      <c r="Q24" s="137"/>
-      <c r="R24" s="137"/>
-      <c r="S24" s="137"/>
-      <c r="T24" s="137"/>
-      <c r="U24" s="137"/>
-      <c r="V24" s="137"/>
-      <c r="W24" s="137"/>
-      <c r="X24" s="137"/>
-      <c r="Y24" s="137"/>
-      <c r="Z24" s="137"/>
+      <c r="K24" s="113"/>
+      <c r="L24" s="113"/>
+      <c r="M24" s="113"/>
+      <c r="N24" s="113"/>
+      <c r="O24" s="113"/>
+      <c r="P24" s="113"/>
+      <c r="Q24" s="113"/>
+      <c r="R24" s="113"/>
+      <c r="S24" s="113"/>
+      <c r="T24" s="113"/>
+      <c r="U24" s="113"/>
+      <c r="V24" s="113"/>
+      <c r="W24" s="113"/>
+      <c r="X24" s="113"/>
+      <c r="Y24" s="113"/>
+      <c r="Z24" s="113"/>
     </row>
     <row r="25" spans="1:26" ht="68">
-      <c r="A25" s="159" t="s">
+      <c r="A25" s="134" t="s">
         <v>95</v>
       </c>
-      <c r="B25" s="155">
+      <c r="B25" s="130">
         <v>1</v>
       </c>
-      <c r="C25" s="156">
+      <c r="C25" s="131">
         <v>29.99</v>
       </c>
-      <c r="D25" s="173" t="s">
+      <c r="D25" s="148" t="s">
         <v>96</v>
       </c>
-      <c r="E25" s="167" t="s">
+      <c r="E25" s="142" t="s">
         <v>97</v>
       </c>
-      <c r="F25" s="137"/>
-      <c r="G25" s="137"/>
-      <c r="H25" s="137"/>
-      <c r="I25" s="137"/>
-      <c r="J25" s="137"/>
-      <c r="K25" s="137"/>
-      <c r="L25" s="137"/>
-      <c r="M25" s="137"/>
-      <c r="N25" s="137"/>
-      <c r="O25" s="137"/>
-      <c r="P25" s="137"/>
-      <c r="Q25" s="137"/>
-      <c r="R25" s="137"/>
-      <c r="S25" s="137"/>
-      <c r="T25" s="137"/>
-      <c r="U25" s="137"/>
-      <c r="V25" s="137"/>
-      <c r="W25" s="137"/>
-      <c r="X25" s="137"/>
-      <c r="Y25" s="137"/>
-      <c r="Z25" s="137"/>
+      <c r="F25" s="113"/>
+      <c r="G25" s="113"/>
+      <c r="H25" s="113"/>
+      <c r="I25" s="113"/>
+      <c r="J25" s="113"/>
+      <c r="K25" s="113"/>
+      <c r="L25" s="113"/>
+      <c r="M25" s="113"/>
+      <c r="N25" s="113"/>
+      <c r="O25" s="113"/>
+      <c r="P25" s="113"/>
+      <c r="Q25" s="113"/>
+      <c r="R25" s="113"/>
+      <c r="S25" s="113"/>
+      <c r="T25" s="113"/>
+      <c r="U25" s="113"/>
+      <c r="V25" s="113"/>
+      <c r="W25" s="113"/>
+      <c r="X25" s="113"/>
+      <c r="Y25" s="113"/>
+      <c r="Z25" s="113"/>
     </row>
     <row r="26" spans="1:26" ht="34">
-      <c r="A26" s="159" t="s">
+      <c r="A26" s="134" t="s">
         <v>98</v>
       </c>
-      <c r="B26" s="155">
+      <c r="B26" s="130">
         <v>1</v>
       </c>
-      <c r="C26" s="156">
+      <c r="C26" s="131">
         <v>6.99</v>
       </c>
-      <c r="D26" s="174"/>
-      <c r="E26" s="175" t="s">
+      <c r="D26" s="149"/>
+      <c r="E26" s="150" t="s">
         <v>99</v>
       </c>
-      <c r="I26" s="137"/>
-      <c r="J26" s="137"/>
-      <c r="K26" s="137"/>
-      <c r="L26" s="137"/>
-      <c r="M26" s="137"/>
-      <c r="N26" s="137"/>
-      <c r="O26" s="137"/>
-      <c r="P26" s="137"/>
-      <c r="Q26" s="137"/>
-      <c r="R26" s="137"/>
-      <c r="S26" s="137"/>
-      <c r="T26" s="137"/>
-      <c r="U26" s="137"/>
-      <c r="V26" s="137"/>
-      <c r="W26" s="137"/>
-      <c r="X26" s="137"/>
-      <c r="Y26" s="137"/>
-      <c r="Z26" s="137"/>
+      <c r="I26" s="113"/>
+      <c r="J26" s="113"/>
+      <c r="K26" s="113"/>
+      <c r="L26" s="113"/>
+      <c r="M26" s="113"/>
+      <c r="N26" s="113"/>
+      <c r="O26" s="113"/>
+      <c r="P26" s="113"/>
+      <c r="Q26" s="113"/>
+      <c r="R26" s="113"/>
+      <c r="S26" s="113"/>
+      <c r="T26" s="113"/>
+      <c r="U26" s="113"/>
+      <c r="V26" s="113"/>
+      <c r="W26" s="113"/>
+      <c r="X26" s="113"/>
+      <c r="Y26" s="113"/>
+      <c r="Z26" s="113"/>
     </row>
     <row r="27" spans="1:26" ht="17">
-      <c r="A27" s="159" t="s">
+      <c r="A27" s="134" t="s">
         <v>100</v>
       </c>
-      <c r="B27" s="155">
+      <c r="B27" s="130">
         <v>1</v>
       </c>
-      <c r="C27" s="156">
+      <c r="C27" s="131">
         <v>9.99</v>
       </c>
-      <c r="D27" s="176" t="s">
+      <c r="D27" s="151" t="s">
         <v>101</v>
       </c>
-      <c r="E27" s="177" t="s">
+      <c r="E27" s="152" t="s">
         <v>102</v>
       </c>
-      <c r="F27" s="139"/>
-      <c r="G27" s="139"/>
-      <c r="H27" s="139"/>
-      <c r="I27" s="137"/>
-      <c r="J27" s="137"/>
-      <c r="K27" s="137"/>
-      <c r="L27" s="137"/>
-      <c r="M27" s="137"/>
-      <c r="N27" s="137"/>
-      <c r="O27" s="137"/>
-      <c r="P27" s="137"/>
-      <c r="Q27" s="137"/>
-      <c r="R27" s="137"/>
-      <c r="S27" s="137"/>
-      <c r="T27" s="137"/>
-      <c r="U27" s="137"/>
-      <c r="V27" s="137"/>
-      <c r="W27" s="137"/>
-      <c r="X27" s="137"/>
-      <c r="Y27" s="137"/>
-      <c r="Z27" s="137"/>
+      <c r="F27" s="115"/>
+      <c r="G27" s="115"/>
+      <c r="H27" s="115"/>
+      <c r="I27" s="113"/>
+      <c r="J27" s="113"/>
+      <c r="K27" s="113"/>
+      <c r="L27" s="113"/>
+      <c r="M27" s="113"/>
+      <c r="N27" s="113"/>
+      <c r="O27" s="113"/>
+      <c r="P27" s="113"/>
+      <c r="Q27" s="113"/>
+      <c r="R27" s="113"/>
+      <c r="S27" s="113"/>
+      <c r="T27" s="113"/>
+      <c r="U27" s="113"/>
+      <c r="V27" s="113"/>
+      <c r="W27" s="113"/>
+      <c r="X27" s="113"/>
+      <c r="Y27" s="113"/>
+      <c r="Z27" s="113"/>
     </row>
     <row r="28" spans="1:26" ht="17">
-      <c r="A28" s="159" t="s">
+      <c r="A28" s="134" t="s">
         <v>103</v>
       </c>
-      <c r="B28" s="155">
+      <c r="B28" s="130">
         <v>1</v>
       </c>
-      <c r="C28" s="156">
+      <c r="C28" s="131">
         <v>8.99</v>
       </c>
-      <c r="D28" s="176" t="s">
+      <c r="D28" s="151" t="s">
         <v>101</v>
       </c>
-      <c r="E28" s="177" t="s">
+      <c r="E28" s="152" t="s">
         <v>104</v>
       </c>
-      <c r="F28" s="139"/>
-      <c r="G28" s="139"/>
-      <c r="H28" s="139"/>
-      <c r="I28" s="137"/>
-      <c r="J28" s="137"/>
-      <c r="K28" s="137"/>
-      <c r="L28" s="137"/>
-      <c r="M28" s="137"/>
-      <c r="N28" s="137"/>
-      <c r="O28" s="137"/>
-      <c r="P28" s="137"/>
-      <c r="Q28" s="137"/>
-      <c r="R28" s="137"/>
-      <c r="S28" s="137"/>
-      <c r="T28" s="137"/>
-      <c r="U28" s="137"/>
-      <c r="V28" s="137"/>
-      <c r="W28" s="137"/>
-      <c r="X28" s="137"/>
-      <c r="Y28" s="137"/>
-      <c r="Z28" s="137"/>
+      <c r="F28" s="115"/>
+      <c r="G28" s="115"/>
+      <c r="H28" s="115"/>
+      <c r="I28" s="113"/>
+      <c r="J28" s="113"/>
+      <c r="K28" s="113"/>
+      <c r="L28" s="113"/>
+      <c r="M28" s="113"/>
+      <c r="N28" s="113"/>
+      <c r="O28" s="113"/>
+      <c r="P28" s="113"/>
+      <c r="Q28" s="113"/>
+      <c r="R28" s="113"/>
+      <c r="S28" s="113"/>
+      <c r="T28" s="113"/>
+      <c r="U28" s="113"/>
+      <c r="V28" s="113"/>
+      <c r="W28" s="113"/>
+      <c r="X28" s="113"/>
+      <c r="Y28" s="113"/>
+      <c r="Z28" s="113"/>
     </row>
     <row r="29" spans="1:26" ht="46">
-      <c r="A29" s="159" t="s">
+      <c r="A29" s="134" t="s">
         <v>105</v>
       </c>
-      <c r="B29" s="155">
+      <c r="B29" s="130">
         <v>1</v>
       </c>
-      <c r="C29" s="156">
+      <c r="C29" s="131">
         <v>7.99</v>
       </c>
-      <c r="D29" s="178"/>
-      <c r="E29" s="179" t="s">
+      <c r="D29" s="153"/>
+      <c r="E29" s="154" t="s">
         <v>106</v>
       </c>
-      <c r="F29" s="139"/>
-      <c r="G29" s="139"/>
-      <c r="H29" s="139"/>
-      <c r="I29" s="137"/>
-      <c r="J29" s="137"/>
-      <c r="K29" s="137"/>
-      <c r="L29" s="137"/>
-      <c r="M29" s="137"/>
-      <c r="N29" s="137"/>
-      <c r="O29" s="137"/>
-      <c r="P29" s="137"/>
-      <c r="Q29" s="137"/>
-      <c r="R29" s="137"/>
-      <c r="S29" s="137"/>
-      <c r="T29" s="137"/>
-      <c r="U29" s="137"/>
-      <c r="V29" s="137"/>
-      <c r="W29" s="137"/>
-      <c r="X29" s="137"/>
-      <c r="Y29" s="137"/>
-      <c r="Z29" s="137"/>
+      <c r="F29" s="115"/>
+      <c r="G29" s="115"/>
+      <c r="H29" s="115"/>
+      <c r="I29" s="113"/>
+      <c r="J29" s="113"/>
+      <c r="K29" s="113"/>
+      <c r="L29" s="113"/>
+      <c r="M29" s="113"/>
+      <c r="N29" s="113"/>
+      <c r="O29" s="113"/>
+      <c r="P29" s="113"/>
+      <c r="Q29" s="113"/>
+      <c r="R29" s="113"/>
+      <c r="S29" s="113"/>
+      <c r="T29" s="113"/>
+      <c r="U29" s="113"/>
+      <c r="V29" s="113"/>
+      <c r="W29" s="113"/>
+      <c r="X29" s="113"/>
+      <c r="Y29" s="113"/>
+      <c r="Z29" s="113"/>
     </row>
     <row r="30" spans="1:26" ht="17">
-      <c r="A30" s="159" t="s">
+      <c r="A30" s="134" t="s">
         <v>107</v>
       </c>
-      <c r="B30" s="155">
+      <c r="B30" s="130">
         <v>1</v>
       </c>
-      <c r="C30" s="156">
+      <c r="C30" s="131">
         <v>334</v>
       </c>
-      <c r="D30" s="171"/>
-      <c r="E30" s="175" t="s">
+      <c r="D30" s="146"/>
+      <c r="E30" s="150" t="s">
         <v>108</v>
       </c>
-      <c r="F30" s="137"/>
-      <c r="G30" s="137"/>
-      <c r="H30" s="137"/>
-      <c r="I30" s="137"/>
-      <c r="J30" s="137"/>
-      <c r="K30" s="137"/>
-      <c r="L30" s="137"/>
-      <c r="M30" s="137"/>
-      <c r="N30" s="137"/>
-      <c r="O30" s="137"/>
-      <c r="P30" s="137"/>
-      <c r="Q30" s="137"/>
-      <c r="R30" s="137"/>
-      <c r="S30" s="137"/>
-      <c r="T30" s="137"/>
-      <c r="U30" s="137"/>
-      <c r="V30" s="137"/>
-      <c r="W30" s="137"/>
-      <c r="X30" s="137"/>
-      <c r="Y30" s="137"/>
-      <c r="Z30" s="137"/>
+      <c r="F30" s="113"/>
+      <c r="G30" s="113"/>
+      <c r="H30" s="113"/>
+      <c r="I30" s="113"/>
+      <c r="J30" s="113"/>
+      <c r="K30" s="113"/>
+      <c r="L30" s="113"/>
+      <c r="M30" s="113"/>
+      <c r="N30" s="113"/>
+      <c r="O30" s="113"/>
+      <c r="P30" s="113"/>
+      <c r="Q30" s="113"/>
+      <c r="R30" s="113"/>
+      <c r="S30" s="113"/>
+      <c r="T30" s="113"/>
+      <c r="U30" s="113"/>
+      <c r="V30" s="113"/>
+      <c r="W30" s="113"/>
+      <c r="X30" s="113"/>
+      <c r="Y30" s="113"/>
+      <c r="Z30" s="113"/>
     </row>
     <row r="31" spans="1:26" ht="17">
-      <c r="A31" s="180" t="s">
+      <c r="A31" s="155" t="s">
         <v>109</v>
       </c>
-      <c r="B31" s="180"/>
-      <c r="C31" s="181"/>
-      <c r="D31" s="180"/>
-      <c r="E31" s="180"/>
+      <c r="B31" s="155"/>
+      <c r="C31" s="156"/>
+      <c r="D31" s="155"/>
+      <c r="E31" s="155"/>
       <c r="F31" s="2"/>
-      <c r="G31" s="137"/>
-      <c r="H31" s="137"/>
-      <c r="I31" s="137"/>
-      <c r="J31" s="137"/>
-      <c r="K31" s="137"/>
-      <c r="L31" s="137"/>
-      <c r="M31" s="137"/>
-      <c r="N31" s="137"/>
-      <c r="O31" s="137"/>
-      <c r="P31" s="137"/>
-      <c r="Q31" s="137"/>
-      <c r="R31" s="137"/>
-      <c r="S31" s="137"/>
-      <c r="T31" s="137"/>
-      <c r="U31" s="137"/>
-      <c r="V31" s="137"/>
-      <c r="W31" s="137"/>
-      <c r="X31" s="137"/>
-      <c r="Y31" s="137"/>
-      <c r="Z31" s="137"/>
+      <c r="G31" s="113"/>
+      <c r="H31" s="113"/>
+      <c r="I31" s="113"/>
+      <c r="J31" s="113"/>
+      <c r="K31" s="113"/>
+      <c r="L31" s="113"/>
+      <c r="M31" s="113"/>
+      <c r="N31" s="113"/>
+      <c r="O31" s="113"/>
+      <c r="P31" s="113"/>
+      <c r="Q31" s="113"/>
+      <c r="R31" s="113"/>
+      <c r="S31" s="113"/>
+      <c r="T31" s="113"/>
+      <c r="U31" s="113"/>
+      <c r="V31" s="113"/>
+      <c r="W31" s="113"/>
+      <c r="X31" s="113"/>
+      <c r="Y31" s="113"/>
+      <c r="Z31" s="113"/>
     </row>
     <row r="32" spans="1:26" ht="17">
-      <c r="A32" s="159" t="s">
+      <c r="A32" s="134" t="s">
         <v>110</v>
       </c>
-      <c r="B32" s="155">
+      <c r="B32" s="130">
         <v>1</v>
       </c>
-      <c r="C32" s="156">
+      <c r="C32" s="131">
         <v>8.99</v>
       </c>
-      <c r="D32" s="159" t="s">
+      <c r="D32" s="134" t="s">
         <v>111</v>
       </c>
-      <c r="E32" s="182" t="s">
+      <c r="E32" s="157" t="s">
         <v>112</v>
       </c>
-      <c r="F32" s="137"/>
-      <c r="G32" s="137"/>
-      <c r="H32" s="137"/>
-      <c r="I32" s="137"/>
-      <c r="J32" s="137"/>
-      <c r="K32" s="137"/>
-      <c r="L32" s="137"/>
-      <c r="M32" s="137"/>
-      <c r="N32" s="137"/>
-      <c r="O32" s="137"/>
-      <c r="P32" s="137"/>
-      <c r="Q32" s="137"/>
-      <c r="R32" s="137"/>
-      <c r="S32" s="137"/>
-      <c r="T32" s="137"/>
-      <c r="U32" s="137"/>
-      <c r="V32" s="137"/>
-      <c r="W32" s="137"/>
-      <c r="X32" s="137"/>
-      <c r="Y32" s="137"/>
-      <c r="Z32" s="137"/>
+      <c r="F32" s="113"/>
+      <c r="G32" s="113"/>
+      <c r="H32" s="113"/>
+      <c r="I32" s="113"/>
+      <c r="J32" s="113"/>
+      <c r="K32" s="113"/>
+      <c r="L32" s="113"/>
+      <c r="M32" s="113"/>
+      <c r="N32" s="113"/>
+      <c r="O32" s="113"/>
+      <c r="P32" s="113"/>
+      <c r="Q32" s="113"/>
+      <c r="R32" s="113"/>
+      <c r="S32" s="113"/>
+      <c r="T32" s="113"/>
+      <c r="U32" s="113"/>
+      <c r="V32" s="113"/>
+      <c r="W32" s="113"/>
+      <c r="X32" s="113"/>
+      <c r="Y32" s="113"/>
+      <c r="Z32" s="113"/>
     </row>
     <row r="33" spans="1:26" ht="17">
-      <c r="A33" s="159" t="s">
+      <c r="A33" s="134" t="s">
         <v>113</v>
       </c>
-      <c r="B33" s="155">
+      <c r="B33" s="130">
         <v>1</v>
       </c>
-      <c r="C33" s="156">
+      <c r="C33" s="131">
         <v>3.38</v>
       </c>
-      <c r="D33" s="173" t="s">
+      <c r="D33" s="148" t="s">
         <v>114</v>
       </c>
-      <c r="E33" s="167" t="s">
+      <c r="E33" s="142" t="s">
         <v>115</v>
       </c>
-      <c r="F33" s="137"/>
-      <c r="G33" s="137"/>
-      <c r="H33" s="137"/>
-      <c r="I33" s="137"/>
-      <c r="J33" s="137"/>
-      <c r="K33" s="137"/>
-      <c r="L33" s="137"/>
-      <c r="M33" s="137"/>
-      <c r="N33" s="137"/>
-      <c r="O33" s="137"/>
-      <c r="P33" s="137"/>
-      <c r="Q33" s="137"/>
-      <c r="R33" s="137"/>
-      <c r="S33" s="137"/>
-      <c r="T33" s="137"/>
-      <c r="U33" s="137"/>
-      <c r="V33" s="137"/>
-      <c r="W33" s="137"/>
-      <c r="X33" s="137"/>
-      <c r="Y33" s="137"/>
-      <c r="Z33" s="137"/>
+      <c r="F33" s="113"/>
+      <c r="G33" s="113"/>
+      <c r="H33" s="113"/>
+      <c r="I33" s="113"/>
+      <c r="J33" s="113"/>
+      <c r="K33" s="113"/>
+      <c r="L33" s="113"/>
+      <c r="M33" s="113"/>
+      <c r="N33" s="113"/>
+      <c r="O33" s="113"/>
+      <c r="P33" s="113"/>
+      <c r="Q33" s="113"/>
+      <c r="R33" s="113"/>
+      <c r="S33" s="113"/>
+      <c r="T33" s="113"/>
+      <c r="U33" s="113"/>
+      <c r="V33" s="113"/>
+      <c r="W33" s="113"/>
+      <c r="X33" s="113"/>
+      <c r="Y33" s="113"/>
+      <c r="Z33" s="113"/>
     </row>
     <row r="34" spans="1:26" ht="68">
-      <c r="A34" s="159" t="s">
+      <c r="A34" s="134" t="s">
         <v>116</v>
       </c>
-      <c r="B34" s="155">
+      <c r="B34" s="130">
         <v>1</v>
       </c>
-      <c r="C34" s="156">
+      <c r="C34" s="131">
         <v>6.99</v>
       </c>
-      <c r="D34" s="166"/>
-      <c r="E34" s="167" t="s">
+      <c r="D34" s="141"/>
+      <c r="E34" s="142" t="s">
         <v>117</v>
       </c>
-      <c r="F34" s="130"/>
-      <c r="G34" s="130"/>
-      <c r="H34" s="130"/>
-      <c r="I34" s="137"/>
-      <c r="J34" s="137"/>
-      <c r="K34" s="137"/>
-      <c r="L34" s="137"/>
-      <c r="M34" s="137"/>
-      <c r="N34" s="137"/>
-      <c r="O34" s="137"/>
-      <c r="P34" s="137"/>
-      <c r="Q34" s="137"/>
-      <c r="R34" s="137"/>
-      <c r="S34" s="137"/>
-      <c r="T34" s="137"/>
-      <c r="U34" s="137"/>
-      <c r="V34" s="137"/>
-      <c r="W34" s="137"/>
-      <c r="X34" s="137"/>
-      <c r="Y34" s="137"/>
-      <c r="Z34" s="137"/>
+      <c r="F34"/>
+      <c r="G34"/>
+      <c r="H34"/>
+      <c r="I34" s="113"/>
+      <c r="J34" s="113"/>
+      <c r="K34" s="113"/>
+      <c r="L34" s="113"/>
+      <c r="M34" s="113"/>
+      <c r="N34" s="113"/>
+      <c r="O34" s="113"/>
+      <c r="P34" s="113"/>
+      <c r="Q34" s="113"/>
+      <c r="R34" s="113"/>
+      <c r="S34" s="113"/>
+      <c r="T34" s="113"/>
+      <c r="U34" s="113"/>
+      <c r="V34" s="113"/>
+      <c r="W34" s="113"/>
+      <c r="X34" s="113"/>
+      <c r="Y34" s="113"/>
+      <c r="Z34" s="113"/>
     </row>
     <row r="35" spans="1:26" ht="17">
-      <c r="A35" s="159" t="s">
+      <c r="A35" s="134" t="s">
         <v>118</v>
       </c>
-      <c r="B35" s="155">
+      <c r="B35" s="130">
         <v>1</v>
       </c>
-      <c r="C35" s="156">
+      <c r="C35" s="131">
         <v>7.99</v>
       </c>
-      <c r="D35" s="159" t="s">
+      <c r="D35" s="134" t="s">
         <v>119</v>
       </c>
-      <c r="E35" s="167" t="s">
+      <c r="E35" s="142" t="s">
         <v>120</v>
       </c>
-      <c r="K35" s="137"/>
-      <c r="L35" s="137"/>
-      <c r="M35" s="137"/>
-      <c r="N35" s="137"/>
-      <c r="O35" s="137"/>
-      <c r="P35" s="137"/>
-      <c r="Q35" s="137"/>
-      <c r="R35" s="137"/>
-      <c r="S35" s="137"/>
-      <c r="T35" s="137"/>
-      <c r="U35" s="137"/>
-      <c r="V35" s="137"/>
-      <c r="W35" s="137"/>
-      <c r="X35" s="137"/>
-      <c r="Y35" s="137"/>
-      <c r="Z35" s="137"/>
+      <c r="K35" s="113"/>
+      <c r="L35" s="113"/>
+      <c r="M35" s="113"/>
+      <c r="N35" s="113"/>
+      <c r="O35" s="113"/>
+      <c r="P35" s="113"/>
+      <c r="Q35" s="113"/>
+      <c r="R35" s="113"/>
+      <c r="S35" s="113"/>
+      <c r="T35" s="113"/>
+      <c r="U35" s="113"/>
+      <c r="V35" s="113"/>
+      <c r="W35" s="113"/>
+      <c r="X35" s="113"/>
+      <c r="Y35" s="113"/>
+      <c r="Z35" s="113"/>
     </row>
     <row r="36" spans="1:26" ht="17">
-      <c r="A36" s="159" t="s">
+      <c r="A36" s="134" t="s">
         <v>121</v>
       </c>
-      <c r="B36" s="155">
+      <c r="B36" s="130">
         <v>1</v>
       </c>
-      <c r="C36" s="156">
+      <c r="C36" s="131">
         <v>7.99</v>
       </c>
-      <c r="D36" s="166"/>
-      <c r="E36" s="183" t="s">
+      <c r="D36" s="141"/>
+      <c r="E36" s="158" t="s">
         <v>122</v>
       </c>
-      <c r="F36" s="135"/>
-      <c r="H36" s="137"/>
-      <c r="I36" s="137"/>
-      <c r="J36" s="137"/>
-      <c r="K36" s="137"/>
-      <c r="L36" s="137"/>
-      <c r="M36" s="137"/>
-      <c r="N36" s="137"/>
-      <c r="O36" s="137"/>
-      <c r="P36" s="137"/>
-      <c r="Q36" s="137"/>
-      <c r="R36" s="137"/>
-      <c r="S36" s="137"/>
-      <c r="T36" s="137"/>
-      <c r="U36" s="137"/>
-      <c r="V36" s="137"/>
-      <c r="W36" s="137"/>
-      <c r="X36" s="137"/>
-      <c r="Y36" s="137"/>
-      <c r="Z36" s="137"/>
+      <c r="F36" s="111"/>
+      <c r="H36" s="113"/>
+      <c r="I36" s="113"/>
+      <c r="J36" s="113"/>
+      <c r="K36" s="113"/>
+      <c r="L36" s="113"/>
+      <c r="M36" s="113"/>
+      <c r="N36" s="113"/>
+      <c r="O36" s="113"/>
+      <c r="P36" s="113"/>
+      <c r="Q36" s="113"/>
+      <c r="R36" s="113"/>
+      <c r="S36" s="113"/>
+      <c r="T36" s="113"/>
+      <c r="U36" s="113"/>
+      <c r="V36" s="113"/>
+      <c r="W36" s="113"/>
+      <c r="X36" s="113"/>
+      <c r="Y36" s="113"/>
+      <c r="Z36" s="113"/>
     </row>
     <row r="37" spans="1:26" ht="34">
-      <c r="A37" s="184"/>
-      <c r="B37" s="185" t="s">
+      <c r="A37" s="159"/>
+      <c r="B37" s="160" t="s">
         <v>123</v>
       </c>
-      <c r="C37" s="186">
+      <c r="C37" s="161">
         <f>SUM(C4:C36)</f>
         <v>3022.2899999999981</v>
       </c>
-      <c r="D37" s="159" t="s">
+      <c r="D37" s="134" t="s">
         <v>124</v>
       </c>
-      <c r="E37" s="187"/>
+      <c r="E37" s="162"/>
       <c r="F37" s="4"/>
       <c r="G37" s="4"/>
       <c r="H37" s="4"/>
@@ -6269,11 +6310,11 @@
       <c r="K37" s="4"/>
     </row>
     <row r="38" spans="1:26" ht="16">
-      <c r="A38" s="142"/>
-      <c r="B38" s="133"/>
-      <c r="C38" s="134"/>
+      <c r="A38" s="118"/>
+      <c r="B38" s="109"/>
+      <c r="C38" s="110"/>
       <c r="D38" s="4"/>
-      <c r="E38" s="141"/>
+      <c r="E38" s="117"/>
       <c r="F38" s="4"/>
       <c r="G38" s="4"/>
       <c r="H38" s="4"/>
@@ -6282,15 +6323,15 @@
       <c r="K38" s="4"/>
     </row>
     <row r="39" spans="1:26" ht="17">
-      <c r="A39" s="140" t="s">
+      <c r="A39" s="116" t="s">
         <v>125</v>
       </c>
-      <c r="B39" s="99" t="s">
+      <c r="B39" s="183" t="s">
         <v>184</v>
       </c>
-      <c r="C39" s="99"/>
-      <c r="D39" s="99"/>
-      <c r="E39" s="143"/>
+      <c r="C39" s="183"/>
+      <c r="D39" s="183"/>
+      <c r="E39" s="119"/>
       <c r="F39" s="4"/>
       <c r="G39" s="4"/>
       <c r="H39" s="4"/>
@@ -6300,10 +6341,10 @@
     </row>
     <row r="40" spans="1:26" ht="16">
       <c r="A40" s="4"/>
-      <c r="B40" s="99"/>
-      <c r="C40" s="99"/>
-      <c r="D40" s="99"/>
-      <c r="E40" s="141"/>
+      <c r="B40" s="183"/>
+      <c r="C40" s="183"/>
+      <c r="D40" s="183"/>
+      <c r="E40" s="117"/>
       <c r="F40" s="4"/>
       <c r="G40" s="4"/>
       <c r="H40" s="4"/>
@@ -6312,16 +6353,16 @@
       <c r="K40" s="4"/>
     </row>
     <row r="41" spans="1:26">
-      <c r="B41" s="99"/>
-      <c r="C41" s="99"/>
-      <c r="D41" s="99"/>
+      <c r="B41" s="183"/>
+      <c r="C41" s="183"/>
+      <c r="D41" s="183"/>
     </row>
     <row r="65" spans="1:11" ht="16">
       <c r="A65" s="4"/>
-      <c r="B65" s="133"/>
-      <c r="C65" s="134"/>
+      <c r="B65" s="109"/>
+      <c r="C65" s="110"/>
       <c r="D65" s="4"/>
-      <c r="E65" s="141"/>
+      <c r="E65" s="117"/>
       <c r="F65" s="4"/>
       <c r="G65" s="4"/>
       <c r="H65" s="4"/>
@@ -6331,10 +6372,10 @@
     </row>
     <row r="66" spans="1:11" ht="16">
       <c r="A66" s="4"/>
-      <c r="B66" s="133"/>
-      <c r="C66" s="134"/>
+      <c r="B66" s="109"/>
+      <c r="C66" s="110"/>
       <c r="D66" s="4"/>
-      <c r="E66" s="141"/>
+      <c r="E66" s="117"/>
       <c r="F66" s="4"/>
       <c r="G66" s="4"/>
       <c r="H66" s="4"/>
@@ -6344,10 +6385,10 @@
     </row>
     <row r="67" spans="1:11" ht="16">
       <c r="A67" s="4"/>
-      <c r="B67" s="133"/>
-      <c r="C67" s="134"/>
+      <c r="B67" s="109"/>
+      <c r="C67" s="110"/>
       <c r="D67" s="4"/>
-      <c r="E67" s="141"/>
+      <c r="E67" s="117"/>
       <c r="F67" s="4"/>
       <c r="G67" s="4"/>
       <c r="H67" s="4"/>
@@ -6357,10 +6398,10 @@
     </row>
     <row r="68" spans="1:11" ht="16">
       <c r="A68" s="4"/>
-      <c r="B68" s="133"/>
-      <c r="C68" s="134"/>
+      <c r="B68" s="109"/>
+      <c r="C68" s="110"/>
       <c r="D68" s="4"/>
-      <c r="E68" s="141"/>
+      <c r="E68" s="117"/>
       <c r="F68" s="4"/>
       <c r="G68" s="4"/>
       <c r="H68" s="4"/>
@@ -6370,10 +6411,10 @@
     </row>
     <row r="69" spans="1:11" ht="16">
       <c r="A69" s="4"/>
-      <c r="B69" s="133"/>
-      <c r="C69" s="134"/>
+      <c r="B69" s="109"/>
+      <c r="C69" s="110"/>
       <c r="D69" s="4"/>
-      <c r="E69" s="141"/>
+      <c r="E69" s="117"/>
       <c r="F69" s="4"/>
       <c r="G69" s="4"/>
       <c r="H69" s="4"/>
@@ -6383,10 +6424,10 @@
     </row>
     <row r="70" spans="1:11" ht="16">
       <c r="A70" s="4"/>
-      <c r="B70" s="133"/>
-      <c r="C70" s="134"/>
+      <c r="B70" s="109"/>
+      <c r="C70" s="110"/>
       <c r="D70" s="4"/>
-      <c r="E70" s="141"/>
+      <c r="E70" s="117"/>
       <c r="F70" s="4"/>
       <c r="G70" s="4"/>
       <c r="H70" s="4"/>
@@ -6396,10 +6437,10 @@
     </row>
     <row r="71" spans="1:11" ht="16">
       <c r="A71" s="4"/>
-      <c r="B71" s="133"/>
-      <c r="C71" s="134"/>
+      <c r="B71" s="109"/>
+      <c r="C71" s="110"/>
       <c r="D71" s="4"/>
-      <c r="E71" s="141"/>
+      <c r="E71" s="117"/>
       <c r="F71" s="4"/>
       <c r="G71" s="4"/>
       <c r="H71" s="4"/>
@@ -6409,10 +6450,10 @@
     </row>
     <row r="72" spans="1:11" ht="16">
       <c r="A72" s="4"/>
-      <c r="B72" s="133"/>
-      <c r="C72" s="134"/>
+      <c r="B72" s="109"/>
+      <c r="C72" s="110"/>
       <c r="D72" s="4"/>
-      <c r="E72" s="141"/>
+      <c r="E72" s="117"/>
       <c r="F72" s="4"/>
       <c r="G72" s="4"/>
       <c r="H72" s="4"/>
@@ -6422,10 +6463,10 @@
     </row>
     <row r="73" spans="1:11" ht="16">
       <c r="A73" s="4"/>
-      <c r="B73" s="133"/>
-      <c r="C73" s="134"/>
+      <c r="B73" s="109"/>
+      <c r="C73" s="110"/>
       <c r="D73" s="4"/>
-      <c r="E73" s="141"/>
+      <c r="E73" s="117"/>
       <c r="F73" s="4"/>
       <c r="G73" s="4"/>
       <c r="H73" s="4"/>
@@ -6435,10 +6476,10 @@
     </row>
     <row r="74" spans="1:11" ht="16">
       <c r="A74" s="4"/>
-      <c r="B74" s="133"/>
-      <c r="C74" s="134"/>
+      <c r="B74" s="109"/>
+      <c r="C74" s="110"/>
       <c r="D74" s="4"/>
-      <c r="E74" s="141"/>
+      <c r="E74" s="117"/>
       <c r="F74" s="4"/>
       <c r="G74" s="4"/>
       <c r="H74" s="4"/>
@@ -6448,10 +6489,10 @@
     </row>
     <row r="75" spans="1:11" ht="16">
       <c r="A75" s="4"/>
-      <c r="B75" s="133"/>
-      <c r="C75" s="134"/>
+      <c r="B75" s="109"/>
+      <c r="C75" s="110"/>
       <c r="D75" s="4"/>
-      <c r="E75" s="141"/>
+      <c r="E75" s="117"/>
       <c r="F75" s="4"/>
       <c r="G75" s="4"/>
       <c r="H75" s="4"/>
@@ -6461,10 +6502,10 @@
     </row>
     <row r="76" spans="1:11" ht="16">
       <c r="A76" s="4"/>
-      <c r="B76" s="133"/>
-      <c r="C76" s="134"/>
+      <c r="B76" s="109"/>
+      <c r="C76" s="110"/>
       <c r="D76" s="4"/>
-      <c r="E76" s="141"/>
+      <c r="E76" s="117"/>
       <c r="F76" s="4"/>
       <c r="G76" s="4"/>
       <c r="H76" s="4"/>
@@ -6474,10 +6515,10 @@
     </row>
     <row r="77" spans="1:11" ht="16">
       <c r="A77" s="4"/>
-      <c r="B77" s="133"/>
-      <c r="C77" s="134"/>
+      <c r="B77" s="109"/>
+      <c r="C77" s="110"/>
       <c r="D77" s="4"/>
-      <c r="E77" s="141"/>
+      <c r="E77" s="117"/>
       <c r="F77" s="4"/>
       <c r="G77" s="4"/>
       <c r="H77" s="4"/>
@@ -6487,10 +6528,10 @@
     </row>
     <row r="78" spans="1:11" ht="16">
       <c r="A78" s="4"/>
-      <c r="B78" s="133"/>
-      <c r="C78" s="134"/>
+      <c r="B78" s="109"/>
+      <c r="C78" s="110"/>
       <c r="D78" s="4"/>
-      <c r="E78" s="141"/>
+      <c r="E78" s="117"/>
       <c r="F78" s="4"/>
       <c r="G78" s="4"/>
       <c r="H78" s="4"/>
@@ -6500,10 +6541,10 @@
     </row>
     <row r="79" spans="1:11" ht="16">
       <c r="A79" s="4"/>
-      <c r="B79" s="133"/>
-      <c r="C79" s="134"/>
+      <c r="B79" s="109"/>
+      <c r="C79" s="110"/>
       <c r="D79" s="4"/>
-      <c r="E79" s="141"/>
+      <c r="E79" s="117"/>
       <c r="F79" s="4"/>
       <c r="G79" s="4"/>
       <c r="H79" s="4"/>
@@ -6513,10 +6554,10 @@
     </row>
     <row r="80" spans="1:11" ht="16">
       <c r="A80" s="4"/>
-      <c r="B80" s="133"/>
-      <c r="C80" s="134"/>
+      <c r="B80" s="109"/>
+      <c r="C80" s="110"/>
       <c r="D80" s="4"/>
-      <c r="E80" s="141"/>
+      <c r="E80" s="117"/>
       <c r="F80" s="4"/>
       <c r="G80" s="4"/>
       <c r="H80" s="4"/>
@@ -6526,10 +6567,10 @@
     </row>
     <row r="81" spans="1:11" ht="16">
       <c r="A81" s="4"/>
-      <c r="B81" s="133"/>
-      <c r="C81" s="134"/>
+      <c r="B81" s="109"/>
+      <c r="C81" s="110"/>
       <c r="D81" s="4"/>
-      <c r="E81" s="141"/>
+      <c r="E81" s="117"/>
       <c r="F81" s="4"/>
       <c r="G81" s="4"/>
       <c r="H81" s="4"/>
@@ -6539,10 +6580,10 @@
     </row>
     <row r="82" spans="1:11" ht="16">
       <c r="A82" s="4"/>
-      <c r="B82" s="133"/>
-      <c r="C82" s="134"/>
+      <c r="B82" s="109"/>
+      <c r="C82" s="110"/>
       <c r="D82" s="4"/>
-      <c r="E82" s="141"/>
+      <c r="E82" s="117"/>
       <c r="F82" s="4"/>
       <c r="G82" s="4"/>
       <c r="H82" s="4"/>
@@ -6552,10 +6593,10 @@
     </row>
     <row r="83" spans="1:11" ht="16">
       <c r="A83" s="4"/>
-      <c r="B83" s="133"/>
-      <c r="C83" s="134"/>
+      <c r="B83" s="109"/>
+      <c r="C83" s="110"/>
       <c r="D83" s="4"/>
-      <c r="E83" s="141"/>
+      <c r="E83" s="117"/>
       <c r="F83" s="4"/>
       <c r="G83" s="4"/>
       <c r="H83" s="4"/>
@@ -6565,10 +6606,10 @@
     </row>
     <row r="84" spans="1:11" ht="16">
       <c r="A84" s="4"/>
-      <c r="B84" s="133"/>
-      <c r="C84" s="134"/>
+      <c r="B84" s="109"/>
+      <c r="C84" s="110"/>
       <c r="D84" s="4"/>
-      <c r="E84" s="145"/>
+      <c r="E84" s="121"/>
       <c r="F84" s="4"/>
       <c r="G84" s="4"/>
       <c r="H84" s="4"/>
@@ -6578,10 +6619,10 @@
     </row>
     <row r="85" spans="1:11" ht="16">
       <c r="A85" s="4"/>
-      <c r="B85" s="133"/>
-      <c r="C85" s="134"/>
+      <c r="B85" s="109"/>
+      <c r="C85" s="110"/>
       <c r="D85" s="4"/>
-      <c r="E85" s="145"/>
+      <c r="E85" s="121"/>
       <c r="F85" s="4"/>
       <c r="G85" s="4"/>
       <c r="H85" s="4"/>
@@ -6591,10 +6632,10 @@
     </row>
     <row r="86" spans="1:11" ht="16">
       <c r="A86" s="4"/>
-      <c r="B86" s="133"/>
-      <c r="C86" s="134"/>
+      <c r="B86" s="109"/>
+      <c r="C86" s="110"/>
       <c r="D86" s="4"/>
-      <c r="E86" s="145"/>
+      <c r="E86" s="121"/>
       <c r="F86" s="4"/>
       <c r="G86" s="4"/>
       <c r="H86" s="4"/>
@@ -6604,10 +6645,10 @@
     </row>
     <row r="87" spans="1:11" ht="16">
       <c r="A87" s="4"/>
-      <c r="B87" s="133"/>
-      <c r="C87" s="134"/>
+      <c r="B87" s="109"/>
+      <c r="C87" s="110"/>
       <c r="D87" s="4"/>
-      <c r="E87" s="145"/>
+      <c r="E87" s="121"/>
       <c r="F87" s="4"/>
       <c r="G87" s="4"/>
       <c r="H87" s="4"/>
@@ -6617,10 +6658,10 @@
     </row>
     <row r="88" spans="1:11" ht="16">
       <c r="A88" s="4"/>
-      <c r="B88" s="133"/>
-      <c r="C88" s="134"/>
+      <c r="B88" s="109"/>
+      <c r="C88" s="110"/>
       <c r="D88" s="4"/>
-      <c r="E88" s="145"/>
+      <c r="E88" s="121"/>
       <c r="F88" s="4"/>
       <c r="G88" s="4"/>
       <c r="H88" s="4"/>
@@ -6630,10 +6671,10 @@
     </row>
     <row r="89" spans="1:11" ht="16">
       <c r="A89" s="4"/>
-      <c r="B89" s="133"/>
-      <c r="C89" s="134"/>
+      <c r="B89" s="109"/>
+      <c r="C89" s="110"/>
       <c r="D89" s="4"/>
-      <c r="E89" s="145"/>
+      <c r="E89" s="121"/>
       <c r="F89" s="4"/>
       <c r="G89" s="4"/>
       <c r="H89" s="4"/>
@@ -6643,10 +6684,10 @@
     </row>
     <row r="90" spans="1:11" ht="16">
       <c r="A90" s="4"/>
-      <c r="B90" s="133"/>
-      <c r="C90" s="134"/>
+      <c r="B90" s="109"/>
+      <c r="C90" s="110"/>
       <c r="D90" s="4"/>
-      <c r="E90" s="145"/>
+      <c r="E90" s="121"/>
       <c r="F90" s="4"/>
       <c r="G90" s="4"/>
       <c r="H90" s="4"/>
@@ -6656,10 +6697,10 @@
     </row>
     <row r="91" spans="1:11" ht="16">
       <c r="A91" s="4"/>
-      <c r="B91" s="133"/>
-      <c r="C91" s="134"/>
+      <c r="B91" s="109"/>
+      <c r="C91" s="110"/>
       <c r="D91" s="4"/>
-      <c r="E91" s="145"/>
+      <c r="E91" s="121"/>
       <c r="F91" s="4"/>
       <c r="G91" s="4"/>
       <c r="H91" s="4"/>
@@ -6669,10 +6710,10 @@
     </row>
     <row r="92" spans="1:11" ht="16">
       <c r="A92" s="4"/>
-      <c r="B92" s="133"/>
-      <c r="C92" s="134"/>
+      <c r="B92" s="109"/>
+      <c r="C92" s="110"/>
       <c r="D92" s="4"/>
-      <c r="E92" s="145"/>
+      <c r="E92" s="121"/>
       <c r="F92" s="4"/>
       <c r="G92" s="4"/>
       <c r="H92" s="4"/>
@@ -6682,10 +6723,10 @@
     </row>
     <row r="93" spans="1:11" ht="16">
       <c r="A93" s="4"/>
-      <c r="B93" s="133"/>
-      <c r="C93" s="134"/>
+      <c r="B93" s="109"/>
+      <c r="C93" s="110"/>
       <c r="D93" s="4"/>
-      <c r="E93" s="145"/>
+      <c r="E93" s="121"/>
       <c r="F93" s="4"/>
       <c r="G93" s="4"/>
       <c r="H93" s="4"/>
@@ -6695,10 +6736,10 @@
     </row>
     <row r="94" spans="1:11" ht="16">
       <c r="A94" s="4"/>
-      <c r="B94" s="133"/>
-      <c r="C94" s="134"/>
+      <c r="B94" s="109"/>
+      <c r="C94" s="110"/>
       <c r="D94" s="4"/>
-      <c r="E94" s="145"/>
+      <c r="E94" s="121"/>
       <c r="F94" s="4"/>
       <c r="G94" s="4"/>
       <c r="H94" s="4"/>
@@ -6708,10 +6749,10 @@
     </row>
     <row r="95" spans="1:11" ht="16">
       <c r="A95" s="4"/>
-      <c r="B95" s="133"/>
-      <c r="C95" s="134"/>
+      <c r="B95" s="109"/>
+      <c r="C95" s="110"/>
       <c r="D95" s="4"/>
-      <c r="E95" s="145"/>
+      <c r="E95" s="121"/>
       <c r="F95" s="4"/>
       <c r="G95" s="4"/>
       <c r="H95" s="4"/>
@@ -6721,10 +6762,10 @@
     </row>
     <row r="96" spans="1:11" ht="16">
       <c r="A96" s="4"/>
-      <c r="B96" s="133"/>
-      <c r="C96" s="134"/>
+      <c r="B96" s="109"/>
+      <c r="C96" s="110"/>
       <c r="D96" s="4"/>
-      <c r="E96" s="145"/>
+      <c r="E96" s="121"/>
       <c r="F96" s="4"/>
       <c r="G96" s="4"/>
       <c r="H96" s="4"/>
@@ -6734,10 +6775,10 @@
     </row>
     <row r="97" spans="1:11" ht="16">
       <c r="A97" s="4"/>
-      <c r="B97" s="133"/>
-      <c r="C97" s="134"/>
+      <c r="B97" s="109"/>
+      <c r="C97" s="110"/>
       <c r="D97" s="4"/>
-      <c r="E97" s="145"/>
+      <c r="E97" s="121"/>
       <c r="F97" s="4"/>
       <c r="G97" s="4"/>
       <c r="H97" s="4"/>
@@ -6747,10 +6788,10 @@
     </row>
     <row r="98" spans="1:11" ht="16">
       <c r="A98" s="4"/>
-      <c r="B98" s="133"/>
-      <c r="C98" s="134"/>
+      <c r="B98" s="109"/>
+      <c r="C98" s="110"/>
       <c r="D98" s="4"/>
-      <c r="E98" s="145"/>
+      <c r="E98" s="121"/>
       <c r="F98" s="4"/>
       <c r="G98" s="4"/>
       <c r="H98" s="4"/>
@@ -6760,10 +6801,10 @@
     </row>
     <row r="99" spans="1:11" ht="16">
       <c r="A99" s="4"/>
-      <c r="B99" s="133"/>
-      <c r="C99" s="134"/>
+      <c r="B99" s="109"/>
+      <c r="C99" s="110"/>
       <c r="D99" s="4"/>
-      <c r="E99" s="145"/>
+      <c r="E99" s="121"/>
       <c r="F99" s="4"/>
       <c r="G99" s="4"/>
       <c r="H99" s="4"/>
@@ -6773,10 +6814,10 @@
     </row>
     <row r="100" spans="1:11" ht="16">
       <c r="A100" s="4"/>
-      <c r="B100" s="133"/>
-      <c r="C100" s="134"/>
+      <c r="B100" s="109"/>
+      <c r="C100" s="110"/>
       <c r="D100" s="4"/>
-      <c r="E100" s="145"/>
+      <c r="E100" s="121"/>
       <c r="F100" s="4"/>
       <c r="G100" s="4"/>
       <c r="H100" s="4"/>
@@ -6786,10 +6827,10 @@
     </row>
     <row r="101" spans="1:11" ht="16">
       <c r="A101" s="4"/>
-      <c r="B101" s="133"/>
-      <c r="C101" s="134"/>
+      <c r="B101" s="109"/>
+      <c r="C101" s="110"/>
       <c r="D101" s="4"/>
-      <c r="E101" s="145"/>
+      <c r="E101" s="121"/>
       <c r="F101" s="4"/>
       <c r="G101" s="4"/>
       <c r="H101" s="4"/>
@@ -6799,10 +6840,10 @@
     </row>
     <row r="102" spans="1:11" ht="16">
       <c r="A102" s="4"/>
-      <c r="B102" s="133"/>
-      <c r="C102" s="134"/>
+      <c r="B102" s="109"/>
+      <c r="C102" s="110"/>
       <c r="D102" s="4"/>
-      <c r="E102" s="145"/>
+      <c r="E102" s="121"/>
       <c r="F102" s="4"/>
       <c r="G102" s="4"/>
       <c r="H102" s="4"/>
@@ -6812,10 +6853,10 @@
     </row>
     <row r="103" spans="1:11" ht="16">
       <c r="A103" s="4"/>
-      <c r="B103" s="133"/>
-      <c r="C103" s="134"/>
+      <c r="B103" s="109"/>
+      <c r="C103" s="110"/>
       <c r="D103" s="4"/>
-      <c r="E103" s="145"/>
+      <c r="E103" s="121"/>
       <c r="F103" s="4"/>
       <c r="G103" s="4"/>
       <c r="H103" s="4"/>
@@ -6825,10 +6866,10 @@
     </row>
     <row r="104" spans="1:11" ht="16">
       <c r="A104" s="4"/>
-      <c r="B104" s="133"/>
-      <c r="C104" s="134"/>
+      <c r="B104" s="109"/>
+      <c r="C104" s="110"/>
       <c r="D104" s="4"/>
-      <c r="E104" s="145"/>
+      <c r="E104" s="121"/>
       <c r="F104" s="4"/>
       <c r="G104" s="4"/>
       <c r="H104" s="4"/>
@@ -6838,10 +6879,10 @@
     </row>
     <row r="105" spans="1:11" ht="16">
       <c r="A105" s="4"/>
-      <c r="B105" s="133"/>
-      <c r="C105" s="134"/>
+      <c r="B105" s="109"/>
+      <c r="C105" s="110"/>
       <c r="D105" s="4"/>
-      <c r="E105" s="145"/>
+      <c r="E105" s="121"/>
       <c r="F105" s="4"/>
       <c r="G105" s="4"/>
       <c r="H105" s="4"/>
@@ -6851,10 +6892,10 @@
     </row>
     <row r="106" spans="1:11" ht="16">
       <c r="A106" s="4"/>
-      <c r="B106" s="133"/>
-      <c r="C106" s="134"/>
+      <c r="B106" s="109"/>
+      <c r="C106" s="110"/>
       <c r="D106" s="4"/>
-      <c r="E106" s="145"/>
+      <c r="E106" s="121"/>
       <c r="F106" s="4"/>
       <c r="G106" s="4"/>
       <c r="H106" s="4"/>
@@ -6864,10 +6905,10 @@
     </row>
     <row r="107" spans="1:11" ht="16">
       <c r="A107" s="4"/>
-      <c r="B107" s="133"/>
-      <c r="C107" s="134"/>
+      <c r="B107" s="109"/>
+      <c r="C107" s="110"/>
       <c r="D107" s="4"/>
-      <c r="E107" s="145"/>
+      <c r="E107" s="121"/>
       <c r="F107" s="4"/>
       <c r="G107" s="4"/>
       <c r="H107" s="4"/>
@@ -6877,10 +6918,10 @@
     </row>
     <row r="108" spans="1:11" ht="16">
       <c r="A108" s="4"/>
-      <c r="B108" s="133"/>
-      <c r="C108" s="134"/>
+      <c r="B108" s="109"/>
+      <c r="C108" s="110"/>
       <c r="D108" s="4"/>
-      <c r="E108" s="145"/>
+      <c r="E108" s="121"/>
       <c r="F108" s="4"/>
       <c r="G108" s="4"/>
       <c r="H108" s="4"/>
@@ -6890,10 +6931,10 @@
     </row>
     <row r="109" spans="1:11" ht="16">
       <c r="A109" s="4"/>
-      <c r="B109" s="133"/>
-      <c r="C109" s="134"/>
+      <c r="B109" s="109"/>
+      <c r="C109" s="110"/>
       <c r="D109" s="4"/>
-      <c r="E109" s="145"/>
+      <c r="E109" s="121"/>
       <c r="F109" s="4"/>
       <c r="G109" s="4"/>
       <c r="H109" s="4"/>
@@ -6903,10 +6944,10 @@
     </row>
     <row r="110" spans="1:11" ht="16">
       <c r="A110" s="4"/>
-      <c r="B110" s="133"/>
-      <c r="C110" s="134"/>
+      <c r="B110" s="109"/>
+      <c r="C110" s="110"/>
       <c r="D110" s="4"/>
-      <c r="E110" s="145"/>
+      <c r="E110" s="121"/>
       <c r="F110" s="4"/>
       <c r="G110" s="4"/>
       <c r="H110" s="4"/>
@@ -6916,10 +6957,10 @@
     </row>
     <row r="111" spans="1:11" ht="16">
       <c r="A111" s="4"/>
-      <c r="B111" s="133"/>
-      <c r="C111" s="134"/>
+      <c r="B111" s="109"/>
+      <c r="C111" s="110"/>
       <c r="D111" s="4"/>
-      <c r="E111" s="145"/>
+      <c r="E111" s="121"/>
       <c r="F111" s="4"/>
       <c r="G111" s="4"/>
       <c r="H111" s="4"/>
@@ -6929,10 +6970,10 @@
     </row>
     <row r="112" spans="1:11" ht="16">
       <c r="A112" s="4"/>
-      <c r="B112" s="133"/>
-      <c r="C112" s="134"/>
+      <c r="B112" s="109"/>
+      <c r="C112" s="110"/>
       <c r="D112" s="4"/>
-      <c r="E112" s="145"/>
+      <c r="E112" s="121"/>
       <c r="F112" s="4"/>
       <c r="G112" s="4"/>
       <c r="H112" s="4"/>
@@ -6942,10 +6983,10 @@
     </row>
     <row r="113" spans="1:11" ht="16">
       <c r="A113" s="4"/>
-      <c r="B113" s="133"/>
-      <c r="C113" s="134"/>
+      <c r="B113" s="109"/>
+      <c r="C113" s="110"/>
       <c r="D113" s="4"/>
-      <c r="E113" s="145"/>
+      <c r="E113" s="121"/>
       <c r="F113" s="4"/>
       <c r="G113" s="4"/>
       <c r="H113" s="4"/>
@@ -6955,10 +6996,10 @@
     </row>
     <row r="114" spans="1:11" ht="16">
       <c r="A114" s="4"/>
-      <c r="B114" s="133"/>
-      <c r="C114" s="134"/>
+      <c r="B114" s="109"/>
+      <c r="C114" s="110"/>
       <c r="D114" s="4"/>
-      <c r="E114" s="145"/>
+      <c r="E114" s="121"/>
       <c r="F114" s="4"/>
       <c r="G114" s="4"/>
       <c r="H114" s="4"/>
@@ -6968,10 +7009,10 @@
     </row>
     <row r="115" spans="1:11" ht="16">
       <c r="A115" s="4"/>
-      <c r="B115" s="133"/>
-      <c r="C115" s="134"/>
+      <c r="B115" s="109"/>
+      <c r="C115" s="110"/>
       <c r="D115" s="4"/>
-      <c r="E115" s="145"/>
+      <c r="E115" s="121"/>
       <c r="F115" s="4"/>
       <c r="G115" s="4"/>
       <c r="H115" s="4"/>
@@ -6981,10 +7022,10 @@
     </row>
     <row r="116" spans="1:11" ht="16">
       <c r="A116" s="4"/>
-      <c r="B116" s="133"/>
-      <c r="C116" s="134"/>
+      <c r="B116" s="109"/>
+      <c r="C116" s="110"/>
       <c r="D116" s="4"/>
-      <c r="E116" s="145"/>
+      <c r="E116" s="121"/>
       <c r="F116" s="4"/>
       <c r="G116" s="4"/>
       <c r="H116" s="4"/>
@@ -6994,10 +7035,10 @@
     </row>
     <row r="117" spans="1:11" ht="16">
       <c r="A117" s="4"/>
-      <c r="B117" s="133"/>
-      <c r="C117" s="134"/>
+      <c r="B117" s="109"/>
+      <c r="C117" s="110"/>
       <c r="D117" s="4"/>
-      <c r="E117" s="145"/>
+      <c r="E117" s="121"/>
       <c r="F117" s="4"/>
       <c r="G117" s="4"/>
       <c r="H117" s="4"/>
@@ -7007,10 +7048,10 @@
     </row>
     <row r="118" spans="1:11" ht="16">
       <c r="A118" s="4"/>
-      <c r="B118" s="133"/>
-      <c r="C118" s="134"/>
+      <c r="B118" s="109"/>
+      <c r="C118" s="110"/>
       <c r="D118" s="4"/>
-      <c r="E118" s="145"/>
+      <c r="E118" s="121"/>
       <c r="F118" s="4"/>
       <c r="G118" s="4"/>
       <c r="H118" s="4"/>
@@ -7020,10 +7061,10 @@
     </row>
     <row r="119" spans="1:11" ht="16">
       <c r="A119" s="4"/>
-      <c r="B119" s="133"/>
-      <c r="C119" s="134"/>
+      <c r="B119" s="109"/>
+      <c r="C119" s="110"/>
       <c r="D119" s="4"/>
-      <c r="E119" s="145"/>
+      <c r="E119" s="121"/>
       <c r="F119" s="4"/>
       <c r="G119" s="4"/>
       <c r="H119" s="4"/>
@@ -7033,10 +7074,10 @@
     </row>
     <row r="120" spans="1:11" ht="16">
       <c r="A120" s="4"/>
-      <c r="B120" s="133"/>
-      <c r="C120" s="134"/>
+      <c r="B120" s="109"/>
+      <c r="C120" s="110"/>
       <c r="D120" s="4"/>
-      <c r="E120" s="145"/>
+      <c r="E120" s="121"/>
       <c r="F120" s="4"/>
       <c r="G120" s="4"/>
       <c r="H120" s="4"/>
@@ -7046,10 +7087,10 @@
     </row>
     <row r="121" spans="1:11" ht="16">
       <c r="A121" s="4"/>
-      <c r="B121" s="133"/>
-      <c r="C121" s="134"/>
+      <c r="B121" s="109"/>
+      <c r="C121" s="110"/>
       <c r="D121" s="4"/>
-      <c r="E121" s="145"/>
+      <c r="E121" s="121"/>
       <c r="F121" s="4"/>
       <c r="G121" s="4"/>
       <c r="H121" s="4"/>
@@ -7059,10 +7100,10 @@
     </row>
     <row r="122" spans="1:11" ht="16">
       <c r="A122" s="4"/>
-      <c r="B122" s="133"/>
-      <c r="C122" s="134"/>
+      <c r="B122" s="109"/>
+      <c r="C122" s="110"/>
       <c r="D122" s="4"/>
-      <c r="E122" s="145"/>
+      <c r="E122" s="121"/>
       <c r="F122" s="4"/>
       <c r="G122" s="4"/>
       <c r="H122" s="4"/>
@@ -7072,10 +7113,10 @@
     </row>
     <row r="123" spans="1:11" ht="16">
       <c r="A123" s="4"/>
-      <c r="B123" s="133"/>
-      <c r="C123" s="134"/>
+      <c r="B123" s="109"/>
+      <c r="C123" s="110"/>
       <c r="D123" s="4"/>
-      <c r="E123" s="145"/>
+      <c r="E123" s="121"/>
       <c r="F123" s="4"/>
       <c r="G123" s="4"/>
       <c r="H123" s="4"/>
@@ -7085,10 +7126,10 @@
     </row>
     <row r="124" spans="1:11" ht="16">
       <c r="A124" s="4"/>
-      <c r="B124" s="133"/>
-      <c r="C124" s="134"/>
+      <c r="B124" s="109"/>
+      <c r="C124" s="110"/>
       <c r="D124" s="4"/>
-      <c r="E124" s="145"/>
+      <c r="E124" s="121"/>
       <c r="F124" s="4"/>
       <c r="G124" s="4"/>
       <c r="H124" s="4"/>
@@ -7098,10 +7139,10 @@
     </row>
     <row r="125" spans="1:11" ht="16">
       <c r="A125" s="4"/>
-      <c r="B125" s="133"/>
-      <c r="C125" s="134"/>
+      <c r="B125" s="109"/>
+      <c r="C125" s="110"/>
       <c r="D125" s="4"/>
-      <c r="E125" s="145"/>
+      <c r="E125" s="121"/>
       <c r="F125" s="4"/>
       <c r="G125" s="4"/>
       <c r="H125" s="4"/>
@@ -7111,10 +7152,10 @@
     </row>
     <row r="126" spans="1:11" ht="16">
       <c r="A126" s="4"/>
-      <c r="B126" s="133"/>
-      <c r="C126" s="134"/>
+      <c r="B126" s="109"/>
+      <c r="C126" s="110"/>
       <c r="D126" s="4"/>
-      <c r="E126" s="145"/>
+      <c r="E126" s="121"/>
       <c r="F126" s="4"/>
       <c r="G126" s="4"/>
       <c r="H126" s="4"/>
@@ -7124,10 +7165,10 @@
     </row>
     <row r="127" spans="1:11" ht="16">
       <c r="A127" s="4"/>
-      <c r="B127" s="133"/>
-      <c r="C127" s="134"/>
+      <c r="B127" s="109"/>
+      <c r="C127" s="110"/>
       <c r="D127" s="4"/>
-      <c r="E127" s="145"/>
+      <c r="E127" s="121"/>
       <c r="F127" s="4"/>
       <c r="G127" s="4"/>
       <c r="H127" s="4"/>
@@ -7137,10 +7178,10 @@
     </row>
     <row r="128" spans="1:11" ht="16">
       <c r="A128" s="4"/>
-      <c r="B128" s="133"/>
-      <c r="C128" s="134"/>
+      <c r="B128" s="109"/>
+      <c r="C128" s="110"/>
       <c r="D128" s="4"/>
-      <c r="E128" s="145"/>
+      <c r="E128" s="121"/>
       <c r="F128" s="4"/>
       <c r="G128" s="4"/>
       <c r="H128" s="4"/>
@@ -7150,10 +7191,10 @@
     </row>
     <row r="129" spans="1:11" ht="16">
       <c r="A129" s="4"/>
-      <c r="B129" s="133"/>
-      <c r="C129" s="134"/>
+      <c r="B129" s="109"/>
+      <c r="C129" s="110"/>
       <c r="D129" s="4"/>
-      <c r="E129" s="145"/>
+      <c r="E129" s="121"/>
       <c r="F129" s="4"/>
       <c r="G129" s="4"/>
       <c r="H129" s="4"/>
@@ -7163,10 +7204,10 @@
     </row>
     <row r="130" spans="1:11" ht="16">
       <c r="A130" s="4"/>
-      <c r="B130" s="133"/>
-      <c r="C130" s="134"/>
+      <c r="B130" s="109"/>
+      <c r="C130" s="110"/>
       <c r="D130" s="4"/>
-      <c r="E130" s="145"/>
+      <c r="E130" s="121"/>
       <c r="F130" s="4"/>
       <c r="G130" s="4"/>
       <c r="H130" s="4"/>
@@ -7176,10 +7217,10 @@
     </row>
     <row r="131" spans="1:11" ht="16">
       <c r="A131" s="4"/>
-      <c r="B131" s="133"/>
-      <c r="C131" s="134"/>
+      <c r="B131" s="109"/>
+      <c r="C131" s="110"/>
       <c r="D131" s="4"/>
-      <c r="E131" s="145"/>
+      <c r="E131" s="121"/>
       <c r="F131" s="4"/>
       <c r="G131" s="4"/>
       <c r="H131" s="4"/>
@@ -7189,10 +7230,10 @@
     </row>
     <row r="132" spans="1:11" ht="16">
       <c r="A132" s="4"/>
-      <c r="B132" s="133"/>
-      <c r="C132" s="134"/>
+      <c r="B132" s="109"/>
+      <c r="C132" s="110"/>
       <c r="D132" s="4"/>
-      <c r="E132" s="145"/>
+      <c r="E132" s="121"/>
       <c r="F132" s="4"/>
       <c r="G132" s="4"/>
       <c r="H132" s="4"/>
@@ -7202,10 +7243,10 @@
     </row>
     <row r="133" spans="1:11" ht="16">
       <c r="A133" s="4"/>
-      <c r="B133" s="133"/>
-      <c r="C133" s="134"/>
+      <c r="B133" s="109"/>
+      <c r="C133" s="110"/>
       <c r="D133" s="4"/>
-      <c r="E133" s="145"/>
+      <c r="E133" s="121"/>
       <c r="F133" s="4"/>
       <c r="G133" s="4"/>
       <c r="H133" s="4"/>
@@ -7215,10 +7256,10 @@
     </row>
     <row r="134" spans="1:11" ht="16">
       <c r="A134" s="4"/>
-      <c r="B134" s="133"/>
-      <c r="C134" s="134"/>
+      <c r="B134" s="109"/>
+      <c r="C134" s="110"/>
       <c r="D134" s="4"/>
-      <c r="E134" s="145"/>
+      <c r="E134" s="121"/>
       <c r="F134" s="4"/>
       <c r="G134" s="4"/>
       <c r="H134" s="4"/>
@@ -7228,10 +7269,10 @@
     </row>
     <row r="135" spans="1:11" ht="16">
       <c r="A135" s="4"/>
-      <c r="B135" s="133"/>
-      <c r="C135" s="134"/>
+      <c r="B135" s="109"/>
+      <c r="C135" s="110"/>
       <c r="D135" s="4"/>
-      <c r="E135" s="145"/>
+      <c r="E135" s="121"/>
       <c r="F135" s="4"/>
       <c r="G135" s="4"/>
       <c r="H135" s="4"/>
@@ -7241,10 +7282,10 @@
     </row>
     <row r="136" spans="1:11" ht="16">
       <c r="A136" s="4"/>
-      <c r="B136" s="133"/>
-      <c r="C136" s="134"/>
+      <c r="B136" s="109"/>
+      <c r="C136" s="110"/>
       <c r="D136" s="4"/>
-      <c r="E136" s="145"/>
+      <c r="E136" s="121"/>
       <c r="F136" s="4"/>
       <c r="G136" s="4"/>
       <c r="H136" s="4"/>
@@ -7254,10 +7295,10 @@
     </row>
     <row r="137" spans="1:11" ht="16">
       <c r="A137" s="4"/>
-      <c r="B137" s="133"/>
-      <c r="C137" s="134"/>
+      <c r="B137" s="109"/>
+      <c r="C137" s="110"/>
       <c r="D137" s="4"/>
-      <c r="E137" s="145"/>
+      <c r="E137" s="121"/>
       <c r="F137" s="4"/>
       <c r="G137" s="4"/>
       <c r="H137" s="4"/>
@@ -7267,10 +7308,10 @@
     </row>
     <row r="138" spans="1:11" ht="16">
       <c r="A138" s="4"/>
-      <c r="B138" s="133"/>
-      <c r="C138" s="134"/>
+      <c r="B138" s="109"/>
+      <c r="C138" s="110"/>
       <c r="D138" s="4"/>
-      <c r="E138" s="145"/>
+      <c r="E138" s="121"/>
       <c r="F138" s="4"/>
       <c r="G138" s="4"/>
       <c r="H138" s="4"/>
@@ -7280,10 +7321,10 @@
     </row>
     <row r="139" spans="1:11" ht="16">
       <c r="A139" s="4"/>
-      <c r="B139" s="133"/>
-      <c r="C139" s="134"/>
+      <c r="B139" s="109"/>
+      <c r="C139" s="110"/>
       <c r="D139" s="4"/>
-      <c r="E139" s="145"/>
+      <c r="E139" s="121"/>
       <c r="F139" s="4"/>
       <c r="G139" s="4"/>
       <c r="H139" s="4"/>
@@ -7293,10 +7334,10 @@
     </row>
     <row r="140" spans="1:11" ht="16">
       <c r="A140" s="4"/>
-      <c r="B140" s="133"/>
-      <c r="C140" s="134"/>
+      <c r="B140" s="109"/>
+      <c r="C140" s="110"/>
       <c r="D140" s="4"/>
-      <c r="E140" s="145"/>
+      <c r="E140" s="121"/>
       <c r="F140" s="4"/>
       <c r="G140" s="4"/>
       <c r="H140" s="4"/>
@@ -7306,10 +7347,10 @@
     </row>
     <row r="141" spans="1:11" ht="16">
       <c r="A141" s="4"/>
-      <c r="B141" s="133"/>
-      <c r="C141" s="134"/>
+      <c r="B141" s="109"/>
+      <c r="C141" s="110"/>
       <c r="D141" s="4"/>
-      <c r="E141" s="145"/>
+      <c r="E141" s="121"/>
       <c r="F141" s="4"/>
       <c r="G141" s="4"/>
       <c r="H141" s="4"/>
@@ -7319,10 +7360,10 @@
     </row>
     <row r="142" spans="1:11" ht="16">
       <c r="A142" s="4"/>
-      <c r="B142" s="133"/>
-      <c r="C142" s="134"/>
+      <c r="B142" s="109"/>
+      <c r="C142" s="110"/>
       <c r="D142" s="4"/>
-      <c r="E142" s="145"/>
+      <c r="E142" s="121"/>
       <c r="F142" s="4"/>
       <c r="G142" s="4"/>
       <c r="H142" s="4"/>
@@ -7332,10 +7373,10 @@
     </row>
     <row r="143" spans="1:11" ht="16">
       <c r="A143" s="4"/>
-      <c r="B143" s="133"/>
-      <c r="C143" s="134"/>
+      <c r="B143" s="109"/>
+      <c r="C143" s="110"/>
       <c r="D143" s="4"/>
-      <c r="E143" s="145"/>
+      <c r="E143" s="121"/>
       <c r="F143" s="4"/>
       <c r="G143" s="4"/>
       <c r="H143" s="4"/>
@@ -7345,10 +7386,10 @@
     </row>
     <row r="144" spans="1:11" ht="16">
       <c r="A144" s="4"/>
-      <c r="B144" s="133"/>
-      <c r="C144" s="134"/>
+      <c r="B144" s="109"/>
+      <c r="C144" s="110"/>
       <c r="D144" s="4"/>
-      <c r="E144" s="145"/>
+      <c r="E144" s="121"/>
       <c r="F144" s="4"/>
       <c r="G144" s="4"/>
       <c r="H144" s="4"/>
@@ -7358,10 +7399,10 @@
     </row>
     <row r="145" spans="1:11" ht="16">
       <c r="A145" s="4"/>
-      <c r="B145" s="133"/>
-      <c r="C145" s="134"/>
+      <c r="B145" s="109"/>
+      <c r="C145" s="110"/>
       <c r="D145" s="4"/>
-      <c r="E145" s="145"/>
+      <c r="E145" s="121"/>
       <c r="F145" s="4"/>
       <c r="G145" s="4"/>
       <c r="H145" s="4"/>
@@ -7371,10 +7412,10 @@
     </row>
     <row r="146" spans="1:11" ht="16">
       <c r="A146" s="4"/>
-      <c r="B146" s="133"/>
-      <c r="C146" s="134"/>
+      <c r="B146" s="109"/>
+      <c r="C146" s="110"/>
       <c r="D146" s="4"/>
-      <c r="E146" s="145"/>
+      <c r="E146" s="121"/>
       <c r="F146" s="4"/>
       <c r="G146" s="4"/>
       <c r="H146" s="4"/>
@@ -7384,10 +7425,10 @@
     </row>
     <row r="147" spans="1:11" ht="16">
       <c r="A147" s="4"/>
-      <c r="B147" s="133"/>
-      <c r="C147" s="134"/>
+      <c r="B147" s="109"/>
+      <c r="C147" s="110"/>
       <c r="D147" s="4"/>
-      <c r="E147" s="145"/>
+      <c r="E147" s="121"/>
       <c r="F147" s="4"/>
       <c r="G147" s="4"/>
       <c r="H147" s="4"/>
@@ -7397,10 +7438,10 @@
     </row>
     <row r="148" spans="1:11" ht="16">
       <c r="A148" s="4"/>
-      <c r="B148" s="133"/>
-      <c r="C148" s="134"/>
+      <c r="B148" s="109"/>
+      <c r="C148" s="110"/>
       <c r="D148" s="4"/>
-      <c r="E148" s="145"/>
+      <c r="E148" s="121"/>
       <c r="F148" s="4"/>
       <c r="G148" s="4"/>
       <c r="H148" s="4"/>
@@ -7410,10 +7451,10 @@
     </row>
     <row r="149" spans="1:11" ht="16">
       <c r="A149" s="4"/>
-      <c r="B149" s="133"/>
-      <c r="C149" s="134"/>
+      <c r="B149" s="109"/>
+      <c r="C149" s="110"/>
       <c r="D149" s="4"/>
-      <c r="E149" s="145"/>
+      <c r="E149" s="121"/>
       <c r="F149" s="4"/>
       <c r="G149" s="4"/>
       <c r="H149" s="4"/>
@@ -7423,10 +7464,10 @@
     </row>
     <row r="150" spans="1:11" ht="16">
       <c r="A150" s="4"/>
-      <c r="B150" s="133"/>
-      <c r="C150" s="134"/>
+      <c r="B150" s="109"/>
+      <c r="C150" s="110"/>
       <c r="D150" s="4"/>
-      <c r="E150" s="145"/>
+      <c r="E150" s="121"/>
       <c r="F150" s="4"/>
       <c r="G150" s="4"/>
       <c r="H150" s="4"/>
@@ -7436,10 +7477,10 @@
     </row>
     <row r="151" spans="1:11" ht="16">
       <c r="A151" s="4"/>
-      <c r="B151" s="133"/>
-      <c r="C151" s="134"/>
+      <c r="B151" s="109"/>
+      <c r="C151" s="110"/>
       <c r="D151" s="4"/>
-      <c r="E151" s="145"/>
+      <c r="E151" s="121"/>
       <c r="F151" s="4"/>
       <c r="G151" s="4"/>
       <c r="H151" s="4"/>
@@ -7449,10 +7490,10 @@
     </row>
     <row r="152" spans="1:11" ht="16">
       <c r="A152" s="4"/>
-      <c r="B152" s="133"/>
-      <c r="C152" s="134"/>
+      <c r="B152" s="109"/>
+      <c r="C152" s="110"/>
       <c r="D152" s="4"/>
-      <c r="E152" s="145"/>
+      <c r="E152" s="121"/>
       <c r="F152" s="4"/>
       <c r="G152" s="4"/>
       <c r="H152" s="4"/>
@@ -7462,10 +7503,10 @@
     </row>
     <row r="153" spans="1:11" ht="16">
       <c r="A153" s="4"/>
-      <c r="B153" s="133"/>
-      <c r="C153" s="134"/>
+      <c r="B153" s="109"/>
+      <c r="C153" s="110"/>
       <c r="D153" s="4"/>
-      <c r="E153" s="145"/>
+      <c r="E153" s="121"/>
       <c r="F153" s="4"/>
       <c r="G153" s="4"/>
       <c r="H153" s="4"/>
@@ -7475,10 +7516,10 @@
     </row>
     <row r="154" spans="1:11" ht="16">
       <c r="A154" s="4"/>
-      <c r="B154" s="133"/>
-      <c r="C154" s="134"/>
+      <c r="B154" s="109"/>
+      <c r="C154" s="110"/>
       <c r="D154" s="4"/>
-      <c r="E154" s="145"/>
+      <c r="E154" s="121"/>
       <c r="F154" s="4"/>
       <c r="G154" s="4"/>
       <c r="H154" s="4"/>
@@ -7488,10 +7529,10 @@
     </row>
     <row r="155" spans="1:11" ht="16">
       <c r="A155" s="4"/>
-      <c r="B155" s="133"/>
-      <c r="C155" s="134"/>
+      <c r="B155" s="109"/>
+      <c r="C155" s="110"/>
       <c r="D155" s="4"/>
-      <c r="E155" s="145"/>
+      <c r="E155" s="121"/>
       <c r="F155" s="4"/>
       <c r="G155" s="4"/>
       <c r="H155" s="4"/>
@@ -7501,10 +7542,10 @@
     </row>
     <row r="156" spans="1:11" ht="16">
       <c r="A156" s="4"/>
-      <c r="B156" s="133"/>
-      <c r="C156" s="134"/>
+      <c r="B156" s="109"/>
+      <c r="C156" s="110"/>
       <c r="D156" s="4"/>
-      <c r="E156" s="145"/>
+      <c r="E156" s="121"/>
       <c r="F156" s="4"/>
       <c r="G156" s="4"/>
       <c r="H156" s="4"/>
@@ -7514,10 +7555,10 @@
     </row>
     <row r="157" spans="1:11" ht="16">
       <c r="A157" s="4"/>
-      <c r="B157" s="133"/>
-      <c r="C157" s="134"/>
+      <c r="B157" s="109"/>
+      <c r="C157" s="110"/>
       <c r="D157" s="4"/>
-      <c r="E157" s="145"/>
+      <c r="E157" s="121"/>
       <c r="F157" s="4"/>
       <c r="G157" s="4"/>
       <c r="H157" s="4"/>
@@ -7527,10 +7568,10 @@
     </row>
     <row r="158" spans="1:11" ht="16">
       <c r="A158" s="4"/>
-      <c r="B158" s="133"/>
-      <c r="C158" s="134"/>
+      <c r="B158" s="109"/>
+      <c r="C158" s="110"/>
       <c r="D158" s="4"/>
-      <c r="E158" s="145"/>
+      <c r="E158" s="121"/>
       <c r="F158" s="4"/>
       <c r="G158" s="4"/>
       <c r="H158" s="4"/>
@@ -7540,10 +7581,10 @@
     </row>
     <row r="159" spans="1:11" ht="16">
       <c r="A159" s="4"/>
-      <c r="B159" s="133"/>
-      <c r="C159" s="134"/>
+      <c r="B159" s="109"/>
+      <c r="C159" s="110"/>
       <c r="D159" s="4"/>
-      <c r="E159" s="145"/>
+      <c r="E159" s="121"/>
       <c r="F159" s="4"/>
       <c r="G159" s="4"/>
       <c r="H159" s="4"/>
@@ -7553,10 +7594,10 @@
     </row>
     <row r="160" spans="1:11" ht="16">
       <c r="A160" s="4"/>
-      <c r="B160" s="133"/>
-      <c r="C160" s="134"/>
+      <c r="B160" s="109"/>
+      <c r="C160" s="110"/>
       <c r="D160" s="4"/>
-      <c r="E160" s="145"/>
+      <c r="E160" s="121"/>
       <c r="F160" s="4"/>
       <c r="G160" s="4"/>
       <c r="H160" s="4"/>
@@ -7566,10 +7607,10 @@
     </row>
     <row r="161" spans="1:11" ht="16">
       <c r="A161" s="4"/>
-      <c r="B161" s="133"/>
-      <c r="C161" s="134"/>
+      <c r="B161" s="109"/>
+      <c r="C161" s="110"/>
       <c r="D161" s="4"/>
-      <c r="E161" s="145"/>
+      <c r="E161" s="121"/>
       <c r="F161" s="4"/>
       <c r="G161" s="4"/>
       <c r="H161" s="4"/>
@@ -7579,10 +7620,10 @@
     </row>
     <row r="162" spans="1:11" ht="16">
       <c r="A162" s="4"/>
-      <c r="B162" s="133"/>
-      <c r="C162" s="134"/>
+      <c r="B162" s="109"/>
+      <c r="C162" s="110"/>
       <c r="D162" s="4"/>
-      <c r="E162" s="145"/>
+      <c r="E162" s="121"/>
       <c r="F162" s="4"/>
       <c r="G162" s="4"/>
       <c r="H162" s="4"/>
@@ -7592,10 +7633,10 @@
     </row>
     <row r="163" spans="1:11" ht="16">
       <c r="A163" s="4"/>
-      <c r="B163" s="133"/>
-      <c r="C163" s="134"/>
+      <c r="B163" s="109"/>
+      <c r="C163" s="110"/>
       <c r="D163" s="4"/>
-      <c r="E163" s="145"/>
+      <c r="E163" s="121"/>
       <c r="F163" s="4"/>
       <c r="G163" s="4"/>
       <c r="H163" s="4"/>
@@ -7605,10 +7646,10 @@
     </row>
     <row r="164" spans="1:11" ht="16">
       <c r="A164" s="4"/>
-      <c r="B164" s="133"/>
-      <c r="C164" s="134"/>
+      <c r="B164" s="109"/>
+      <c r="C164" s="110"/>
       <c r="D164" s="4"/>
-      <c r="E164" s="145"/>
+      <c r="E164" s="121"/>
       <c r="F164" s="4"/>
       <c r="G164" s="4"/>
       <c r="H164" s="4"/>
@@ -7618,10 +7659,10 @@
     </row>
     <row r="165" spans="1:11" ht="16">
       <c r="A165" s="4"/>
-      <c r="B165" s="133"/>
-      <c r="C165" s="134"/>
+      <c r="B165" s="109"/>
+      <c r="C165" s="110"/>
       <c r="D165" s="4"/>
-      <c r="E165" s="145"/>
+      <c r="E165" s="121"/>
       <c r="F165" s="4"/>
       <c r="G165" s="4"/>
       <c r="H165" s="4"/>
@@ -7631,10 +7672,10 @@
     </row>
     <row r="166" spans="1:11" ht="16">
       <c r="A166" s="4"/>
-      <c r="B166" s="133"/>
-      <c r="C166" s="134"/>
+      <c r="B166" s="109"/>
+      <c r="C166" s="110"/>
       <c r="D166" s="4"/>
-      <c r="E166" s="145"/>
+      <c r="E166" s="121"/>
       <c r="F166" s="4"/>
       <c r="G166" s="4"/>
       <c r="H166" s="4"/>
@@ -7644,10 +7685,10 @@
     </row>
     <row r="167" spans="1:11" ht="16">
       <c r="A167" s="4"/>
-      <c r="B167" s="133"/>
-      <c r="C167" s="134"/>
+      <c r="B167" s="109"/>
+      <c r="C167" s="110"/>
       <c r="D167" s="4"/>
-      <c r="E167" s="145"/>
+      <c r="E167" s="121"/>
       <c r="F167" s="4"/>
       <c r="G167" s="4"/>
       <c r="H167" s="4"/>
@@ -7657,10 +7698,10 @@
     </row>
     <row r="168" spans="1:11" ht="16">
       <c r="A168" s="4"/>
-      <c r="B168" s="133"/>
-      <c r="C168" s="134"/>
+      <c r="B168" s="109"/>
+      <c r="C168" s="110"/>
       <c r="D168" s="4"/>
-      <c r="E168" s="145"/>
+      <c r="E168" s="121"/>
       <c r="F168" s="4"/>
       <c r="G168" s="4"/>
       <c r="H168" s="4"/>
@@ -7670,10 +7711,10 @@
     </row>
     <row r="169" spans="1:11" ht="16">
       <c r="A169" s="4"/>
-      <c r="B169" s="133"/>
-      <c r="C169" s="134"/>
+      <c r="B169" s="109"/>
+      <c r="C169" s="110"/>
       <c r="D169" s="4"/>
-      <c r="E169" s="145"/>
+      <c r="E169" s="121"/>
       <c r="F169" s="4"/>
       <c r="G169" s="4"/>
       <c r="H169" s="4"/>
@@ -7683,10 +7724,10 @@
     </row>
     <row r="170" spans="1:11" ht="16">
       <c r="A170" s="4"/>
-      <c r="B170" s="133"/>
-      <c r="C170" s="134"/>
+      <c r="B170" s="109"/>
+      <c r="C170" s="110"/>
       <c r="D170" s="4"/>
-      <c r="E170" s="145"/>
+      <c r="E170" s="121"/>
       <c r="F170" s="4"/>
       <c r="G170" s="4"/>
       <c r="H170" s="4"/>
@@ -7696,10 +7737,10 @@
     </row>
     <row r="171" spans="1:11" ht="16">
       <c r="A171" s="4"/>
-      <c r="B171" s="133"/>
-      <c r="C171" s="134"/>
+      <c r="B171" s="109"/>
+      <c r="C171" s="110"/>
       <c r="D171" s="4"/>
-      <c r="E171" s="145"/>
+      <c r="E171" s="121"/>
       <c r="F171" s="4"/>
       <c r="G171" s="4"/>
       <c r="H171" s="4"/>
@@ -7709,10 +7750,10 @@
     </row>
     <row r="172" spans="1:11" ht="16">
       <c r="A172" s="4"/>
-      <c r="B172" s="133"/>
-      <c r="C172" s="134"/>
+      <c r="B172" s="109"/>
+      <c r="C172" s="110"/>
       <c r="D172" s="4"/>
-      <c r="E172" s="145"/>
+      <c r="E172" s="121"/>
       <c r="F172" s="4"/>
       <c r="G172" s="4"/>
       <c r="H172" s="4"/>
@@ -7722,10 +7763,10 @@
     </row>
     <row r="173" spans="1:11" ht="16">
       <c r="A173" s="4"/>
-      <c r="B173" s="133"/>
-      <c r="C173" s="134"/>
+      <c r="B173" s="109"/>
+      <c r="C173" s="110"/>
       <c r="D173" s="4"/>
-      <c r="E173" s="145"/>
+      <c r="E173" s="121"/>
       <c r="F173" s="4"/>
       <c r="G173" s="4"/>
       <c r="H173" s="4"/>
@@ -7735,10 +7776,10 @@
     </row>
     <row r="174" spans="1:11" ht="16">
       <c r="A174" s="4"/>
-      <c r="B174" s="133"/>
-      <c r="C174" s="134"/>
+      <c r="B174" s="109"/>
+      <c r="C174" s="110"/>
       <c r="D174" s="4"/>
-      <c r="E174" s="145"/>
+      <c r="E174" s="121"/>
       <c r="F174" s="4"/>
       <c r="G174" s="4"/>
       <c r="H174" s="4"/>
@@ -7748,10 +7789,10 @@
     </row>
     <row r="175" spans="1:11" ht="16">
       <c r="A175" s="4"/>
-      <c r="B175" s="133"/>
-      <c r="C175" s="134"/>
+      <c r="B175" s="109"/>
+      <c r="C175" s="110"/>
       <c r="D175" s="4"/>
-      <c r="E175" s="145"/>
+      <c r="E175" s="121"/>
       <c r="F175" s="4"/>
       <c r="G175" s="4"/>
       <c r="H175" s="4"/>
@@ -7761,10 +7802,10 @@
     </row>
     <row r="176" spans="1:11" ht="16">
       <c r="A176" s="4"/>
-      <c r="B176" s="133"/>
-      <c r="C176" s="134"/>
+      <c r="B176" s="109"/>
+      <c r="C176" s="110"/>
       <c r="D176" s="4"/>
-      <c r="E176" s="145"/>
+      <c r="E176" s="121"/>
       <c r="F176" s="4"/>
       <c r="G176" s="4"/>
       <c r="H176" s="4"/>
@@ -7774,10 +7815,10 @@
     </row>
     <row r="177" spans="1:11" ht="16">
       <c r="A177" s="4"/>
-      <c r="B177" s="133"/>
-      <c r="C177" s="134"/>
+      <c r="B177" s="109"/>
+      <c r="C177" s="110"/>
       <c r="D177" s="4"/>
-      <c r="E177" s="145"/>
+      <c r="E177" s="121"/>
       <c r="F177" s="4"/>
       <c r="G177" s="4"/>
       <c r="H177" s="4"/>
@@ -7787,10 +7828,10 @@
     </row>
     <row r="178" spans="1:11" ht="16">
       <c r="A178" s="4"/>
-      <c r="B178" s="133"/>
-      <c r="C178" s="134"/>
+      <c r="B178" s="109"/>
+      <c r="C178" s="110"/>
       <c r="D178" s="4"/>
-      <c r="E178" s="145"/>
+      <c r="E178" s="121"/>
       <c r="F178" s="4"/>
       <c r="G178" s="4"/>
       <c r="H178" s="4"/>
@@ -7800,10 +7841,10 @@
     </row>
     <row r="179" spans="1:11" ht="16">
       <c r="A179" s="4"/>
-      <c r="B179" s="133"/>
-      <c r="C179" s="134"/>
+      <c r="B179" s="109"/>
+      <c r="C179" s="110"/>
       <c r="D179" s="4"/>
-      <c r="E179" s="145"/>
+      <c r="E179" s="121"/>
       <c r="F179" s="4"/>
       <c r="G179" s="4"/>
       <c r="H179" s="4"/>
@@ -7813,10 +7854,10 @@
     </row>
     <row r="180" spans="1:11" ht="16">
       <c r="A180" s="4"/>
-      <c r="B180" s="133"/>
-      <c r="C180" s="134"/>
+      <c r="B180" s="109"/>
+      <c r="C180" s="110"/>
       <c r="D180" s="4"/>
-      <c r="E180" s="145"/>
+      <c r="E180" s="121"/>
       <c r="F180" s="4"/>
       <c r="G180" s="4"/>
       <c r="H180" s="4"/>
@@ -7826,10 +7867,10 @@
     </row>
     <row r="181" spans="1:11" ht="16">
       <c r="A181" s="4"/>
-      <c r="B181" s="133"/>
-      <c r="C181" s="134"/>
+      <c r="B181" s="109"/>
+      <c r="C181" s="110"/>
       <c r="D181" s="4"/>
-      <c r="E181" s="145"/>
+      <c r="E181" s="121"/>
       <c r="F181" s="4"/>
       <c r="G181" s="4"/>
       <c r="H181" s="4"/>
@@ -7839,10 +7880,10 @@
     </row>
     <row r="182" spans="1:11" ht="16">
       <c r="A182" s="4"/>
-      <c r="B182" s="133"/>
-      <c r="C182" s="134"/>
+      <c r="B182" s="109"/>
+      <c r="C182" s="110"/>
       <c r="D182" s="4"/>
-      <c r="E182" s="145"/>
+      <c r="E182" s="121"/>
       <c r="F182" s="4"/>
       <c r="G182" s="4"/>
       <c r="H182" s="4"/>
@@ -7852,10 +7893,10 @@
     </row>
     <row r="183" spans="1:11" ht="16">
       <c r="A183" s="4"/>
-      <c r="B183" s="133"/>
-      <c r="C183" s="134"/>
+      <c r="B183" s="109"/>
+      <c r="C183" s="110"/>
       <c r="D183" s="4"/>
-      <c r="E183" s="145"/>
+      <c r="E183" s="121"/>
       <c r="F183" s="4"/>
       <c r="G183" s="4"/>
       <c r="H183" s="4"/>
@@ -7865,10 +7906,10 @@
     </row>
     <row r="184" spans="1:11" ht="16">
       <c r="A184" s="4"/>
-      <c r="B184" s="133"/>
-      <c r="C184" s="134"/>
+      <c r="B184" s="109"/>
+      <c r="C184" s="110"/>
       <c r="D184" s="4"/>
-      <c r="E184" s="145"/>
+      <c r="E184" s="121"/>
       <c r="F184" s="4"/>
       <c r="G184" s="4"/>
       <c r="H184" s="4"/>
@@ -7878,10 +7919,10 @@
     </row>
     <row r="185" spans="1:11" ht="16">
       <c r="A185" s="4"/>
-      <c r="B185" s="133"/>
-      <c r="C185" s="134"/>
+      <c r="B185" s="109"/>
+      <c r="C185" s="110"/>
       <c r="D185" s="4"/>
-      <c r="E185" s="145"/>
+      <c r="E185" s="121"/>
       <c r="F185" s="4"/>
       <c r="G185" s="4"/>
       <c r="H185" s="4"/>
@@ -7891,10 +7932,10 @@
     </row>
     <row r="186" spans="1:11" ht="16">
       <c r="A186" s="4"/>
-      <c r="B186" s="133"/>
-      <c r="C186" s="134"/>
+      <c r="B186" s="109"/>
+      <c r="C186" s="110"/>
       <c r="D186" s="4"/>
-      <c r="E186" s="145"/>
+      <c r="E186" s="121"/>
       <c r="F186" s="4"/>
       <c r="G186" s="4"/>
       <c r="H186" s="4"/>
@@ -7904,10 +7945,10 @@
     </row>
     <row r="187" spans="1:11" ht="16">
       <c r="A187" s="4"/>
-      <c r="B187" s="133"/>
-      <c r="C187" s="134"/>
+      <c r="B187" s="109"/>
+      <c r="C187" s="110"/>
       <c r="D187" s="4"/>
-      <c r="E187" s="145"/>
+      <c r="E187" s="121"/>
       <c r="F187" s="4"/>
       <c r="G187" s="4"/>
       <c r="H187" s="4"/>
@@ -7917,10 +7958,10 @@
     </row>
     <row r="188" spans="1:11" ht="16">
       <c r="A188" s="4"/>
-      <c r="B188" s="133"/>
-      <c r="C188" s="134"/>
+      <c r="B188" s="109"/>
+      <c r="C188" s="110"/>
       <c r="D188" s="4"/>
-      <c r="E188" s="145"/>
+      <c r="E188" s="121"/>
       <c r="F188" s="4"/>
       <c r="G188" s="4"/>
       <c r="H188" s="4"/>
@@ -7930,10 +7971,10 @@
     </row>
     <row r="189" spans="1:11" ht="16">
       <c r="A189" s="4"/>
-      <c r="B189" s="133"/>
-      <c r="C189" s="134"/>
+      <c r="B189" s="109"/>
+      <c r="C189" s="110"/>
       <c r="D189" s="4"/>
-      <c r="E189" s="145"/>
+      <c r="E189" s="121"/>
       <c r="F189" s="4"/>
       <c r="G189" s="4"/>
       <c r="H189" s="4"/>
@@ -7943,10 +7984,10 @@
     </row>
     <row r="190" spans="1:11" ht="16">
       <c r="A190" s="4"/>
-      <c r="B190" s="133"/>
-      <c r="C190" s="134"/>
+      <c r="B190" s="109"/>
+      <c r="C190" s="110"/>
       <c r="D190" s="4"/>
-      <c r="E190" s="145"/>
+      <c r="E190" s="121"/>
       <c r="F190" s="4"/>
       <c r="G190" s="4"/>
       <c r="H190" s="4"/>
@@ -7956,10 +7997,10 @@
     </row>
     <row r="191" spans="1:11" ht="16">
       <c r="A191" s="4"/>
-      <c r="B191" s="133"/>
-      <c r="C191" s="134"/>
+      <c r="B191" s="109"/>
+      <c r="C191" s="110"/>
       <c r="D191" s="4"/>
-      <c r="E191" s="145"/>
+      <c r="E191" s="121"/>
       <c r="F191" s="4"/>
       <c r="G191" s="4"/>
       <c r="H191" s="4"/>
@@ -7969,10 +8010,10 @@
     </row>
     <row r="192" spans="1:11" ht="16">
       <c r="A192" s="4"/>
-      <c r="B192" s="133"/>
-      <c r="C192" s="134"/>
+      <c r="B192" s="109"/>
+      <c r="C192" s="110"/>
       <c r="D192" s="4"/>
-      <c r="E192" s="145"/>
+      <c r="E192" s="121"/>
       <c r="F192" s="4"/>
       <c r="G192" s="4"/>
       <c r="H192" s="4"/>
@@ -7982,10 +8023,10 @@
     </row>
     <row r="193" spans="1:11" ht="16">
       <c r="A193" s="4"/>
-      <c r="B193" s="133"/>
-      <c r="C193" s="134"/>
+      <c r="B193" s="109"/>
+      <c r="C193" s="110"/>
       <c r="D193" s="4"/>
-      <c r="E193" s="145"/>
+      <c r="E193" s="121"/>
       <c r="F193" s="4"/>
       <c r="G193" s="4"/>
       <c r="H193" s="4"/>
@@ -7995,10 +8036,10 @@
     </row>
     <row r="194" spans="1:11" ht="16">
       <c r="A194" s="4"/>
-      <c r="B194" s="133"/>
-      <c r="C194" s="134"/>
+      <c r="B194" s="109"/>
+      <c r="C194" s="110"/>
       <c r="D194" s="4"/>
-      <c r="E194" s="145"/>
+      <c r="E194" s="121"/>
       <c r="F194" s="4"/>
       <c r="G194" s="4"/>
       <c r="H194" s="4"/>
@@ -8008,10 +8049,10 @@
     </row>
     <row r="195" spans="1:11" ht="16">
       <c r="A195" s="4"/>
-      <c r="B195" s="133"/>
-      <c r="C195" s="134"/>
+      <c r="B195" s="109"/>
+      <c r="C195" s="110"/>
       <c r="D195" s="4"/>
-      <c r="E195" s="145"/>
+      <c r="E195" s="121"/>
       <c r="F195" s="4"/>
       <c r="G195" s="4"/>
       <c r="H195" s="4"/>
@@ -8021,10 +8062,10 @@
     </row>
     <row r="196" spans="1:11" ht="16">
       <c r="A196" s="4"/>
-      <c r="B196" s="133"/>
-      <c r="C196" s="134"/>
+      <c r="B196" s="109"/>
+      <c r="C196" s="110"/>
       <c r="D196" s="4"/>
-      <c r="E196" s="145"/>
+      <c r="E196" s="121"/>
       <c r="F196" s="4"/>
       <c r="G196" s="4"/>
       <c r="H196" s="4"/>
@@ -8034,10 +8075,10 @@
     </row>
     <row r="197" spans="1:11" ht="16">
       <c r="A197" s="4"/>
-      <c r="B197" s="133"/>
-      <c r="C197" s="134"/>
+      <c r="B197" s="109"/>
+      <c r="C197" s="110"/>
       <c r="D197" s="4"/>
-      <c r="E197" s="145"/>
+      <c r="E197" s="121"/>
       <c r="F197" s="4"/>
       <c r="G197" s="4"/>
       <c r="H197" s="4"/>
@@ -8047,10 +8088,10 @@
     </row>
     <row r="198" spans="1:11" ht="16">
       <c r="A198" s="4"/>
-      <c r="B198" s="133"/>
-      <c r="C198" s="134"/>
+      <c r="B198" s="109"/>
+      <c r="C198" s="110"/>
       <c r="D198" s="4"/>
-      <c r="E198" s="145"/>
+      <c r="E198" s="121"/>
       <c r="F198" s="4"/>
       <c r="G198" s="4"/>
       <c r="H198" s="4"/>
@@ -8060,10 +8101,10 @@
     </row>
     <row r="199" spans="1:11" ht="16">
       <c r="A199" s="4"/>
-      <c r="B199" s="133"/>
-      <c r="C199" s="134"/>
+      <c r="B199" s="109"/>
+      <c r="C199" s="110"/>
       <c r="D199" s="4"/>
-      <c r="E199" s="145"/>
+      <c r="E199" s="121"/>
       <c r="F199" s="4"/>
       <c r="G199" s="4"/>
       <c r="H199" s="4"/>
@@ -8073,10 +8114,10 @@
     </row>
     <row r="200" spans="1:11" ht="16">
       <c r="A200" s="4"/>
-      <c r="B200" s="133"/>
-      <c r="C200" s="134"/>
+      <c r="B200" s="109"/>
+      <c r="C200" s="110"/>
       <c r="D200" s="4"/>
-      <c r="E200" s="145"/>
+      <c r="E200" s="121"/>
       <c r="F200" s="4"/>
       <c r="G200" s="4"/>
       <c r="H200" s="4"/>
@@ -8086,10 +8127,10 @@
     </row>
     <row r="201" spans="1:11" ht="16">
       <c r="A201" s="4"/>
-      <c r="B201" s="133"/>
-      <c r="C201" s="134"/>
+      <c r="B201" s="109"/>
+      <c r="C201" s="110"/>
       <c r="D201" s="4"/>
-      <c r="E201" s="145"/>
+      <c r="E201" s="121"/>
       <c r="F201" s="4"/>
       <c r="G201" s="4"/>
       <c r="H201" s="4"/>
@@ -8099,10 +8140,10 @@
     </row>
     <row r="202" spans="1:11" ht="16">
       <c r="A202" s="4"/>
-      <c r="B202" s="133"/>
-      <c r="C202" s="134"/>
+      <c r="B202" s="109"/>
+      <c r="C202" s="110"/>
       <c r="D202" s="4"/>
-      <c r="E202" s="145"/>
+      <c r="E202" s="121"/>
       <c r="F202" s="4"/>
       <c r="G202" s="4"/>
       <c r="H202" s="4"/>
@@ -8112,10 +8153,10 @@
     </row>
     <row r="203" spans="1:11" ht="16">
       <c r="A203" s="4"/>
-      <c r="B203" s="133"/>
-      <c r="C203" s="134"/>
+      <c r="B203" s="109"/>
+      <c r="C203" s="110"/>
       <c r="D203" s="4"/>
-      <c r="E203" s="145"/>
+      <c r="E203" s="121"/>
       <c r="F203" s="4"/>
       <c r="G203" s="4"/>
       <c r="H203" s="4"/>
@@ -8125,10 +8166,10 @@
     </row>
     <row r="204" spans="1:11" ht="16">
       <c r="A204" s="4"/>
-      <c r="B204" s="133"/>
-      <c r="C204" s="134"/>
+      <c r="B204" s="109"/>
+      <c r="C204" s="110"/>
       <c r="D204" s="4"/>
-      <c r="E204" s="145"/>
+      <c r="E204" s="121"/>
       <c r="F204" s="4"/>
       <c r="G204" s="4"/>
       <c r="H204" s="4"/>
@@ -8138,10 +8179,10 @@
     </row>
     <row r="205" spans="1:11" ht="16">
       <c r="A205" s="4"/>
-      <c r="B205" s="133"/>
-      <c r="C205" s="134"/>
+      <c r="B205" s="109"/>
+      <c r="C205" s="110"/>
       <c r="D205" s="4"/>
-      <c r="E205" s="145"/>
+      <c r="E205" s="121"/>
       <c r="F205" s="4"/>
       <c r="G205" s="4"/>
       <c r="H205" s="4"/>
@@ -8151,10 +8192,10 @@
     </row>
     <row r="206" spans="1:11" ht="16">
       <c r="A206" s="4"/>
-      <c r="B206" s="133"/>
-      <c r="C206" s="134"/>
+      <c r="B206" s="109"/>
+      <c r="C206" s="110"/>
       <c r="D206" s="4"/>
-      <c r="E206" s="145"/>
+      <c r="E206" s="121"/>
       <c r="F206" s="4"/>
       <c r="G206" s="4"/>
       <c r="H206" s="4"/>
@@ -8164,10 +8205,10 @@
     </row>
     <row r="207" spans="1:11" ht="16">
       <c r="A207" s="4"/>
-      <c r="B207" s="133"/>
-      <c r="C207" s="134"/>
+      <c r="B207" s="109"/>
+      <c r="C207" s="110"/>
       <c r="D207" s="4"/>
-      <c r="E207" s="145"/>
+      <c r="E207" s="121"/>
       <c r="F207" s="4"/>
       <c r="G207" s="4"/>
       <c r="H207" s="4"/>
@@ -8177,10 +8218,10 @@
     </row>
     <row r="208" spans="1:11" ht="16">
       <c r="A208" s="4"/>
-      <c r="B208" s="133"/>
-      <c r="C208" s="134"/>
+      <c r="B208" s="109"/>
+      <c r="C208" s="110"/>
       <c r="D208" s="4"/>
-      <c r="E208" s="145"/>
+      <c r="E208" s="121"/>
       <c r="F208" s="4"/>
       <c r="G208" s="4"/>
       <c r="H208" s="4"/>
@@ -8190,10 +8231,10 @@
     </row>
     <row r="209" spans="1:11" ht="16">
       <c r="A209" s="4"/>
-      <c r="B209" s="133"/>
-      <c r="C209" s="134"/>
+      <c r="B209" s="109"/>
+      <c r="C209" s="110"/>
       <c r="D209" s="4"/>
-      <c r="E209" s="145"/>
+      <c r="E209" s="121"/>
       <c r="F209" s="4"/>
       <c r="G209" s="4"/>
       <c r="H209" s="4"/>
@@ -8203,10 +8244,10 @@
     </row>
     <row r="210" spans="1:11" ht="16">
       <c r="A210" s="4"/>
-      <c r="B210" s="133"/>
-      <c r="C210" s="134"/>
+      <c r="B210" s="109"/>
+      <c r="C210" s="110"/>
       <c r="D210" s="4"/>
-      <c r="E210" s="145"/>
+      <c r="E210" s="121"/>
       <c r="F210" s="4"/>
       <c r="G210" s="4"/>
       <c r="H210" s="4"/>
@@ -8216,10 +8257,10 @@
     </row>
     <row r="211" spans="1:11" ht="16">
       <c r="A211" s="4"/>
-      <c r="B211" s="133"/>
-      <c r="C211" s="134"/>
+      <c r="B211" s="109"/>
+      <c r="C211" s="110"/>
       <c r="D211" s="4"/>
-      <c r="E211" s="145"/>
+      <c r="E211" s="121"/>
       <c r="F211" s="4"/>
       <c r="G211" s="4"/>
       <c r="H211" s="4"/>
@@ -8229,10 +8270,10 @@
     </row>
     <row r="212" spans="1:11" ht="16">
       <c r="A212" s="4"/>
-      <c r="B212" s="133"/>
-      <c r="C212" s="134"/>
+      <c r="B212" s="109"/>
+      <c r="C212" s="110"/>
       <c r="D212" s="4"/>
-      <c r="E212" s="145"/>
+      <c r="E212" s="121"/>
       <c r="F212" s="4"/>
       <c r="G212" s="4"/>
       <c r="H212" s="4"/>
@@ -8242,10 +8283,10 @@
     </row>
     <row r="213" spans="1:11" ht="16">
       <c r="A213" s="4"/>
-      <c r="B213" s="133"/>
-      <c r="C213" s="134"/>
+      <c r="B213" s="109"/>
+      <c r="C213" s="110"/>
       <c r="D213" s="4"/>
-      <c r="E213" s="145"/>
+      <c r="E213" s="121"/>
       <c r="F213" s="4"/>
       <c r="G213" s="4"/>
       <c r="H213" s="4"/>
@@ -8255,10 +8296,10 @@
     </row>
     <row r="214" spans="1:11" ht="16">
       <c r="A214" s="4"/>
-      <c r="B214" s="133"/>
-      <c r="C214" s="134"/>
+      <c r="B214" s="109"/>
+      <c r="C214" s="110"/>
       <c r="D214" s="4"/>
-      <c r="E214" s="145"/>
+      <c r="E214" s="121"/>
       <c r="F214" s="4"/>
       <c r="G214" s="4"/>
       <c r="H214" s="4"/>
@@ -8268,10 +8309,10 @@
     </row>
     <row r="215" spans="1:11" ht="16">
       <c r="A215" s="4"/>
-      <c r="B215" s="133"/>
-      <c r="C215" s="134"/>
+      <c r="B215" s="109"/>
+      <c r="C215" s="110"/>
       <c r="D215" s="4"/>
-      <c r="E215" s="145"/>
+      <c r="E215" s="121"/>
       <c r="F215" s="4"/>
       <c r="G215" s="4"/>
       <c r="H215" s="4"/>
@@ -8281,10 +8322,10 @@
     </row>
     <row r="216" spans="1:11" ht="16">
       <c r="A216" s="4"/>
-      <c r="B216" s="133"/>
-      <c r="C216" s="134"/>
+      <c r="B216" s="109"/>
+      <c r="C216" s="110"/>
       <c r="D216" s="4"/>
-      <c r="E216" s="145"/>
+      <c r="E216" s="121"/>
       <c r="F216" s="4"/>
       <c r="G216" s="4"/>
       <c r="H216" s="4"/>
@@ -8294,10 +8335,10 @@
     </row>
     <row r="217" spans="1:11" ht="16">
       <c r="A217" s="4"/>
-      <c r="B217" s="133"/>
-      <c r="C217" s="134"/>
+      <c r="B217" s="109"/>
+      <c r="C217" s="110"/>
       <c r="D217" s="4"/>
-      <c r="E217" s="145"/>
+      <c r="E217" s="121"/>
       <c r="F217" s="4"/>
       <c r="G217" s="4"/>
       <c r="H217" s="4"/>
@@ -8307,10 +8348,10 @@
     </row>
     <row r="218" spans="1:11" ht="16">
       <c r="A218" s="4"/>
-      <c r="B218" s="133"/>
-      <c r="C218" s="134"/>
+      <c r="B218" s="109"/>
+      <c r="C218" s="110"/>
       <c r="D218" s="4"/>
-      <c r="E218" s="145"/>
+      <c r="E218" s="121"/>
       <c r="F218" s="4"/>
       <c r="G218" s="4"/>
       <c r="H218" s="4"/>
@@ -8320,10 +8361,10 @@
     </row>
     <row r="219" spans="1:11" ht="16">
       <c r="A219" s="4"/>
-      <c r="B219" s="133"/>
-      <c r="C219" s="134"/>
+      <c r="B219" s="109"/>
+      <c r="C219" s="110"/>
       <c r="D219" s="4"/>
-      <c r="E219" s="145"/>
+      <c r="E219" s="121"/>
       <c r="F219" s="4"/>
       <c r="G219" s="4"/>
       <c r="H219" s="4"/>
@@ -8333,10 +8374,10 @@
     </row>
     <row r="220" spans="1:11" ht="16">
       <c r="A220" s="4"/>
-      <c r="B220" s="133"/>
-      <c r="C220" s="134"/>
+      <c r="B220" s="109"/>
+      <c r="C220" s="110"/>
       <c r="D220" s="4"/>
-      <c r="E220" s="145"/>
+      <c r="E220" s="121"/>
       <c r="F220" s="4"/>
       <c r="G220" s="4"/>
       <c r="H220" s="4"/>
@@ -8346,10 +8387,10 @@
     </row>
     <row r="221" spans="1:11" ht="16">
       <c r="A221" s="4"/>
-      <c r="B221" s="133"/>
-      <c r="C221" s="134"/>
+      <c r="B221" s="109"/>
+      <c r="C221" s="110"/>
       <c r="D221" s="4"/>
-      <c r="E221" s="145"/>
+      <c r="E221" s="121"/>
       <c r="F221" s="4"/>
       <c r="G221" s="4"/>
       <c r="H221" s="4"/>
@@ -8359,10 +8400,10 @@
     </row>
     <row r="222" spans="1:11" ht="16">
       <c r="A222" s="4"/>
-      <c r="B222" s="133"/>
-      <c r="C222" s="134"/>
+      <c r="B222" s="109"/>
+      <c r="C222" s="110"/>
       <c r="D222" s="4"/>
-      <c r="E222" s="145"/>
+      <c r="E222" s="121"/>
       <c r="F222" s="4"/>
       <c r="G222" s="4"/>
       <c r="H222" s="4"/>
@@ -8372,10 +8413,10 @@
     </row>
     <row r="223" spans="1:11" ht="16">
       <c r="A223" s="4"/>
-      <c r="B223" s="133"/>
-      <c r="C223" s="134"/>
+      <c r="B223" s="109"/>
+      <c r="C223" s="110"/>
       <c r="D223" s="4"/>
-      <c r="E223" s="145"/>
+      <c r="E223" s="121"/>
       <c r="F223" s="4"/>
       <c r="G223" s="4"/>
       <c r="H223" s="4"/>
@@ -8385,10 +8426,10 @@
     </row>
     <row r="224" spans="1:11" ht="16">
       <c r="A224" s="4"/>
-      <c r="B224" s="133"/>
-      <c r="C224" s="134"/>
+      <c r="B224" s="109"/>
+      <c r="C224" s="110"/>
       <c r="D224" s="4"/>
-      <c r="E224" s="145"/>
+      <c r="E224" s="121"/>
       <c r="F224" s="4"/>
       <c r="G224" s="4"/>
       <c r="H224" s="4"/>
@@ -8398,10 +8439,10 @@
     </row>
     <row r="225" spans="1:11" ht="16">
       <c r="A225" s="4"/>
-      <c r="B225" s="133"/>
-      <c r="C225" s="134"/>
+      <c r="B225" s="109"/>
+      <c r="C225" s="110"/>
       <c r="D225" s="4"/>
-      <c r="E225" s="145"/>
+      <c r="E225" s="121"/>
       <c r="F225" s="4"/>
       <c r="G225" s="4"/>
       <c r="H225" s="4"/>
@@ -8411,10 +8452,10 @@
     </row>
     <row r="226" spans="1:11" ht="16">
       <c r="A226" s="4"/>
-      <c r="B226" s="133"/>
-      <c r="C226" s="134"/>
+      <c r="B226" s="109"/>
+      <c r="C226" s="110"/>
       <c r="D226" s="4"/>
-      <c r="E226" s="145"/>
+      <c r="E226" s="121"/>
       <c r="F226" s="4"/>
       <c r="G226" s="4"/>
       <c r="H226" s="4"/>
@@ -8424,10 +8465,10 @@
     </row>
     <row r="227" spans="1:11" ht="16">
       <c r="A227" s="4"/>
-      <c r="B227" s="133"/>
-      <c r="C227" s="134"/>
+      <c r="B227" s="109"/>
+      <c r="C227" s="110"/>
       <c r="D227" s="4"/>
-      <c r="E227" s="145"/>
+      <c r="E227" s="121"/>
       <c r="F227" s="4"/>
       <c r="G227" s="4"/>
       <c r="H227" s="4"/>
@@ -8437,10 +8478,10 @@
     </row>
     <row r="228" spans="1:11" ht="16">
       <c r="A228" s="4"/>
-      <c r="B228" s="133"/>
-      <c r="C228" s="134"/>
+      <c r="B228" s="109"/>
+      <c r="C228" s="110"/>
       <c r="D228" s="4"/>
-      <c r="E228" s="145"/>
+      <c r="E228" s="121"/>
       <c r="F228" s="4"/>
       <c r="G228" s="4"/>
       <c r="H228" s="4"/>
@@ -8450,10 +8491,10 @@
     </row>
     <row r="229" spans="1:11" ht="16">
       <c r="A229" s="4"/>
-      <c r="B229" s="133"/>
-      <c r="C229" s="134"/>
+      <c r="B229" s="109"/>
+      <c r="C229" s="110"/>
       <c r="D229" s="4"/>
-      <c r="E229" s="145"/>
+      <c r="E229" s="121"/>
       <c r="F229" s="4"/>
       <c r="G229" s="4"/>
       <c r="H229" s="4"/>
@@ -8463,10 +8504,10 @@
     </row>
     <row r="230" spans="1:11" ht="16">
       <c r="A230" s="4"/>
-      <c r="B230" s="133"/>
-      <c r="C230" s="134"/>
+      <c r="B230" s="109"/>
+      <c r="C230" s="110"/>
       <c r="D230" s="4"/>
-      <c r="E230" s="145"/>
+      <c r="E230" s="121"/>
       <c r="F230" s="4"/>
       <c r="G230" s="4"/>
       <c r="H230" s="4"/>
@@ -8476,10 +8517,10 @@
     </row>
     <row r="231" spans="1:11" ht="16">
       <c r="A231" s="4"/>
-      <c r="B231" s="133"/>
-      <c r="C231" s="134"/>
+      <c r="B231" s="109"/>
+      <c r="C231" s="110"/>
       <c r="D231" s="4"/>
-      <c r="E231" s="145"/>
+      <c r="E231" s="121"/>
       <c r="F231" s="4"/>
       <c r="G231" s="4"/>
       <c r="H231" s="4"/>
@@ -8489,10 +8530,10 @@
     </row>
     <row r="232" spans="1:11" ht="16">
       <c r="A232" s="4"/>
-      <c r="B232" s="133"/>
-      <c r="C232" s="134"/>
+      <c r="B232" s="109"/>
+      <c r="C232" s="110"/>
       <c r="D232" s="4"/>
-      <c r="E232" s="145"/>
+      <c r="E232" s="121"/>
       <c r="F232" s="4"/>
       <c r="G232" s="4"/>
       <c r="H232" s="4"/>
@@ -8502,10 +8543,10 @@
     </row>
     <row r="233" spans="1:11" ht="16">
       <c r="A233" s="4"/>
-      <c r="B233" s="133"/>
-      <c r="C233" s="134"/>
+      <c r="B233" s="109"/>
+      <c r="C233" s="110"/>
       <c r="D233" s="4"/>
-      <c r="E233" s="145"/>
+      <c r="E233" s="121"/>
       <c r="F233" s="4"/>
       <c r="G233" s="4"/>
       <c r="H233" s="4"/>
@@ -8515,10 +8556,10 @@
     </row>
     <row r="234" spans="1:11" ht="16">
       <c r="A234" s="4"/>
-      <c r="B234" s="133"/>
-      <c r="C234" s="134"/>
+      <c r="B234" s="109"/>
+      <c r="C234" s="110"/>
       <c r="D234" s="4"/>
-      <c r="E234" s="145"/>
+      <c r="E234" s="121"/>
       <c r="F234" s="4"/>
       <c r="G234" s="4"/>
       <c r="H234" s="4"/>
@@ -8528,10 +8569,10 @@
     </row>
     <row r="235" spans="1:11" ht="16">
       <c r="A235" s="4"/>
-      <c r="B235" s="133"/>
-      <c r="C235" s="134"/>
+      <c r="B235" s="109"/>
+      <c r="C235" s="110"/>
       <c r="D235" s="4"/>
-      <c r="E235" s="145"/>
+      <c r="E235" s="121"/>
       <c r="F235" s="4"/>
       <c r="G235" s="4"/>
       <c r="H235" s="4"/>
@@ -8541,10 +8582,10 @@
     </row>
     <row r="236" spans="1:11" ht="16">
       <c r="A236" s="4"/>
-      <c r="B236" s="133"/>
-      <c r="C236" s="134"/>
+      <c r="B236" s="109"/>
+      <c r="C236" s="110"/>
       <c r="D236" s="4"/>
-      <c r="E236" s="145"/>
+      <c r="E236" s="121"/>
       <c r="F236" s="4"/>
       <c r="G236" s="4"/>
       <c r="H236" s="4"/>
@@ -8554,10 +8595,10 @@
     </row>
     <row r="237" spans="1:11" ht="16">
       <c r="A237" s="4"/>
-      <c r="B237" s="133"/>
-      <c r="C237" s="134"/>
+      <c r="B237" s="109"/>
+      <c r="C237" s="110"/>
       <c r="D237" s="4"/>
-      <c r="E237" s="145"/>
+      <c r="E237" s="121"/>
       <c r="F237" s="4"/>
       <c r="G237" s="4"/>
       <c r="H237" s="4"/>
@@ -8567,10 +8608,10 @@
     </row>
     <row r="238" spans="1:11" ht="16">
       <c r="A238" s="4"/>
-      <c r="B238" s="133"/>
-      <c r="C238" s="134"/>
+      <c r="B238" s="109"/>
+      <c r="C238" s="110"/>
       <c r="D238" s="4"/>
-      <c r="E238" s="145"/>
+      <c r="E238" s="121"/>
       <c r="F238" s="4"/>
       <c r="G238" s="4"/>
       <c r="H238" s="4"/>
@@ -8580,10 +8621,10 @@
     </row>
     <row r="239" spans="1:11" ht="16">
       <c r="A239" s="4"/>
-      <c r="B239" s="133"/>
-      <c r="C239" s="134"/>
+      <c r="B239" s="109"/>
+      <c r="C239" s="110"/>
       <c r="D239" s="4"/>
-      <c r="E239" s="145"/>
+      <c r="E239" s="121"/>
       <c r="F239" s="4"/>
       <c r="G239" s="4"/>
       <c r="H239" s="4"/>
@@ -8650,213 +8691,213 @@
     <col min="5" max="16384" width="12.6640625" style="3"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" s="105" customFormat="1" ht="64" customHeight="1">
-      <c r="A1" s="128" t="s">
+    <row r="1" spans="1:4" s="85" customFormat="1" ht="64" customHeight="1">
+      <c r="A1" s="185" t="s">
         <v>188</v>
       </c>
-      <c r="B1" s="128"/>
+      <c r="B1" s="185"/>
     </row>
     <row r="2" spans="1:4" ht="15.75" customHeight="1">
-      <c r="A2" s="102" t="s">
+      <c r="A2" s="82" t="s">
         <v>18</v>
       </c>
-      <c r="B2" s="103" t="s">
+      <c r="B2" s="83" t="s">
         <v>2</v>
       </c>
-      <c r="C2" s="97"/>
-      <c r="D2" s="97"/>
+      <c r="C2" s="78"/>
+      <c r="D2" s="78"/>
     </row>
     <row r="3" spans="1:4" ht="15.75" customHeight="1">
-      <c r="A3" s="100" t="s">
+      <c r="A3" s="80" t="s">
         <v>21</v>
       </c>
-      <c r="B3" s="101">
+      <c r="B3" s="81">
         <v>2</v>
       </c>
-      <c r="C3" s="97"/>
-      <c r="D3" s="97"/>
+      <c r="C3" s="78"/>
+      <c r="D3" s="78"/>
     </row>
     <row r="4" spans="1:4" ht="15.75" customHeight="1">
-      <c r="A4" s="100" t="s">
+      <c r="A4" s="80" t="s">
         <v>23</v>
       </c>
-      <c r="B4" s="101">
+      <c r="B4" s="81">
         <v>2</v>
       </c>
-      <c r="C4" s="97"/>
-      <c r="D4" s="97"/>
+      <c r="C4" s="78"/>
+      <c r="D4" s="78"/>
     </row>
     <row r="5" spans="1:4" ht="15.75" customHeight="1">
-      <c r="A5" s="100"/>
-      <c r="B5" s="101"/>
-      <c r="C5" s="97"/>
-      <c r="D5" s="97"/>
+      <c r="A5" s="80"/>
+      <c r="B5" s="81"/>
+      <c r="C5" s="78"/>
+      <c r="D5" s="78"/>
     </row>
     <row r="6" spans="1:4" ht="15.75" customHeight="1">
-      <c r="A6" s="102" t="s">
+      <c r="A6" s="82" t="s">
         <v>27</v>
       </c>
-      <c r="B6" s="104"/>
-      <c r="C6" s="97"/>
-      <c r="D6" s="97"/>
+      <c r="B6" s="84"/>
+      <c r="C6" s="78"/>
+      <c r="D6" s="78"/>
     </row>
     <row r="7" spans="1:4" ht="15.75" customHeight="1">
-      <c r="A7" s="100" t="s">
+      <c r="A7" s="80" t="s">
         <v>28</v>
       </c>
-      <c r="B7" s="101">
+      <c r="B7" s="81">
         <v>2</v>
       </c>
-      <c r="C7" s="97"/>
-      <c r="D7" s="97"/>
+      <c r="C7" s="78"/>
+      <c r="D7" s="78"/>
     </row>
     <row r="8" spans="1:4" ht="15.75" customHeight="1">
-      <c r="A8" s="100"/>
-      <c r="B8" s="101"/>
-      <c r="C8" s="97"/>
-      <c r="D8" s="97"/>
+      <c r="A8" s="80"/>
+      <c r="B8" s="81"/>
+      <c r="C8" s="78"/>
+      <c r="D8" s="78"/>
     </row>
     <row r="9" spans="1:4" ht="15.75" customHeight="1">
-      <c r="A9" s="102" t="s">
+      <c r="A9" s="82" t="s">
         <v>37</v>
       </c>
-      <c r="B9" s="104"/>
-      <c r="C9" s="97"/>
-      <c r="D9" s="97"/>
+      <c r="B9" s="84"/>
+      <c r="C9" s="78"/>
+      <c r="D9" s="78"/>
     </row>
     <row r="10" spans="1:4" ht="15.75" customHeight="1">
-      <c r="A10" s="100" t="s">
+      <c r="A10" s="80" t="s">
         <v>38</v>
       </c>
-      <c r="B10" s="101">
+      <c r="B10" s="81">
         <v>4</v>
       </c>
-      <c r="C10" s="97"/>
-      <c r="D10" s="97"/>
+      <c r="C10" s="78"/>
+      <c r="D10" s="78"/>
     </row>
     <row r="11" spans="1:4" ht="15.75" customHeight="1">
-      <c r="A11" s="100" t="s">
+      <c r="A11" s="80" t="s">
         <v>23</v>
       </c>
-      <c r="B11" s="101">
+      <c r="B11" s="81">
         <v>4</v>
       </c>
-      <c r="C11" s="97"/>
-      <c r="D11" s="97"/>
+      <c r="C11" s="78"/>
+      <c r="D11" s="78"/>
     </row>
     <row r="12" spans="1:4" ht="15.75" customHeight="1">
-      <c r="A12" s="100"/>
-      <c r="B12" s="101"/>
-      <c r="C12" s="97"/>
-      <c r="D12" s="97"/>
+      <c r="A12" s="80"/>
+      <c r="B12" s="81"/>
+      <c r="C12" s="78"/>
+      <c r="D12" s="78"/>
     </row>
     <row r="13" spans="1:4" ht="15.75" customHeight="1">
-      <c r="A13" s="102" t="s">
+      <c r="A13" s="82" t="s">
         <v>42</v>
       </c>
-      <c r="B13" s="104"/>
-      <c r="C13" s="97"/>
-      <c r="D13" s="97"/>
+      <c r="B13" s="84"/>
+      <c r="C13" s="78"/>
+      <c r="D13" s="78"/>
     </row>
     <row r="14" spans="1:4" ht="15.75" customHeight="1">
-      <c r="A14" s="100" t="s">
+      <c r="A14" s="80" t="s">
         <v>23</v>
       </c>
-      <c r="B14" s="101">
+      <c r="B14" s="81">
         <v>4</v>
       </c>
-      <c r="C14" s="97"/>
-      <c r="D14" s="97"/>
+      <c r="C14" s="78"/>
+      <c r="D14" s="78"/>
     </row>
     <row r="15" spans="1:4" ht="15.75" customHeight="1">
-      <c r="A15" s="100"/>
-      <c r="B15" s="101"/>
-      <c r="C15" s="97"/>
-      <c r="D15" s="97"/>
+      <c r="A15" s="80"/>
+      <c r="B15" s="81"/>
+      <c r="C15" s="78"/>
+      <c r="D15" s="78"/>
     </row>
     <row r="16" spans="1:4" ht="15.75" customHeight="1">
-      <c r="A16" s="102" t="s">
+      <c r="A16" s="82" t="s">
         <v>47</v>
       </c>
-      <c r="B16" s="104"/>
-      <c r="C16" s="97"/>
-      <c r="D16" s="97"/>
+      <c r="B16" s="84"/>
+      <c r="C16" s="78"/>
+      <c r="D16" s="78"/>
     </row>
     <row r="17" spans="1:4" ht="15.75" customHeight="1">
-      <c r="A17" s="100" t="s">
+      <c r="A17" s="80" t="s">
         <v>50</v>
       </c>
-      <c r="B17" s="101">
+      <c r="B17" s="81">
         <v>4</v>
       </c>
-      <c r="C17" s="97"/>
-      <c r="D17" s="97"/>
+      <c r="C17" s="78"/>
+      <c r="D17" s="78"/>
     </row>
     <row r="18" spans="1:4" ht="15.75" customHeight="1">
-      <c r="A18" s="100" t="s">
+      <c r="A18" s="80" t="s">
         <v>23</v>
       </c>
-      <c r="B18" s="101">
+      <c r="B18" s="81">
         <v>8</v>
       </c>
-      <c r="C18" s="97"/>
-      <c r="D18" s="97"/>
+      <c r="C18" s="78"/>
+      <c r="D18" s="78"/>
     </row>
     <row r="19" spans="1:4" ht="15.75" customHeight="1">
-      <c r="A19" s="100" t="s">
+      <c r="A19" s="80" t="s">
         <v>54</v>
       </c>
-      <c r="B19" s="101">
+      <c r="B19" s="81">
         <v>2</v>
       </c>
-      <c r="C19" s="97"/>
-      <c r="D19" s="97"/>
+      <c r="C19" s="78"/>
+      <c r="D19" s="78"/>
     </row>
     <row r="20" spans="1:4" ht="15.75" customHeight="1">
-      <c r="A20" s="100" t="s">
+      <c r="A20" s="80" t="s">
         <v>23</v>
       </c>
-      <c r="B20" s="101">
+      <c r="B20" s="81">
         <v>2</v>
       </c>
-      <c r="C20" s="97"/>
-      <c r="D20" s="97"/>
+      <c r="C20" s="78"/>
+      <c r="D20" s="78"/>
     </row>
     <row r="21" spans="1:4" ht="15.75" customHeight="1">
-      <c r="A21" s="97"/>
-      <c r="B21" s="98"/>
-      <c r="C21" s="97"/>
-      <c r="D21" s="97"/>
+      <c r="A21" s="78"/>
+      <c r="B21" s="79"/>
+      <c r="C21" s="78"/>
+      <c r="D21" s="78"/>
     </row>
     <row r="22" spans="1:4" ht="15.75" customHeight="1">
-      <c r="A22" s="97"/>
-      <c r="B22" s="98"/>
-      <c r="C22" s="97"/>
-      <c r="D22" s="97"/>
+      <c r="A22" s="78"/>
+      <c r="B22" s="79"/>
+      <c r="C22" s="78"/>
+      <c r="D22" s="78"/>
     </row>
     <row r="23" spans="1:4" ht="15.75" customHeight="1">
-      <c r="A23" s="97"/>
-      <c r="B23" s="98"/>
-      <c r="C23" s="97"/>
-      <c r="D23" s="97"/>
+      <c r="A23" s="78"/>
+      <c r="B23" s="79"/>
+      <c r="C23" s="78"/>
+      <c r="D23" s="78"/>
     </row>
     <row r="24" spans="1:4" ht="15.75" customHeight="1">
-      <c r="A24" s="97"/>
-      <c r="B24" s="98"/>
-      <c r="C24" s="97"/>
-      <c r="D24" s="97"/>
+      <c r="A24" s="78"/>
+      <c r="B24" s="79"/>
+      <c r="C24" s="78"/>
+      <c r="D24" s="78"/>
     </row>
     <row r="25" spans="1:4" ht="15.75" customHeight="1">
-      <c r="A25" s="97"/>
-      <c r="B25" s="98"/>
-      <c r="C25" s="97"/>
-      <c r="D25" s="97"/>
+      <c r="A25" s="78"/>
+      <c r="B25" s="79"/>
+      <c r="C25" s="78"/>
+      <c r="D25" s="78"/>
     </row>
     <row r="26" spans="1:4" ht="15.75" customHeight="1">
-      <c r="A26" s="97"/>
-      <c r="B26" s="98"/>
-      <c r="C26" s="97"/>
-      <c r="D26" s="97"/>
+      <c r="A26" s="78"/>
+      <c r="B26" s="79"/>
+      <c r="C26" s="78"/>
+      <c r="D26" s="78"/>
     </row>
     <row r="27" spans="1:4" ht="15.75" customHeight="1">
       <c r="B27" s="1"/>
@@ -10241,290 +10282,290 @@
   <dimension ref="A1:D36"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="12.6640625" defaultRowHeight="13"/>
   <cols>
-    <col min="1" max="1" width="50" style="105" customWidth="1"/>
-    <col min="2" max="2" width="4.33203125" style="105" customWidth="1"/>
-    <col min="3" max="3" width="28.83203125" style="105" customWidth="1"/>
-    <col min="4" max="4" width="160.33203125" style="105" customWidth="1"/>
-    <col min="5" max="16384" width="12.6640625" style="105"/>
+    <col min="1" max="1" width="50" style="85" customWidth="1"/>
+    <col min="2" max="2" width="4.33203125" style="85" customWidth="1"/>
+    <col min="3" max="3" width="28.83203125" style="85" customWidth="1"/>
+    <col min="4" max="4" width="160.33203125" style="85" customWidth="1"/>
+    <col min="5" max="16384" width="12.6640625" style="85"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:4" ht="47" customHeight="1">
-      <c r="A1" s="126" t="s">
+      <c r="A1" s="186" t="s">
         <v>187</v>
       </c>
-      <c r="B1" s="126"/>
-      <c r="C1" s="126"/>
-      <c r="D1" s="126"/>
+      <c r="B1" s="186"/>
+      <c r="C1" s="186"/>
+      <c r="D1" s="186"/>
     </row>
     <row r="2" spans="1:4" ht="23" customHeight="1">
-      <c r="A2" s="120"/>
-      <c r="B2" s="121" t="s">
+      <c r="A2" s="100"/>
+      <c r="B2" s="101" t="s">
         <v>2</v>
       </c>
-      <c r="C2" s="120" t="s">
+      <c r="C2" s="100" t="s">
         <v>4</v>
       </c>
-      <c r="D2" s="122" t="s">
+      <c r="D2" s="102" t="s">
         <v>5</v>
       </c>
     </row>
     <row r="3" spans="1:4" ht="17">
-      <c r="A3" s="123" t="s">
+      <c r="A3" s="103" t="s">
         <v>7</v>
       </c>
-      <c r="B3" s="109"/>
-      <c r="C3" s="109"/>
-      <c r="D3" s="109"/>
+      <c r="B3" s="89"/>
+      <c r="C3" s="89"/>
+      <c r="D3" s="89"/>
     </row>
     <row r="4" spans="1:4" ht="17">
-      <c r="A4" s="110" t="s">
+      <c r="A4" s="90" t="s">
         <v>9</v>
       </c>
-      <c r="B4" s="111">
+      <c r="B4" s="91">
         <v>1</v>
       </c>
-      <c r="C4" s="110"/>
-      <c r="D4" s="112" t="s">
+      <c r="C4" s="90"/>
+      <c r="D4" s="92" t="s">
         <v>11</v>
       </c>
     </row>
     <row r="5" spans="1:4" ht="17">
-      <c r="A5" s="110" t="s">
+      <c r="A5" s="90" t="s">
         <v>12</v>
       </c>
-      <c r="B5" s="111">
+      <c r="B5" s="91">
         <v>1</v>
       </c>
-      <c r="C5" s="110"/>
-      <c r="D5" s="112" t="s">
+      <c r="C5" s="90"/>
+      <c r="D5" s="92" t="s">
         <v>11</v>
       </c>
     </row>
     <row r="6" spans="1:4" ht="17">
-      <c r="A6" s="110" t="s">
+      <c r="A6" s="90" t="s">
         <v>14</v>
       </c>
-      <c r="B6" s="111">
+      <c r="B6" s="91">
         <v>1</v>
       </c>
-      <c r="C6" s="110"/>
-      <c r="D6" s="112" t="s">
+      <c r="C6" s="90"/>
+      <c r="D6" s="92" t="s">
         <v>11</v>
       </c>
     </row>
     <row r="7" spans="1:4" ht="34">
-      <c r="A7" s="110" t="s">
+      <c r="A7" s="90" t="s">
         <v>15</v>
       </c>
-      <c r="B7" s="111">
+      <c r="B7" s="91">
         <v>0</v>
       </c>
-      <c r="C7" s="110"/>
-      <c r="D7" s="113" t="s">
+      <c r="C7" s="90"/>
+      <c r="D7" s="93" t="s">
         <v>17</v>
       </c>
     </row>
     <row r="8" spans="1:4" ht="17">
-      <c r="A8" s="110" t="s">
+      <c r="A8" s="90" t="s">
         <v>29</v>
       </c>
-      <c r="B8" s="111">
+      <c r="B8" s="91">
         <v>1</v>
       </c>
-      <c r="C8" s="110"/>
-      <c r="D8" s="113" t="s">
+      <c r="C8" s="90"/>
+      <c r="D8" s="93" t="s">
         <v>30</v>
       </c>
     </row>
     <row r="9" spans="1:4" ht="17">
-      <c r="A9" s="110" t="s">
+      <c r="A9" s="90" t="s">
         <v>34</v>
       </c>
-      <c r="B9" s="111">
+      <c r="B9" s="91">
         <v>1</v>
       </c>
-      <c r="C9" s="110" t="s">
+      <c r="C9" s="90" t="s">
         <v>35</v>
       </c>
-      <c r="D9" s="113" t="s">
+      <c r="D9" s="93" t="s">
         <v>36</v>
       </c>
     </row>
     <row r="10" spans="1:4" ht="16">
-      <c r="A10" s="114"/>
-      <c r="B10" s="111"/>
-      <c r="C10" s="110"/>
-      <c r="D10" s="112"/>
+      <c r="A10" s="94"/>
+      <c r="B10" s="91"/>
+      <c r="C10" s="90"/>
+      <c r="D10" s="92"/>
     </row>
     <row r="11" spans="1:4" ht="17">
-      <c r="A11" s="110" t="s">
+      <c r="A11" s="90" t="s">
         <v>46</v>
       </c>
-      <c r="B11" s="111">
+      <c r="B11" s="91">
         <v>1</v>
       </c>
-      <c r="C11" s="110"/>
-      <c r="D11" s="112"/>
+      <c r="C11" s="90"/>
+      <c r="D11" s="92"/>
     </row>
     <row r="12" spans="1:4" ht="34">
-      <c r="A12" s="110" t="s">
+      <c r="A12" s="90" t="s">
         <v>48</v>
       </c>
-      <c r="B12" s="111">
+      <c r="B12" s="91">
         <v>1</v>
       </c>
-      <c r="C12" s="110" t="s">
+      <c r="C12" s="90" t="s">
         <v>49</v>
       </c>
-      <c r="D12" s="112"/>
+      <c r="D12" s="92"/>
     </row>
     <row r="13" spans="1:4" ht="17">
-      <c r="A13" s="124" t="s">
+      <c r="A13" s="104" t="s">
         <v>53</v>
       </c>
-      <c r="B13" s="116"/>
-      <c r="C13" s="115"/>
-      <c r="D13" s="115"/>
+      <c r="B13" s="96"/>
+      <c r="C13" s="95"/>
+      <c r="D13" s="95"/>
     </row>
     <row r="14" spans="1:4" ht="40">
-      <c r="A14" s="110" t="s">
+      <c r="A14" s="90" t="s">
         <v>56</v>
       </c>
-      <c r="B14" s="107" t="s">
+      <c r="B14" s="87" t="s">
         <v>58</v>
       </c>
-      <c r="C14" s="108"/>
-      <c r="D14" s="117" t="s">
+      <c r="C14" s="88"/>
+      <c r="D14" s="97" t="s">
         <v>175</v>
       </c>
     </row>
     <row r="15" spans="1:4" ht="17">
-      <c r="A15" s="112" t="s">
+      <c r="A15" s="92" t="s">
         <v>61</v>
       </c>
-      <c r="B15" s="107" t="s">
+      <c r="B15" s="87" t="s">
         <v>58</v>
       </c>
-      <c r="C15" s="108"/>
-      <c r="D15" s="117" t="s">
+      <c r="C15" s="88"/>
+      <c r="D15" s="97" t="s">
         <v>63</v>
       </c>
     </row>
     <row r="16" spans="1:4" ht="17">
-      <c r="A16" s="112" t="s">
+      <c r="A16" s="92" t="s">
         <v>68</v>
       </c>
-      <c r="B16" s="107" t="s">
+      <c r="B16" s="87" t="s">
         <v>58</v>
       </c>
-      <c r="C16" s="108"/>
-      <c r="D16" s="117" t="s">
+      <c r="C16" s="88"/>
+      <c r="D16" s="97" t="s">
         <v>185</v>
       </c>
     </row>
     <row r="17" spans="1:4" ht="34">
-      <c r="A17" s="112" t="s">
+      <c r="A17" s="92" t="s">
         <v>70</v>
       </c>
-      <c r="B17" s="107">
+      <c r="B17" s="87">
         <v>1</v>
       </c>
-      <c r="C17" s="118" t="s">
+      <c r="C17" s="98" t="s">
         <v>186</v>
       </c>
-      <c r="D17" s="117" t="s">
+      <c r="D17" s="97" t="s">
         <v>73</v>
       </c>
     </row>
     <row r="18" spans="1:4" ht="17">
-      <c r="A18" s="124" t="s">
+      <c r="A18" s="104" t="s">
         <v>76</v>
       </c>
-      <c r="B18" s="116"/>
-      <c r="C18" s="115"/>
-      <c r="D18" s="115"/>
+      <c r="B18" s="96"/>
+      <c r="C18" s="95"/>
+      <c r="D18" s="95"/>
     </row>
     <row r="19" spans="1:4" ht="17">
-      <c r="A19" s="110" t="s">
+      <c r="A19" s="90" t="s">
         <v>77</v>
       </c>
-      <c r="B19" s="111">
+      <c r="B19" s="91">
         <v>1</v>
       </c>
-      <c r="C19" s="110"/>
-      <c r="D19" s="112"/>
+      <c r="C19" s="90"/>
+      <c r="D19" s="92"/>
     </row>
     <row r="20" spans="1:4" ht="17">
-      <c r="A20" s="110" t="s">
+      <c r="A20" s="90" t="s">
         <v>79</v>
       </c>
-      <c r="B20" s="111">
+      <c r="B20" s="91">
         <v>1</v>
       </c>
-      <c r="C20" s="110"/>
-      <c r="D20" s="112"/>
+      <c r="C20" s="90"/>
+      <c r="D20" s="92"/>
     </row>
     <row r="21" spans="1:4" ht="34">
-      <c r="A21" s="110" t="s">
+      <c r="A21" s="90" t="s">
         <v>80</v>
       </c>
-      <c r="B21" s="111">
+      <c r="B21" s="91">
         <v>1</v>
       </c>
-      <c r="C21" s="110"/>
-      <c r="D21" s="113" t="s">
+      <c r="C21" s="90"/>
+      <c r="D21" s="93" t="s">
         <v>81</v>
       </c>
     </row>
     <row r="22" spans="1:4" ht="68">
-      <c r="A22" s="110" t="s">
+      <c r="A22" s="90" t="s">
         <v>84</v>
       </c>
-      <c r="B22" s="111">
+      <c r="B22" s="91">
         <v>1</v>
       </c>
-      <c r="C22" s="110"/>
-      <c r="D22" s="113" t="s">
+      <c r="C22" s="90"/>
+      <c r="D22" s="93" t="s">
         <v>85</v>
       </c>
     </row>
     <row r="23" spans="1:4" ht="14">
-      <c r="A23" s="125" t="s">
+      <c r="A23" s="105" t="s">
         <v>86</v>
       </c>
-      <c r="B23" s="109"/>
-      <c r="C23" s="109"/>
-      <c r="D23" s="109"/>
+      <c r="B23" s="89"/>
+      <c r="C23" s="89"/>
+      <c r="D23" s="89"/>
     </row>
     <row r="24" spans="1:4" ht="14">
-      <c r="A24" s="114" t="s">
+      <c r="A24" s="94" t="s">
         <v>87</v>
       </c>
-      <c r="B24" s="114">
+      <c r="B24" s="94">
         <v>1</v>
       </c>
-      <c r="C24" s="114"/>
-      <c r="D24" s="119" t="s">
+      <c r="C24" s="94"/>
+      <c r="D24" s="99" t="s">
         <v>88</v>
       </c>
     </row>
     <row r="29" spans="1:4">
-      <c r="D29" s="106"/>
+      <c r="D29" s="86"/>
     </row>
     <row r="30" spans="1:4">
-      <c r="D30" s="106"/>
+      <c r="D30" s="86"/>
     </row>
     <row r="32" spans="1:4">
-      <c r="D32" s="106"/>
+      <c r="D32" s="86"/>
     </row>
     <row r="33" spans="4:4">
-      <c r="D33" s="106"/>
+      <c r="D33" s="86"/>
     </row>
     <row r="35" spans="4:4">
-      <c r="D35" s="106"/>
+      <c r="D35" s="86"/>
     </row>
     <row r="36" spans="4:4">
-      <c r="D36" s="106"/>
+      <c r="D36" s="86"/>
     </row>
   </sheetData>
   <mergeCells count="1">

--- a/hardware/bom/master_bom.xlsx
+++ b/hardware/bom/master_bom.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Volumes/POLI/Magistrale/21_ACAV/f1tenth_PoliMI/hardware/bom/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{87C25656-06EC-F340-8227-D2DEED38C3E3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D02418E1-894F-8C46-BCCD-FD479C975720}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="4360" yWindow="660" windowWidth="30200" windowHeight="19820" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -646,51 +646,6 @@
   </si>
   <si>
     <t>https://openelab.io/products/orbbec-gemini-335l-stereo-camera?srsltid=AU7gw4WV_LMucG3H9iXtPq4gxBth5IaVVh1p7ClCoNp5OEf0dFrP1rbj</t>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">Choose ONE of the listed cameras - </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="18"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-      </rPr>
-      <t>ONE LEFT IN STOCK</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="18"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">
-</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">Orbbec Gemini 335L </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-      </rPr>
-      <t>is by far the best choice. Global shutter, Stereo Vision, 60fps @ 1080p, 6DoF IMU</t>
-    </r>
   </si>
   <si>
     <t>https://www.digikey.it/it/products/detail/orbbec/100100478/23024082?srsltid=AU7gw4WokcDz96KtNyGnA0IWpYbt4VXk_WfC6iO1PVKhbTkxg6MTspV0</t>
@@ -749,6 +704,51 @@
   </si>
   <si>
     <t>Updated: 2026-10-7</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Choose ONE of the listed cameras - </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="18"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t>ONE LEFT IN STOCK</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="18"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">Orbbec Gemini 335L </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t>is by far the best choice. Global shutter, Stereo Vision, 60fps @ 800p, 6DoF IMU</t>
+    </r>
   </si>
 </sst>
 </file>
@@ -2020,6 +2020,33 @@
     <xf numFmtId="0" fontId="3" fillId="4" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="52" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="19" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1"/>
+    <xf numFmtId="164" fontId="4" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="35" fillId="6" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="31" fillId="5" borderId="7" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="6" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="4" fillId="5" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
@@ -2035,10 +2062,6 @@
     <xf numFmtId="0" fontId="34" fillId="5" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="4" fillId="6" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
@@ -2046,32 +2069,9 @@
     <xf numFmtId="0" fontId="34" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="52" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="19" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="4" fillId="5" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="4" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="35" fillId="6" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="31" fillId="5" borderId="7" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="34" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="6" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="10" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -2330,15 +2330,15 @@
   <sheetData>
     <row r="2" spans="1:8" s="74" customFormat="1" ht="47" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
       <c r="A2" s="95"/>
-      <c r="B2" s="178" t="s">
+      <c r="B2" s="168" t="s">
         <v>0</v>
       </c>
-      <c r="C2" s="179"/>
-      <c r="D2" s="179"/>
-      <c r="E2" s="179"/>
-      <c r="F2" s="179"/>
-      <c r="G2" s="179"/>
-      <c r="H2" s="179"/>
+      <c r="C2" s="169"/>
+      <c r="D2" s="169"/>
+      <c r="E2" s="169"/>
+      <c r="F2" s="169"/>
+      <c r="G2" s="169"/>
+      <c r="H2" s="169"/>
     </row>
     <row r="3" spans="1:8" s="33" customFormat="1" ht="23" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
       <c r="B3" s="61" t="s">
@@ -2375,7 +2375,7 @@
       <c r="H4" s="60"/>
     </row>
     <row r="5" spans="1:8" ht="17" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B5" s="188" t="s">
+      <c r="B5" s="179" t="s">
         <v>9</v>
       </c>
       <c r="C5" s="49">
@@ -2389,7 +2389,7 @@
         <v>479.9</v>
       </c>
       <c r="F5" s="16"/>
-      <c r="G5" s="183" t="s">
+      <c r="G5" s="175" t="s">
         <v>188</v>
       </c>
       <c r="H5" s="40" t="s">
@@ -2397,7 +2397,7 @@
       </c>
     </row>
     <row r="6" spans="1:8" ht="17" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B6" s="189"/>
+      <c r="B6" s="180"/>
       <c r="C6" s="49">
         <v>1</v>
       </c>
@@ -2411,13 +2411,13 @@
       <c r="F6" s="16" t="s">
         <v>11</v>
       </c>
-      <c r="G6" s="184"/>
+      <c r="G6" s="176"/>
       <c r="H6" s="40" t="s">
         <v>12</v>
       </c>
     </row>
     <row r="7" spans="1:8" ht="17" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B7" s="189"/>
+      <c r="B7" s="180"/>
       <c r="C7" s="49">
         <v>1</v>
       </c>
@@ -2429,7 +2429,7 @@
         <v>425</v>
       </c>
       <c r="F7" s="16"/>
-      <c r="G7" s="184"/>
+      <c r="G7" s="176"/>
       <c r="H7" s="40" t="s">
         <v>13</v>
       </c>
@@ -2589,23 +2589,23 @@
       <c r="B15" s="53" t="s">
         <v>31</v>
       </c>
-      <c r="C15" s="180">
+      <c r="C15" s="170">
         <v>1</v>
       </c>
-      <c r="D15" s="173">
+      <c r="D15" s="174">
         <v>12</v>
       </c>
-      <c r="E15" s="173">
+      <c r="E15" s="174">
         <f>C15*D15</f>
         <v>12</v>
       </c>
-      <c r="F15" s="173" t="s">
+      <c r="F15" s="174" t="s">
         <v>11</v>
       </c>
-      <c r="G15" s="182" t="s">
+      <c r="G15" s="172" t="s">
         <v>32</v>
       </c>
-      <c r="H15" s="185" t="s">
+      <c r="H15" s="177" t="s">
         <v>33</v>
       </c>
     </row>
@@ -2613,12 +2613,12 @@
       <c r="B16" s="53" t="s">
         <v>34</v>
       </c>
-      <c r="C16" s="181"/>
-      <c r="D16" s="174"/>
-      <c r="E16" s="174"/>
-      <c r="F16" s="174"/>
-      <c r="G16" s="174"/>
-      <c r="H16" s="186"/>
+      <c r="C16" s="171"/>
+      <c r="D16" s="173"/>
+      <c r="E16" s="173"/>
+      <c r="F16" s="173"/>
+      <c r="G16" s="173"/>
+      <c r="H16" s="178"/>
     </row>
     <row r="17" spans="2:17" ht="17" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B17" s="54" t="s">
@@ -2728,7 +2728,7 @@
       <c r="F21" s="14" t="s">
         <v>11</v>
       </c>
-      <c r="G21" s="177" t="s">
+      <c r="G21" s="188" t="s">
         <v>46</v>
       </c>
       <c r="H21" s="44" t="s">
@@ -2756,7 +2756,7 @@
         <v>529</v>
       </c>
       <c r="F22" s="14"/>
-      <c r="G22" s="174"/>
+      <c r="G22" s="173"/>
       <c r="H22" s="44" t="s">
         <v>48</v>
       </c>
@@ -2835,8 +2835,8 @@
         <v>1200</v>
       </c>
       <c r="F25" s="14"/>
-      <c r="G25" s="170" t="s">
-        <v>193</v>
+      <c r="G25" s="183" t="s">
+        <v>192</v>
       </c>
       <c r="H25" s="47" t="s">
         <v>53</v>
@@ -2868,7 +2868,7 @@
       <c r="F26" s="14" t="s">
         <v>11</v>
       </c>
-      <c r="G26" s="184"/>
+      <c r="G26" s="176"/>
       <c r="H26" s="44" t="s">
         <v>55</v>
       </c>
@@ -2897,7 +2897,7 @@
         <v>553.44000000000005</v>
       </c>
       <c r="F27" s="14"/>
-      <c r="G27" s="184"/>
+      <c r="G27" s="176"/>
       <c r="H27" s="44" t="s">
         <v>57</v>
       </c>
@@ -2926,7 +2926,7 @@
         <v>442.53</v>
       </c>
       <c r="F28" s="14"/>
-      <c r="G28" s="184"/>
+      <c r="G28" s="176"/>
       <c r="H28" s="44" t="s">
         <v>59</v>
       </c>
@@ -3151,7 +3151,7 @@
       <c r="Q35" s="34"/>
     </row>
     <row r="36" spans="2:17" ht="17" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B36" s="175" t="s">
+      <c r="B36" s="186" t="s">
         <v>74</v>
       </c>
       <c r="C36" s="49">
@@ -3165,7 +3165,7 @@
         <v>13</v>
       </c>
       <c r="F36" s="16"/>
-      <c r="G36" s="187" t="s">
+      <c r="G36" s="189" t="s">
         <v>189</v>
       </c>
       <c r="H36" s="40" t="s">
@@ -3182,7 +3182,7 @@
       <c r="Q36" s="34"/>
     </row>
     <row r="37" spans="2:17" ht="17" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B37" s="176"/>
+      <c r="B37" s="187"/>
       <c r="C37" s="49">
         <v>1</v>
       </c>
@@ -3196,7 +3196,7 @@
       <c r="F37" s="16" t="s">
         <v>11</v>
       </c>
-      <c r="G37" s="174"/>
+      <c r="G37" s="173"/>
       <c r="H37" s="40" t="s">
         <v>76</v>
       </c>
@@ -3225,8 +3225,8 @@
         <v>405</v>
       </c>
       <c r="F38" s="14"/>
-      <c r="G38" s="170" t="s">
-        <v>191</v>
+      <c r="G38" s="183" t="s">
+        <v>196</v>
       </c>
       <c r="H38" s="41" t="s">
         <v>78</v>
@@ -3242,7 +3242,7 @@
       <c r="Q38" s="34"/>
     </row>
     <row r="39" spans="2:17" ht="17" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B39" s="168" t="s">
+      <c r="B39" s="181" t="s">
         <v>79</v>
       </c>
       <c r="C39" s="50">
@@ -3258,7 +3258,7 @@
       <c r="F39" s="14" t="s">
         <v>11</v>
       </c>
-      <c r="G39" s="171"/>
+      <c r="G39" s="184"/>
       <c r="H39" s="41" t="s">
         <v>190</v>
       </c>
@@ -3273,7 +3273,7 @@
       <c r="Q39" s="34"/>
     </row>
     <row r="40" spans="2:17" ht="17" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B40" s="169"/>
+      <c r="B40" s="182"/>
       <c r="C40" s="50">
         <v>1</v>
       </c>
@@ -3285,9 +3285,9 @@
         <v>408</v>
       </c>
       <c r="F40" s="14"/>
-      <c r="G40" s="172"/>
+      <c r="G40" s="185"/>
       <c r="H40" s="41" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="I40" s="34"/>
       <c r="J40" s="34"/>
@@ -3602,7 +3602,7 @@
       </c>
       <c r="F51" s="10"/>
       <c r="G51" s="7" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="H51" s="164"/>
       <c r="I51" s="34"/>
@@ -3618,14 +3618,14 @@
     <row r="52" spans="2:17" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
       <c r="B52" s="157"/>
       <c r="C52" s="166" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="D52" s="165">
         <v>0.22</v>
       </c>
       <c r="E52" s="158">
-        <f>E51*(1-D52)</f>
-        <v>2012.1971999999992</v>
+        <f>E51/(1+D52)</f>
+        <v>2114.5409836065564</v>
       </c>
       <c r="F52" s="159"/>
       <c r="G52" s="160" t="str">
@@ -3645,7 +3645,7 @@
     </row>
     <row r="54" spans="2:17" ht="17" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B54" s="66" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="C54" s="9"/>
       <c r="D54" s="10"/>
@@ -5064,13 +5064,6 @@
     </row>
   </sheetData>
   <mergeCells count="15">
-    <mergeCell ref="B2:H2"/>
-    <mergeCell ref="C15:C16"/>
-    <mergeCell ref="G15:G16"/>
-    <mergeCell ref="E15:E16"/>
-    <mergeCell ref="G5:G7"/>
-    <mergeCell ref="H15:H16"/>
-    <mergeCell ref="B5:B7"/>
     <mergeCell ref="B39:B40"/>
     <mergeCell ref="G38:G40"/>
     <mergeCell ref="F15:F16"/>
@@ -5079,6 +5072,13 @@
     <mergeCell ref="G21:G22"/>
     <mergeCell ref="G36:G37"/>
     <mergeCell ref="G25:G28"/>
+    <mergeCell ref="B2:H2"/>
+    <mergeCell ref="C15:C16"/>
+    <mergeCell ref="G15:G16"/>
+    <mergeCell ref="E15:E16"/>
+    <mergeCell ref="G5:G7"/>
+    <mergeCell ref="H15:H16"/>
+    <mergeCell ref="B5:B7"/>
   </mergeCells>
   <hyperlinks>
     <hyperlink ref="H5" r:id="rId1" xr:uid="{00000000-0004-0000-0000-000000000000}"/>

--- a/hardware/bom/master_bom.xlsx
+++ b/hardware/bom/master_bom.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10927"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11011"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Volumes/POLI/Magistrale/21_ACAV/f1tenth_PoliMI/hardware/bom/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D02418E1-894F-8C46-BCCD-FD479C975720}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0D641C2E-F454-0443-81A2-8850F3BD84D4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="4360" yWindow="660" windowWidth="30200" windowHeight="19820" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="660" windowWidth="34560" windowHeight="21680" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="(POLIMI) Rally + Orin Nano v1" sheetId="1" r:id="rId1"/>
@@ -1525,7 +1525,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="30" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="198">
+  <cellXfs count="199">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -2093,6 +2093,9 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="18" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="52" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="31" fillId="10" borderId="7" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -3259,7 +3262,7 @@
         <v>11</v>
       </c>
       <c r="G39" s="184"/>
-      <c r="H39" s="41" t="s">
+      <c r="H39" s="198" t="s">
         <v>190</v>
       </c>
       <c r="I39" s="34"/>
